--- a/Form_Processing.xlsx
+++ b/Form_Processing.xlsx
@@ -411,7 +411,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>From - 15/07/2026       To - 13/09/2026</v>
+        <v>From - 15/07/2026       To - 14/09/2026</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>FORM6</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -537,7 +537,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -637,7 +637,7 @@
         <v>AC Form Total</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>8</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -735,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9">
         <v>1</v>
@@ -747,10 +747,10 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="R9">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -868,10 +868,10 @@
         <v>0</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>3</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>18</v>
       </c>
       <c r="G12">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -933,16 +933,16 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12">
         <v>4</v>
@@ -954,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="R12">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1306,7 +1306,7 @@
         <v>41</v>
       </c>
       <c r="R17">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -1365,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="R18">
         <v>11</v>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -1510,10 +1510,10 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="R20">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -1542,49 +1542,49 @@
         <v>FORM6</v>
       </c>
       <c r="D21">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
+        <v>27</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>4</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
         <v>24</v>
       </c>
-      <c r="G21">
-        <v>4</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>15</v>
-      </c>
-      <c r="N21">
-        <v>2</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>21</v>
-      </c>
       <c r="R21">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="R23">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -1797,7 +1797,7 @@
         <v>15</v>
       </c>
       <c r="R24">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -1820,16 +1820,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D25">
-        <v>3391</v>
+        <v>3394</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1844,13 +1844,13 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="N25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="R25">
-        <v>1073</v>
+        <v>1137</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>FORM6</v>
       </c>
       <c r="D26">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -2033,13 +2033,13 @@
         <v>FORM8</v>
       </c>
       <c r="D28">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -2098,13 +2098,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D29">
-        <v>3454</v>
+        <v>3456</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -2190,10 +2190,10 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -2208,10 +2208,10 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="R30">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         <v>151</v>
       </c>
       <c r="R32">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -2382,13 +2382,13 @@
         <v>FORM8</v>
       </c>
       <c r="D33">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -2447,13 +2447,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D34">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -2468,10 +2468,10 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L34">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2486,10 +2486,10 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="R34">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L35">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -2557,10 +2557,10 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R35">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -2702,7 +2702,7 @@
         <v>87</v>
       </c>
       <c r="R37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L39">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -2835,10 +2835,10 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R39">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -2867,16 +2867,16 @@
         <v>FORM6</v>
       </c>
       <c r="D40">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -2909,7 +2909,7 @@
         <v>28</v>
       </c>
       <c r="R40">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -3074,16 +3074,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D43">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -3095,13 +3095,13 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L43">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -3116,7 +3116,7 @@
         <v>198</v>
       </c>
       <c r="R43">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>FORM6</v>
       </c>
       <c r="D44">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -3163,13 +3163,13 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K44">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R44">
-        <v>275</v>
+        <v>356</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -3287,7 +3287,7 @@
         <v>FORM8</v>
       </c>
       <c r="D46">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3308,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R46">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -3352,13 +3352,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D47">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -3370,13 +3370,13 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="L47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -3391,10 +3391,10 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="R47">
-        <v>324</v>
+        <v>411</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -3423,13 +3423,13 @@
         <v>FORM6</v>
       </c>
       <c r="D48">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -3444,10 +3444,10 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="L48">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>5</v>
       </c>
       <c r="R48">
-        <v>224</v>
+        <v>257</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="U48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48">
         <v>0</v>
@@ -3565,13 +3565,13 @@
         <v>FORM8</v>
       </c>
       <c r="D50">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -3630,13 +3630,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D51">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -3651,10 +3651,10 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="L51">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -3672,7 +3672,7 @@
         <v>27</v>
       </c>
       <c r="R51">
-        <v>352</v>
+        <v>385</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="U51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51">
         <v>0</v>
@@ -3701,13 +3701,13 @@
         <v>FORM6</v>
       </c>
       <c r="D52">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E52">
         <v>0</v>
       </c>
       <c r="F52">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -3740,10 +3740,10 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R52">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -3914,13 +3914,13 @@
         <v>FORM8</v>
       </c>
       <c r="D55">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -3979,13 +3979,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D56">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -4000,10 +4000,10 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L56">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M56">
         <v>0</v>
@@ -4018,10 +4018,10 @@
         <v>0</v>
       </c>
       <c r="Q56">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="R56">
-        <v>1144</v>
+        <v>1151</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -4089,10 +4089,10 @@
         <v>0</v>
       </c>
       <c r="Q57">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R57">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -4192,13 +4192,13 @@
         <v>FORM8</v>
       </c>
       <c r="D59">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E59">
         <v>0</v>
       </c>
       <c r="F59">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -4257,13 +4257,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D60">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="E60">
         <v>0</v>
       </c>
       <c r="F60">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -4278,7 +4278,7 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -4296,10 +4296,10 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="R60">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -4349,10 +4349,10 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M61">
         <v>0</v>
@@ -4370,7 +4370,7 @@
         <v>28</v>
       </c>
       <c r="R61">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -4583,7 +4583,7 @@
         <v>19</v>
       </c>
       <c r="R64">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -4592,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="U64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V64">
         <v>0</v>
@@ -4627,10 +4627,10 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L65">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M65">
         <v>0</v>
@@ -4648,7 +4648,7 @@
         <v>117</v>
       </c>
       <c r="R65">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="U65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V65">
         <v>0</v>
@@ -5047,16 +5047,16 @@
         <v>0</v>
       </c>
       <c r="K71">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="L71">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M71">
         <v>0</v>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5065,10 +5065,10 @@
         <v>0</v>
       </c>
       <c r="Q71">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="R71">
-        <v>2194</v>
+        <v>2208</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -5097,7 +5097,7 @@
         <v>FORM7</v>
       </c>
       <c r="D72">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="K72">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -5127,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5168,13 +5168,13 @@
         <v>FORM8</v>
       </c>
       <c r="D73">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -5233,13 +5233,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D74">
-        <v>4373</v>
+        <v>4378</v>
       </c>
       <c r="E74">
         <v>0</v>
       </c>
       <c r="F74">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G74">
         <v>11</v>
@@ -5254,16 +5254,16 @@
         <v>0</v>
       </c>
       <c r="K74">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="L74">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M74">
         <v>0</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -5272,10 +5272,10 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="R74">
-        <v>2950</v>
+        <v>2964</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -5304,16 +5304,16 @@
         <v>FORM6</v>
       </c>
       <c r="D75">
-        <v>3693</v>
+        <v>3695</v>
       </c>
       <c r="E75">
         <v>0</v>
       </c>
       <c r="F75">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G75">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -5325,10 +5325,10 @@
         <v>327</v>
       </c>
       <c r="K75">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="L75">
-        <v>1031</v>
+        <v>1013</v>
       </c>
       <c r="M75">
         <v>0</v>
@@ -5346,7 +5346,7 @@
         <v>8</v>
       </c>
       <c r="R75">
-        <v>1748</v>
+        <v>1766</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -5355,7 +5355,7 @@
         <v>0</v>
       </c>
       <c r="U75">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="V75">
         <v>0</v>
@@ -5532,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>321</v>
+        <v>140</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -5556,10 +5556,10 @@
         <v>0</v>
       </c>
       <c r="Q78">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="R78">
-        <v>746</v>
+        <v>908</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -5582,31 +5582,31 @@
         <v>AC Form Total</v>
       </c>
       <c r="D79">
-        <v>6589</v>
+        <v>6591</v>
       </c>
       <c r="E79">
         <v>0</v>
       </c>
       <c r="F79">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G79">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H79">
         <v>0</v>
       </c>
       <c r="I79">
-        <v>326</v>
+        <v>145</v>
       </c>
       <c r="J79">
         <v>327</v>
       </c>
       <c r="K79">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="L79">
-        <v>1031</v>
+        <v>1013</v>
       </c>
       <c r="M79">
         <v>0</v>
@@ -5621,10 +5621,10 @@
         <v>0</v>
       </c>
       <c r="Q79">
-        <v>1414</v>
+        <v>1433</v>
       </c>
       <c r="R79">
-        <v>2617</v>
+        <v>2797</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -5633,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="U79">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="V79">
         <v>0</v>
@@ -5653,13 +5653,13 @@
         <v>FORM6</v>
       </c>
       <c r="D80">
-        <v>4742</v>
+        <v>4751</v>
       </c>
       <c r="E80">
         <v>0</v>
       </c>
       <c r="F80">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="G80">
         <v>111</v>
@@ -5677,16 +5677,16 @@
         <v>234</v>
       </c>
       <c r="L80">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="M80">
         <v>2</v>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O80">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P80">
         <v>0</v>
@@ -5695,7 +5695,7 @@
         <v>63</v>
       </c>
       <c r="R80">
-        <v>3198</v>
+        <v>3215</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -5866,13 +5866,13 @@
         <v>FORM8</v>
       </c>
       <c r="D83">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="E83">
         <v>0</v>
       </c>
       <c r="F83">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G83">
         <v>2</v>
@@ -5881,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>515</v>
+        <v>178</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="Q83">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="R83">
-        <v>743</v>
+        <v>1070</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -5931,13 +5931,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D84">
-        <v>7234</v>
+        <v>7246</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
       <c r="F84">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="G84">
         <v>113</v>
@@ -5946,7 +5946,7 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>523</v>
+        <v>186</v>
       </c>
       <c r="J84">
         <v>23</v>
@@ -5955,25 +5955,25 @@
         <v>234</v>
       </c>
       <c r="L84">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="M84">
         <v>2</v>
       </c>
       <c r="N84">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O84">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P84">
         <v>0</v>
       </c>
       <c r="Q84">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="R84">
-        <v>4275</v>
+        <v>4619</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -6002,49 +6002,49 @@
         <v>FORM6</v>
       </c>
       <c r="D85">
-        <v>9576</v>
+        <v>9596</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="G85">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="H85">
         <v>10</v>
       </c>
       <c r="I85">
-        <v>536</v>
+        <v>615</v>
       </c>
       <c r="J85">
-        <v>272</v>
+        <v>97</v>
       </c>
       <c r="K85">
+        <v>459</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>18</v>
+      </c>
+      <c r="N85">
         <v>456</v>
       </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>20</v>
-      </c>
-      <c r="N85">
-        <v>610</v>
-      </c>
       <c r="O85">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P85">
         <v>0</v>
       </c>
       <c r="Q85">
-        <v>643</v>
+        <v>657</v>
       </c>
       <c r="R85">
-        <v>6226</v>
+        <v>6498</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>0</v>
       </c>
       <c r="U85">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="V85">
         <v>0</v>
@@ -6215,16 +6215,16 @@
         <v>FORM8</v>
       </c>
       <c r="D88">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="E88">
         <v>0</v>
       </c>
       <c r="F88">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>7</v>
       </c>
       <c r="N88">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O88">
         <v>1</v>
@@ -6280,49 +6280,49 @@
         <v>AC Form Total</v>
       </c>
       <c r="D89">
-        <v>13185</v>
+        <v>13207</v>
       </c>
       <c r="E89">
         <v>0</v>
       </c>
       <c r="F89">
-        <v>752</v>
+        <v>773</v>
       </c>
       <c r="G89">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="H89">
         <v>10</v>
       </c>
       <c r="I89">
-        <v>666</v>
+        <v>745</v>
       </c>
       <c r="J89">
-        <v>291</v>
+        <v>116</v>
       </c>
       <c r="K89">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L89">
         <v>0</v>
       </c>
       <c r="M89">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N89">
-        <v>636</v>
+        <v>483</v>
       </c>
       <c r="O89">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P89">
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>1732</v>
+        <v>1746</v>
       </c>
       <c r="R89">
-        <v>8282</v>
+        <v>8554</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -6331,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="U89">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="V89">
         <v>0</v>
@@ -6351,16 +6351,16 @@
         <v>FORM6</v>
       </c>
       <c r="D90">
-        <v>4854</v>
+        <v>4862</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
       <c r="F90">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="G90">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -6369,13 +6369,13 @@
         <v>0</v>
       </c>
       <c r="J90">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K90">
         <v>0</v>
       </c>
       <c r="L90">
-        <v>1151</v>
+        <v>1081</v>
       </c>
       <c r="M90">
         <v>26</v>
@@ -6384,16 +6384,16 @@
         <v>19</v>
       </c>
       <c r="O90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P90">
         <v>0</v>
       </c>
       <c r="Q90">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R90">
-        <v>2739</v>
+        <v>2803</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -6514,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="Q92">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="R92">
         <v>128</v>
@@ -6564,13 +6564,13 @@
         <v>FORM8</v>
       </c>
       <c r="D93">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="E93">
         <v>0</v>
       </c>
       <c r="F93">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -6629,16 +6629,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D94">
-        <v>8712</v>
+        <v>8721</v>
       </c>
       <c r="E94">
         <v>0</v>
       </c>
       <c r="F94">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="G94">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -6647,13 +6647,13 @@
         <v>120</v>
       </c>
       <c r="J94">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L94">
-        <v>1262</v>
+        <v>1192</v>
       </c>
       <c r="M94">
         <v>26</v>
@@ -6662,16 +6662,16 @@
         <v>21</v>
       </c>
       <c r="O94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P94">
         <v>0</v>
       </c>
       <c r="Q94">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="R94">
-        <v>4217</v>
+        <v>4281</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -6700,13 +6700,13 @@
         <v>FORM6</v>
       </c>
       <c r="D95">
-        <v>3985</v>
+        <v>3989</v>
       </c>
       <c r="E95">
         <v>0</v>
       </c>
       <c r="F95">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G95">
         <v>22</v>
@@ -6842,7 +6842,7 @@
         <v>FORM7</v>
       </c>
       <c r="D97">
-        <v>3817</v>
+        <v>3818</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -6913,13 +6913,13 @@
         <v>FORM8</v>
       </c>
       <c r="D98">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="E98">
         <v>0</v>
       </c>
       <c r="F98">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -6978,13 +6978,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D99">
-        <v>8941</v>
+        <v>8950</v>
       </c>
       <c r="E99">
         <v>0</v>
       </c>
       <c r="F99">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="G99">
         <v>22</v>
@@ -6999,7 +6999,7 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -7049,13 +7049,13 @@
         <v>FORM6</v>
       </c>
       <c r="D100">
-        <v>3462</v>
+        <v>3469</v>
       </c>
       <c r="E100">
         <v>0</v>
       </c>
       <c r="F100">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -7073,7 +7073,7 @@
         <v>279</v>
       </c>
       <c r="L100">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="M100">
         <v>10</v>
@@ -7088,10 +7088,10 @@
         <v>0</v>
       </c>
       <c r="Q100">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R100">
-        <v>2112</v>
+        <v>2156</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -7327,13 +7327,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D104">
-        <v>5810</v>
+        <v>5817</v>
       </c>
       <c r="E104">
         <v>0</v>
       </c>
       <c r="F104">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -7351,7 +7351,7 @@
         <v>283</v>
       </c>
       <c r="L104">
-        <v>413</v>
+        <v>365</v>
       </c>
       <c r="M104">
         <v>10</v>
@@ -7366,10 +7366,10 @@
         <v>0</v>
       </c>
       <c r="Q104">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="R104">
-        <v>3040</v>
+        <v>3084</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -7398,13 +7398,13 @@
         <v>FORM6</v>
       </c>
       <c r="D105">
-        <v>4894</v>
+        <v>4895</v>
       </c>
       <c r="E105">
         <v>0</v>
       </c>
       <c r="F105">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G105">
         <v>31</v>
@@ -7422,7 +7422,7 @@
         <v>377</v>
       </c>
       <c r="L105">
-        <v>783</v>
+        <v>115</v>
       </c>
       <c r="M105">
         <v>1</v>
@@ -7431,16 +7431,16 @@
         <v>18</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P105">
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>530</v>
+        <v>881</v>
       </c>
       <c r="R105">
-        <v>2311</v>
+        <v>2633</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -7449,7 +7449,7 @@
         <v>0</v>
       </c>
       <c r="U105">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V105">
         <v>0</v>
@@ -7611,13 +7611,13 @@
         <v>FORM8</v>
       </c>
       <c r="D108">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E108">
         <v>0</v>
       </c>
       <c r="F108">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G108">
         <v>4</v>
@@ -7676,13 +7676,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D109">
-        <v>10431</v>
+        <v>10433</v>
       </c>
       <c r="E109">
         <v>0</v>
       </c>
       <c r="F109">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G109">
         <v>35</v>
@@ -7700,7 +7700,7 @@
         <v>377</v>
       </c>
       <c r="L109">
-        <v>783</v>
+        <v>115</v>
       </c>
       <c r="M109">
         <v>2</v>
@@ -7709,16 +7709,16 @@
         <v>44</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109">
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>1959</v>
+        <v>2310</v>
       </c>
       <c r="R109">
-        <v>3363</v>
+        <v>3685</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -7727,7 +7727,7 @@
         <v>0</v>
       </c>
       <c r="U109">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="V109">
         <v>0</v>
@@ -7747,13 +7747,13 @@
         <v>FORM6</v>
       </c>
       <c r="D110">
-        <v>5097</v>
+        <v>5122</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="F110">
-        <v>667</v>
+        <v>692</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -7771,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="L110">
-        <v>1043</v>
+        <v>1008</v>
       </c>
       <c r="M110">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N110">
         <v>3</v>
@@ -7789,7 +7789,7 @@
         <v>20</v>
       </c>
       <c r="R110">
-        <v>3330</v>
+        <v>3362</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -7960,13 +7960,13 @@
         <v>FORM8</v>
       </c>
       <c r="D113">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
       <c r="F113">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -8025,13 +8025,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D114">
-        <v>12088</v>
+        <v>12114</v>
       </c>
       <c r="E114">
         <v>0</v>
       </c>
       <c r="F114">
-        <v>870</v>
+        <v>896</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -8049,10 +8049,10 @@
         <v>0</v>
       </c>
       <c r="L114">
-        <v>1043</v>
+        <v>1008</v>
       </c>
       <c r="M114">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N114">
         <v>55</v>
@@ -8067,7 +8067,7 @@
         <v>1331</v>
       </c>
       <c r="R114">
-        <v>5316</v>
+        <v>5348</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -8096,37 +8096,37 @@
         <v>FORM6</v>
       </c>
       <c r="D115">
-        <v>5065</v>
+        <v>5098</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="G115">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="H115">
         <v>0</v>
       </c>
       <c r="I115">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="L115">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="M115">
         <v>1</v>
       </c>
       <c r="N115">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -8138,7 +8138,7 @@
         <v>24</v>
       </c>
       <c r="R115">
-        <v>2043</v>
+        <v>2057</v>
       </c>
       <c r="S115">
         <v>0</v>
@@ -8309,13 +8309,13 @@
         <v>FORM8</v>
       </c>
       <c r="D118">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="E118">
         <v>0</v>
       </c>
       <c r="F118">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -8374,37 +8374,37 @@
         <v>AC Form Total</v>
       </c>
       <c r="D119">
-        <v>8018</v>
+        <v>8052</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
       <c r="F119">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="G119">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="H119">
         <v>0</v>
       </c>
       <c r="I119">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="L119">
-        <v>1096</v>
+        <v>1089</v>
       </c>
       <c r="M119">
         <v>1</v>
       </c>
       <c r="N119">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="O119">
         <v>0</v>
@@ -8416,7 +8416,7 @@
         <v>965</v>
       </c>
       <c r="R119">
-        <v>3138</v>
+        <v>3152</v>
       </c>
       <c r="S119">
         <v>0</v>
@@ -8445,13 +8445,13 @@
         <v>FORM6</v>
       </c>
       <c r="D120">
-        <v>5668</v>
+        <v>5674</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -8466,13 +8466,13 @@
         <v>4</v>
       </c>
       <c r="K120">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="L120">
-        <v>1123</v>
+        <v>1140</v>
       </c>
       <c r="M120">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N120">
         <v>106</v>
@@ -8484,10 +8484,10 @@
         <v>0</v>
       </c>
       <c r="Q120">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R120">
-        <v>3883</v>
+        <v>3943</v>
       </c>
       <c r="S120">
         <v>0</v>
@@ -8587,13 +8587,13 @@
         <v>FORM8</v>
       </c>
       <c r="D122">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="E122">
         <v>0</v>
       </c>
       <c r="F122">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G122">
         <v>64</v>
@@ -8652,13 +8652,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D123">
-        <v>6846</v>
+        <v>6858</v>
       </c>
       <c r="E123">
         <v>0</v>
       </c>
       <c r="F123">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="G123">
         <v>100</v>
@@ -8673,13 +8673,13 @@
         <v>18</v>
       </c>
       <c r="K123">
-        <v>629</v>
+        <v>549</v>
       </c>
       <c r="L123">
-        <v>1397</v>
+        <v>1414</v>
       </c>
       <c r="M123">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N123">
         <v>110</v>
@@ -8691,10 +8691,10 @@
         <v>0</v>
       </c>
       <c r="Q123">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R123">
-        <v>3908</v>
+        <v>3968</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -8723,13 +8723,13 @@
         <v>FORM6</v>
       </c>
       <c r="D124">
-        <v>4424</v>
+        <v>4431</v>
       </c>
       <c r="E124">
         <v>0</v>
       </c>
       <c r="F124">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -8738,7 +8738,7 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -8747,13 +8747,13 @@
         <v>7</v>
       </c>
       <c r="L124">
-        <v>1317</v>
+        <v>1406</v>
       </c>
       <c r="M124">
         <v>0</v>
       </c>
       <c r="N124">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O124">
         <v>1</v>
@@ -8762,10 +8762,10 @@
         <v>0</v>
       </c>
       <c r="Q124">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R124">
-        <v>2573</v>
+        <v>2620</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -8774,7 +8774,7 @@
         <v>0</v>
       </c>
       <c r="U124">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="V124">
         <v>0</v>
@@ -8800,7 +8800,7 @@
         <v>0</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -8815,7 +8815,7 @@
         <v>0</v>
       </c>
       <c r="K125">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L125">
         <v>0</v>
@@ -8865,13 +8865,13 @@
         <v>FORM7</v>
       </c>
       <c r="D126">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="E126">
         <v>0</v>
       </c>
       <c r="F126">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G126">
         <v>7</v>
@@ -8936,13 +8936,13 @@
         <v>FORM8</v>
       </c>
       <c r="D127">
-        <v>1518</v>
+        <v>1525</v>
       </c>
       <c r="E127">
         <v>0</v>
       </c>
       <c r="F127">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -8951,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="I127">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -8975,7 +8975,7 @@
         <v>0</v>
       </c>
       <c r="Q127">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="R127">
         <v>1285</v>
@@ -9001,13 +9001,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D128">
-        <v>8138</v>
+        <v>8153</v>
       </c>
       <c r="E128">
         <v>0</v>
       </c>
       <c r="F128">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="G128">
         <v>7</v>
@@ -9016,22 +9016,22 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="K128">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L128">
-        <v>1317</v>
+        <v>1406</v>
       </c>
       <c r="M128">
         <v>0</v>
       </c>
       <c r="N128">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O128">
         <v>3</v>
@@ -9040,10 +9040,10 @@
         <v>0</v>
       </c>
       <c r="Q128">
-        <v>2202</v>
+        <v>2243</v>
       </c>
       <c r="R128">
-        <v>3917</v>
+        <v>3964</v>
       </c>
       <c r="S128">
         <v>0</v>
@@ -9052,7 +9052,7 @@
         <v>0</v>
       </c>
       <c r="U128">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="V128">
         <v>0</v>
@@ -9072,13 +9072,13 @@
         <v>FORM6</v>
       </c>
       <c r="D129">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="E129">
         <v>0</v>
       </c>
       <c r="F129">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G129">
         <v>3</v>
@@ -9285,13 +9285,13 @@
         <v>FORM8</v>
       </c>
       <c r="D132">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="E132">
         <v>0</v>
       </c>
       <c r="F132">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -9350,13 +9350,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D133">
-        <v>6246</v>
+        <v>6252</v>
       </c>
       <c r="E133">
         <v>0</v>
       </c>
       <c r="F133">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G133">
         <v>213</v>
@@ -9421,13 +9421,13 @@
         <v>FORM6</v>
       </c>
       <c r="D134">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="E134">
         <v>0</v>
       </c>
       <c r="F134">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G134">
         <v>98</v>
@@ -9436,19 +9436,19 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J134">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="K134">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L134">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="M134">
-        <v>192</v>
+        <v>2</v>
       </c>
       <c r="N134">
         <v>0</v>
@@ -9460,10 +9460,10 @@
         <v>0</v>
       </c>
       <c r="Q134">
-        <v>143</v>
+        <v>395</v>
       </c>
       <c r="R134">
-        <v>640</v>
+        <v>922</v>
       </c>
       <c r="S134">
         <v>0</v>
@@ -9507,7 +9507,7 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>433</v>
       </c>
       <c r="R135">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="S135">
         <v>0</v>
@@ -9563,13 +9563,13 @@
         <v>FORM8</v>
       </c>
       <c r="D136">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="E136">
         <v>0</v>
       </c>
       <c r="F136">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G136">
         <v>30</v>
@@ -9628,13 +9628,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D137">
-        <v>4772</v>
+        <v>4775</v>
       </c>
       <c r="E137">
         <v>0</v>
       </c>
       <c r="F137">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G137">
         <v>129</v>
@@ -9643,19 +9643,19 @@
         <v>0</v>
       </c>
       <c r="I137">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J137">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="K137">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="L137">
-        <v>253</v>
+        <v>4</v>
       </c>
       <c r="M137">
-        <v>194</v>
+        <v>4</v>
       </c>
       <c r="N137">
         <v>1</v>
@@ -9667,10 +9667,10 @@
         <v>0</v>
       </c>
       <c r="Q137">
-        <v>591</v>
+        <v>843</v>
       </c>
       <c r="R137">
-        <v>1351</v>
+        <v>1648</v>
       </c>
       <c r="S137">
         <v>0</v>
@@ -9699,13 +9699,13 @@
         <v>FORM6</v>
       </c>
       <c r="D138">
-        <v>1654</v>
+        <v>1657</v>
       </c>
       <c r="E138">
         <v>0</v>
       </c>
       <c r="F138">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G138">
         <v>27</v>
@@ -9720,16 +9720,16 @@
         <v>0</v>
       </c>
       <c r="K138">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L138">
-        <v>871</v>
+        <v>691</v>
       </c>
       <c r="M138">
         <v>0</v>
       </c>
       <c r="N138">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O138">
         <v>6</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Q138">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="R138">
-        <v>610</v>
+        <v>778</v>
       </c>
       <c r="S138">
         <v>0</v>
@@ -9865,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="L140">
-        <v>1986</v>
+        <v>1755</v>
       </c>
       <c r="M140">
         <v>0</v>
@@ -9880,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="Q140">
-        <v>2464</v>
+        <v>2695</v>
       </c>
       <c r="R140">
         <v>8</v>
@@ -9912,13 +9912,13 @@
         <v>FORM8</v>
       </c>
       <c r="D141">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="E141">
         <v>0</v>
       </c>
       <c r="F141">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -9977,13 +9977,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D142">
-        <v>8790</v>
+        <v>8799</v>
       </c>
       <c r="E142">
         <v>0</v>
       </c>
       <c r="F142">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G142">
         <v>27</v>
@@ -9998,16 +9998,16 @@
         <v>0</v>
       </c>
       <c r="K142">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L142">
-        <v>2857</v>
+        <v>2446</v>
       </c>
       <c r="M142">
         <v>0</v>
       </c>
       <c r="N142">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O142">
         <v>6</v>
@@ -10016,10 +10016,10 @@
         <v>0</v>
       </c>
       <c r="Q142">
-        <v>2498</v>
+        <v>2740</v>
       </c>
       <c r="R142">
-        <v>1344</v>
+        <v>1512</v>
       </c>
       <c r="S142">
         <v>0</v>
@@ -10048,13 +10048,13 @@
         <v>FORM6</v>
       </c>
       <c r="D143">
-        <v>2359</v>
+        <v>2362</v>
       </c>
       <c r="E143">
         <v>0</v>
       </c>
       <c r="F143">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G143">
         <v>4</v>
@@ -10066,34 +10066,34 @@
         <v>0</v>
       </c>
       <c r="J143">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K143">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L143">
-        <v>598</v>
+        <v>360</v>
       </c>
       <c r="M143">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="N143">
         <v>70</v>
       </c>
       <c r="O143">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P143">
         <v>0</v>
       </c>
       <c r="Q143">
-        <v>802</v>
+        <v>985</v>
       </c>
       <c r="R143">
-        <v>684</v>
+        <v>736</v>
       </c>
       <c r="S143">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T143">
         <v>0</v>
@@ -10190,13 +10190,13 @@
         <v>FORM8</v>
       </c>
       <c r="D145">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="E145">
         <v>0</v>
       </c>
       <c r="F145">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G145">
         <v>2</v>
@@ -10214,7 +10214,7 @@
         <v>414</v>
       </c>
       <c r="L145">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="M145">
         <v>0</v>
@@ -10229,10 +10229,10 @@
         <v>0</v>
       </c>
       <c r="Q145">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="R145">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -10255,13 +10255,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D146">
-        <v>6428</v>
+        <v>6434</v>
       </c>
       <c r="E146">
         <v>0</v>
       </c>
       <c r="F146">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G146">
         <v>10</v>
@@ -10273,34 +10273,34 @@
         <v>0</v>
       </c>
       <c r="J146">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K146">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L146">
-        <v>720</v>
+        <v>475</v>
       </c>
       <c r="M146">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="N146">
         <v>135</v>
       </c>
       <c r="O146">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P146">
         <v>0</v>
       </c>
       <c r="Q146">
-        <v>2830</v>
+        <v>3018</v>
       </c>
       <c r="R146">
-        <v>922</v>
+        <v>976</v>
       </c>
       <c r="S146">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T146">
         <v>0</v>
@@ -10326,25 +10326,25 @@
         <v>FORM6</v>
       </c>
       <c r="D147">
-        <v>2927</v>
+        <v>2929</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="H147">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I147">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J147">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="K147">
         <v>0</v>
@@ -10353,19 +10353,19 @@
         <v>1256</v>
       </c>
       <c r="M147">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="N147">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="O147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P147">
         <v>0</v>
       </c>
       <c r="Q147">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="R147">
         <v>833</v>
@@ -10539,13 +10539,13 @@
         <v>FORM8</v>
       </c>
       <c r="D150">
-        <v>1478</v>
+        <v>1451</v>
       </c>
       <c r="E150">
         <v>0</v>
       </c>
       <c r="F150">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -10560,7 +10560,7 @@
         <v>0</v>
       </c>
       <c r="K150">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="L150">
         <v>0</v>
@@ -10578,10 +10578,10 @@
         <v>0</v>
       </c>
       <c r="Q150">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R150">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="S150">
         <v>0</v>
@@ -10604,49 +10604,49 @@
         <v>AC Form Total</v>
       </c>
       <c r="D151">
-        <v>6260</v>
+        <v>6235</v>
       </c>
       <c r="E151">
         <v>0</v>
       </c>
       <c r="F151">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="G151">
-        <v>8</v>
+        <v>228</v>
       </c>
       <c r="H151">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I151">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J151">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="K151">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="L151">
         <v>1256</v>
       </c>
       <c r="M151">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="N151">
-        <v>307</v>
+        <v>69</v>
       </c>
       <c r="O151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P151">
         <v>0</v>
       </c>
       <c r="Q151">
-        <v>1490</v>
+        <v>1498</v>
       </c>
       <c r="R151">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -10675,13 +10675,13 @@
         <v>FORM6</v>
       </c>
       <c r="D152">
-        <v>2390</v>
+        <v>2401</v>
       </c>
       <c r="E152">
         <v>0</v>
       </c>
       <c r="F152">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -10708,13 +10708,13 @@
         <v>0</v>
       </c>
       <c r="O152">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P152">
         <v>0</v>
       </c>
       <c r="Q152">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R152">
         <v>278</v>
@@ -10888,13 +10888,13 @@
         <v>FORM8</v>
       </c>
       <c r="D155">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="E155">
         <v>0</v>
       </c>
       <c r="F155">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -10953,13 +10953,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D156">
-        <v>6411</v>
+        <v>6427</v>
       </c>
       <c r="E156">
         <v>0</v>
       </c>
       <c r="F156">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -10986,13 +10986,13 @@
         <v>0</v>
       </c>
       <c r="O156">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P156">
         <v>0</v>
       </c>
       <c r="Q156">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="R156">
         <v>393</v>
@@ -11024,13 +11024,13 @@
         <v>FORM6</v>
       </c>
       <c r="D157">
-        <v>3128</v>
+        <v>3143</v>
       </c>
       <c r="E157">
         <v>0</v>
       </c>
       <c r="F157">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="G157">
         <v>14</v>
@@ -11042,19 +11042,19 @@
         <v>0</v>
       </c>
       <c r="J157">
-        <v>460</v>
+        <v>38</v>
       </c>
       <c r="K157">
-        <v>515</v>
+        <v>635</v>
       </c>
       <c r="L157">
-        <v>320</v>
+        <v>581</v>
       </c>
       <c r="M157">
-        <v>1100</v>
+        <v>1028</v>
       </c>
       <c r="N157">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O157">
         <v>3</v>
@@ -11063,10 +11063,10 @@
         <v>0</v>
       </c>
       <c r="Q157">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R157">
-        <v>198</v>
+        <v>317</v>
       </c>
       <c r="S157">
         <v>0</v>
@@ -11166,13 +11166,13 @@
         <v>FORM8</v>
       </c>
       <c r="D159">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="E159">
         <v>0</v>
       </c>
       <c r="F159">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -11231,13 +11231,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D160">
-        <v>7255</v>
+        <v>7273</v>
       </c>
       <c r="E160">
         <v>0</v>
       </c>
       <c r="F160">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="G160">
         <v>14</v>
@@ -11249,19 +11249,19 @@
         <v>7</v>
       </c>
       <c r="J160">
-        <v>461</v>
+        <v>39</v>
       </c>
       <c r="K160">
-        <v>1188</v>
+        <v>1308</v>
       </c>
       <c r="L160">
-        <v>320</v>
+        <v>581</v>
       </c>
       <c r="M160">
-        <v>1100</v>
+        <v>1028</v>
       </c>
       <c r="N160">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O160">
         <v>3</v>
@@ -11270,10 +11270,10 @@
         <v>0</v>
       </c>
       <c r="Q160">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="R160">
-        <v>376</v>
+        <v>495</v>
       </c>
       <c r="S160">
         <v>0</v>
@@ -11302,13 +11302,13 @@
         <v>FORM6</v>
       </c>
       <c r="D161">
-        <v>1960</v>
+        <v>1964</v>
       </c>
       <c r="E161">
         <v>0</v>
       </c>
       <c r="F161">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G161">
         <v>1</v>
@@ -11444,13 +11444,13 @@
         <v>FORM8</v>
       </c>
       <c r="D163">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="E163">
         <v>0</v>
       </c>
       <c r="F163">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G163">
         <v>13</v>
@@ -11509,13 +11509,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D164">
-        <v>6114</v>
+        <v>6122</v>
       </c>
       <c r="E164">
         <v>0</v>
       </c>
       <c r="F164">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="G164">
         <v>14</v>
@@ -11580,13 +11580,13 @@
         <v>FORM6</v>
       </c>
       <c r="D165">
-        <v>3566</v>
+        <v>3576</v>
       </c>
       <c r="E165">
         <v>0</v>
       </c>
       <c r="F165">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="G165">
         <v>0</v>
@@ -11722,13 +11722,13 @@
         <v>FORM8</v>
       </c>
       <c r="D167">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E167">
         <v>0</v>
       </c>
       <c r="F167">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G167">
         <v>0</v>
@@ -11787,13 +11787,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D168">
-        <v>8792</v>
+        <v>8805</v>
       </c>
       <c r="E168">
         <v>0</v>
       </c>
       <c r="F168">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="G168">
         <v>7</v>
@@ -11971,7 +11971,7 @@
         <v>556</v>
       </c>
       <c r="R170">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="S170">
         <v>0</v>
@@ -11980,7 +11980,7 @@
         <v>0</v>
       </c>
       <c r="U170">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V170">
         <v>0</v>
@@ -12000,13 +12000,13 @@
         <v>FORM8</v>
       </c>
       <c r="D171">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E171">
         <v>0</v>
       </c>
       <c r="F171">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G171">
         <v>0</v>
@@ -12065,13 +12065,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D172">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="E172">
         <v>0</v>
       </c>
       <c r="F172">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G172">
         <v>40</v>
@@ -12107,7 +12107,7 @@
         <v>623</v>
       </c>
       <c r="R172">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -12116,7 +12116,7 @@
         <v>0</v>
       </c>
       <c r="U172">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V172">
         <v>0</v>
@@ -12136,13 +12136,13 @@
         <v>FORM6</v>
       </c>
       <c r="D173">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E173">
         <v>0</v>
       </c>
       <c r="F173">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G173">
         <v>5</v>
@@ -12305,7 +12305,7 @@
         <v>0</v>
       </c>
       <c r="M175">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N175">
         <v>0</v>
@@ -12317,10 +12317,10 @@
         <v>0</v>
       </c>
       <c r="Q175">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="R175">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -12414,13 +12414,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D177">
-        <v>1527</v>
+        <v>1530</v>
       </c>
       <c r="E177">
         <v>0</v>
       </c>
       <c r="F177">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G177">
         <v>10</v>
@@ -12441,7 +12441,7 @@
         <v>0</v>
       </c>
       <c r="M177">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N177">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         <v>0</v>
       </c>
       <c r="Q177">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R177">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="S177">
         <v>0</v>
@@ -12485,16 +12485,16 @@
         <v>FORM6</v>
       </c>
       <c r="D178">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="E178">
         <v>0</v>
       </c>
       <c r="F178">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G178">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H178">
         <v>0</v>
@@ -12524,10 +12524,10 @@
         <v>0</v>
       </c>
       <c r="Q178">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R178">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="S178">
         <v>0</v>
@@ -12627,13 +12627,13 @@
         <v>FORM8</v>
       </c>
       <c r="D180">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E180">
         <v>0</v>
       </c>
       <c r="F180">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G180">
         <v>2</v>
@@ -12692,16 +12692,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D181">
-        <v>3468</v>
+        <v>3470</v>
       </c>
       <c r="E181">
         <v>0</v>
       </c>
       <c r="F181">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G181">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -12731,10 +12731,10 @@
         <v>0</v>
       </c>
       <c r="Q181">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="R181">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -12763,13 +12763,13 @@
         <v>FORM6</v>
       </c>
       <c r="D182">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E182">
         <v>0</v>
       </c>
       <c r="F182">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G182">
         <v>0</v>
@@ -12793,7 +12793,7 @@
         <v>0</v>
       </c>
       <c r="N182">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O182">
         <v>0</v>
@@ -12805,7 +12805,7 @@
         <v>21</v>
       </c>
       <c r="R182">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -12855,16 +12855,16 @@
         <v>0</v>
       </c>
       <c r="K183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L183">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M183">
         <v>0</v>
       </c>
       <c r="N183">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O183">
         <v>0</v>
@@ -12876,7 +12876,7 @@
         <v>285</v>
       </c>
       <c r="R183">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="S183">
         <v>0</v>
@@ -12905,13 +12905,13 @@
         <v>FORM8</v>
       </c>
       <c r="D184">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E184">
         <v>0</v>
       </c>
       <c r="F184">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G184">
         <v>0</v>
@@ -12935,19 +12935,19 @@
         <v>0</v>
       </c>
       <c r="N184">
+        <v>0</v>
+      </c>
+      <c r="O184">
+        <v>0</v>
+      </c>
+      <c r="P184">
+        <v>0</v>
+      </c>
+      <c r="Q184">
         <v>12</v>
       </c>
-      <c r="O184">
-        <v>0</v>
-      </c>
-      <c r="P184">
-        <v>0</v>
-      </c>
-      <c r="Q184">
-        <v>10</v>
-      </c>
       <c r="R184">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -12970,13 +12970,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D185">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="E185">
         <v>0</v>
       </c>
       <c r="F185">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G185">
         <v>22</v>
@@ -12991,16 +12991,16 @@
         <v>0</v>
       </c>
       <c r="K185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L185">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M185">
         <v>0</v>
       </c>
       <c r="N185">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O185">
         <v>0</v>
@@ -13009,10 +13009,10 @@
         <v>0</v>
       </c>
       <c r="Q185">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="R185">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -13041,16 +13041,16 @@
         <v>FORM6</v>
       </c>
       <c r="D186">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="E186">
         <v>0</v>
       </c>
       <c r="F186">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G186">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H186">
         <v>0</v>
@@ -13059,7 +13059,7 @@
         <v>0</v>
       </c>
       <c r="J186">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K186">
         <v>0</v>
@@ -13068,7 +13068,7 @@
         <v>0</v>
       </c>
       <c r="M186">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N186">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="Q186">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="R186">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -13142,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="N187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O187">
         <v>0</v>
@@ -13154,7 +13154,7 @@
         <v>263</v>
       </c>
       <c r="R187">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -13183,13 +13183,13 @@
         <v>FORM8</v>
       </c>
       <c r="D188">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E188">
         <v>0</v>
       </c>
       <c r="F188">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G188">
         <v>0</v>
@@ -13248,16 +13248,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D189">
-        <v>2222</v>
+        <v>2226</v>
       </c>
       <c r="E189">
         <v>0</v>
       </c>
       <c r="F189">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G189">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H189">
         <v>0</v>
@@ -13266,7 +13266,7 @@
         <v>0</v>
       </c>
       <c r="J189">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K189">
         <v>0</v>
@@ -13275,10 +13275,10 @@
         <v>0</v>
       </c>
       <c r="M189">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O189">
         <v>0</v>
@@ -13287,10 +13287,10 @@
         <v>0</v>
       </c>
       <c r="Q189">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="R189">
-        <v>951</v>
+        <v>964</v>
       </c>
       <c r="S189">
         <v>0</v>
@@ -13319,13 +13319,13 @@
         <v>FORM6</v>
       </c>
       <c r="D190">
-        <v>2667</v>
+        <v>2669</v>
       </c>
       <c r="E190">
         <v>0</v>
       </c>
       <c r="F190">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G190">
         <v>0</v>
@@ -13343,13 +13343,13 @@
         <v>0</v>
       </c>
       <c r="L190">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="M190">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N190">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O190">
         <v>0</v>
@@ -13358,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="Q190">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="R190">
-        <v>2150</v>
+        <v>2164</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -13461,7 +13461,7 @@
         <v>FORM7</v>
       </c>
       <c r="D192">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -13470,7 +13470,7 @@
         <v>1</v>
       </c>
       <c r="G192">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H192">
         <v>0</v>
@@ -13485,7 +13485,7 @@
         <v>0</v>
       </c>
       <c r="L192">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M192">
         <v>0</v>
@@ -13500,10 +13500,10 @@
         <v>0</v>
       </c>
       <c r="Q192">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="R192">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="S192">
         <v>0</v>
@@ -13532,16 +13532,16 @@
         <v>FORM8</v>
       </c>
       <c r="D193">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E193">
         <v>0</v>
       </c>
       <c r="F193">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H193">
         <v>0</v>
@@ -13553,16 +13553,16 @@
         <v>0</v>
       </c>
       <c r="K193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L193">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="M193">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O193">
         <v>0</v>
@@ -13571,10 +13571,10 @@
         <v>0</v>
       </c>
       <c r="Q193">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="R193">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -13597,16 +13597,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D194">
-        <v>4773</v>
+        <v>4778</v>
       </c>
       <c r="E194">
         <v>0</v>
       </c>
       <c r="F194">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G194">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H194">
         <v>0</v>
@@ -13618,16 +13618,16 @@
         <v>1</v>
       </c>
       <c r="K194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L194">
-        <v>286</v>
+        <v>209</v>
       </c>
       <c r="M194">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N194">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -13636,10 +13636,10 @@
         <v>0</v>
       </c>
       <c r="Q194">
-        <v>468</v>
+        <v>536</v>
       </c>
       <c r="R194">
-        <v>2950</v>
+        <v>2976</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -13668,16 +13668,16 @@
         <v>FORM6</v>
       </c>
       <c r="D195">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E195">
         <v>0</v>
       </c>
       <c r="F195">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H195">
         <v>0</v>
@@ -13689,7 +13689,7 @@
         <v>0</v>
       </c>
       <c r="K195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L195">
         <v>0</v>
@@ -13698,7 +13698,7 @@
         <v>0</v>
       </c>
       <c r="N195">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O195">
         <v>0</v>
@@ -13707,10 +13707,10 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R195">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -13769,7 +13769,7 @@
         <v>0</v>
       </c>
       <c r="N196">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O196">
         <v>0</v>
@@ -13781,7 +13781,7 @@
         <v>120</v>
       </c>
       <c r="R196">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="S196">
         <v>0</v>
@@ -13840,7 +13840,7 @@
         <v>0</v>
       </c>
       <c r="N197">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O197">
         <v>0</v>
@@ -13849,10 +13849,10 @@
         <v>0</v>
       </c>
       <c r="Q197">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S197">
         <v>0</v>
@@ -13875,16 +13875,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D198">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="E198">
         <v>0</v>
       </c>
       <c r="F198">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H198">
         <v>0</v>
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="K198">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L198">
         <v>0</v>
@@ -13905,7 +13905,7 @@
         <v>0</v>
       </c>
       <c r="N198">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O198">
         <v>0</v>
@@ -13914,10 +13914,10 @@
         <v>0</v>
       </c>
       <c r="Q198">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="R198">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="S198">
         <v>0</v>
@@ -13946,13 +13946,13 @@
         <v>FORM6</v>
       </c>
       <c r="D199">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="E199">
         <v>0</v>
       </c>
       <c r="F199">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G199">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="N199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O199">
         <v>0</v>
@@ -13985,7 +13985,7 @@
         <v>0</v>
       </c>
       <c r="Q199">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R199">
         <v>1117</v>
@@ -14127,10 +14127,10 @@
         <v>0</v>
       </c>
       <c r="Q201">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R201">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -14153,13 +14153,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D202">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="E202">
         <v>0</v>
       </c>
       <c r="F202">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G202">
         <v>0</v>
@@ -14183,7 +14183,7 @@
         <v>0</v>
       </c>
       <c r="N202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O202">
         <v>0</v>
@@ -14192,10 +14192,10 @@
         <v>0</v>
       </c>
       <c r="Q202">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R202">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -14224,16 +14224,16 @@
         <v>FORM6</v>
       </c>
       <c r="D203">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="E203">
         <v>0</v>
       </c>
       <c r="F203">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G203">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H203">
         <v>0</v>
@@ -14254,7 +14254,7 @@
         <v>0</v>
       </c>
       <c r="N203">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O203">
         <v>0</v>
@@ -14263,10 +14263,10 @@
         <v>0</v>
       </c>
       <c r="Q203">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R203">
-        <v>1049</v>
+        <v>1061</v>
       </c>
       <c r="S203">
         <v>0</v>
@@ -14461,13 +14461,13 @@
         <v>0</v>
       </c>
       <c r="L206">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M206">
         <v>0</v>
       </c>
       <c r="N206">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O206">
         <v>0</v>
@@ -14476,10 +14476,10 @@
         <v>0</v>
       </c>
       <c r="Q206">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="R206">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="S206">
         <v>0</v>
@@ -14502,16 +14502,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D207">
-        <v>3009</v>
+        <v>3013</v>
       </c>
       <c r="E207">
         <v>0</v>
       </c>
       <c r="F207">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G207">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H207">
         <v>0</v>
@@ -14526,13 +14526,13 @@
         <v>1</v>
       </c>
       <c r="L207">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M207">
         <v>0</v>
       </c>
       <c r="N207">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="O207">
         <v>0</v>
@@ -14541,10 +14541,10 @@
         <v>0</v>
       </c>
       <c r="Q207">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="R207">
-        <v>1162</v>
+        <v>1194</v>
       </c>
       <c r="S207">
         <v>0</v>
@@ -14573,13 +14573,13 @@
         <v>FORM6</v>
       </c>
       <c r="D208">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E208">
         <v>0</v>
       </c>
       <c r="F208">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G208">
         <v>0</v>
@@ -14603,7 +14603,7 @@
         <v>0</v>
       </c>
       <c r="N208">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O208">
         <v>0</v>
@@ -14612,10 +14612,10 @@
         <v>0</v>
       </c>
       <c r="Q208">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="R208">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="S208">
         <v>0</v>
@@ -14745,7 +14745,7 @@
         <v>0</v>
       </c>
       <c r="N210">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O210">
         <v>0</v>
@@ -14757,7 +14757,7 @@
         <v>12</v>
       </c>
       <c r="R210">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -14780,13 +14780,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D211">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="E211">
         <v>0</v>
       </c>
       <c r="F211">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G211">
         <v>0</v>
@@ -14810,7 +14810,7 @@
         <v>0</v>
       </c>
       <c r="N211">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O211">
         <v>0</v>
@@ -14819,10 +14819,10 @@
         <v>0</v>
       </c>
       <c r="Q211">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="R211">
-        <v>896</v>
+        <v>930</v>
       </c>
       <c r="S211">
         <v>0</v>
@@ -14878,7 +14878,7 @@
         <v>3</v>
       </c>
       <c r="M212">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N212">
         <v>0</v>
@@ -14893,7 +14893,7 @@
         <v>43</v>
       </c>
       <c r="R212">
-        <v>2574</v>
+        <v>2577</v>
       </c>
       <c r="S212">
         <v>0</v>
@@ -14993,13 +14993,13 @@
         <v>FORM8</v>
       </c>
       <c r="D214">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E214">
         <v>0</v>
       </c>
       <c r="F214">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G214">
         <v>0</v>
@@ -15058,13 +15058,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D215">
-        <v>3827</v>
+        <v>3828</v>
       </c>
       <c r="E215">
         <v>0</v>
       </c>
       <c r="F215">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G215">
         <v>3</v>
@@ -15085,7 +15085,7 @@
         <v>3</v>
       </c>
       <c r="M215">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N215">
         <v>0</v>
@@ -15100,7 +15100,7 @@
         <v>172</v>
       </c>
       <c r="R215">
-        <v>2952</v>
+        <v>2955</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -15129,16 +15129,16 @@
         <v>FORM6</v>
       </c>
       <c r="D216">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="E216">
         <v>0</v>
       </c>
       <c r="F216">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G216">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H216">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         <v>0</v>
       </c>
       <c r="M216">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N216">
         <v>0</v>
@@ -15200,7 +15200,7 @@
         <v>FORM7</v>
       </c>
       <c r="D217">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -15221,7 +15221,7 @@
         <v>0</v>
       </c>
       <c r="K217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L217">
         <v>0</v>
@@ -15271,16 +15271,16 @@
         <v>FORM8</v>
       </c>
       <c r="D218">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="E218">
         <v>0</v>
       </c>
       <c r="F218">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218">
         <v>0</v>
@@ -15298,7 +15298,7 @@
         <v>0</v>
       </c>
       <c r="M218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N218">
         <v>0</v>
@@ -15336,16 +15336,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D219">
-        <v>3604</v>
+        <v>3609</v>
       </c>
       <c r="E219">
         <v>0</v>
       </c>
       <c r="F219">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G219">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H219">
         <v>0</v>
@@ -15357,13 +15357,13 @@
         <v>0</v>
       </c>
       <c r="K219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L219">
         <v>0</v>
       </c>
       <c r="M219">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N219">
         <v>0</v>
@@ -15407,13 +15407,13 @@
         <v>FORM6</v>
       </c>
       <c r="D220">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="E220">
         <v>0</v>
       </c>
       <c r="F220">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G220">
         <v>1</v>
@@ -15614,13 +15614,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D223">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="E223">
         <v>0</v>
       </c>
       <c r="F223">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G223">
         <v>6</v>
@@ -15685,13 +15685,13 @@
         <v>FORM6</v>
       </c>
       <c r="D224">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="E224">
         <v>0</v>
       </c>
       <c r="F224">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G224">
         <v>17</v>
@@ -15898,13 +15898,13 @@
         <v>FORM8</v>
       </c>
       <c r="D227">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E227">
         <v>0</v>
       </c>
       <c r="F227">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G227">
         <v>9</v>
@@ -15963,13 +15963,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D228">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="E228">
         <v>0</v>
       </c>
       <c r="F228">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G228">
         <v>27</v>
@@ -16034,16 +16034,16 @@
         <v>FORM6</v>
       </c>
       <c r="D229">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="E229">
         <v>0</v>
       </c>
       <c r="F229">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G229">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H229">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="K229">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="L229">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M229">
         <v>6</v>
@@ -16073,10 +16073,10 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R229">
-        <v>293</v>
+        <v>440</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -16247,13 +16247,13 @@
         <v>FORM8</v>
       </c>
       <c r="D232">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E232">
         <v>0</v>
       </c>
       <c r="F232">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G232">
         <v>8</v>
@@ -16265,7 +16265,7 @@
         <v>0</v>
       </c>
       <c r="J232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K232">
         <v>4</v>
@@ -16274,7 +16274,7 @@
         <v>0</v>
       </c>
       <c r="M232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N232">
         <v>7</v>
@@ -16312,16 +16312,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D233">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="E233">
         <v>0</v>
       </c>
       <c r="F233">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G233">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -16330,16 +16330,16 @@
         <v>0</v>
       </c>
       <c r="J233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K233">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="L233">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M233">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N233">
         <v>7</v>
@@ -16351,10 +16351,10 @@
         <v>0</v>
       </c>
       <c r="Q233">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="R233">
-        <v>434</v>
+        <v>581</v>
       </c>
       <c r="S233">
         <v>0</v>
@@ -16383,13 +16383,13 @@
         <v>FORM6</v>
       </c>
       <c r="D234">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="E234">
         <v>0</v>
       </c>
       <c r="F234">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G234">
         <v>6</v>
@@ -16525,13 +16525,13 @@
         <v>FORM8</v>
       </c>
       <c r="D236">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E236">
         <v>0</v>
       </c>
       <c r="F236">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G236">
         <v>3</v>
@@ -16590,13 +16590,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D237">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="E237">
         <v>0</v>
       </c>
       <c r="F237">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G237">
         <v>11</v>
@@ -16661,13 +16661,13 @@
         <v>FORM6</v>
       </c>
       <c r="D238">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="E238">
         <v>0</v>
       </c>
       <c r="F238">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G238">
         <v>0</v>
@@ -16824,7 +16824,7 @@
         <v>0</v>
       </c>
       <c r="K240">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -16845,7 +16845,7 @@
         <v>208</v>
       </c>
       <c r="R240">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S240">
         <v>0</v>
@@ -16874,13 +16874,13 @@
         <v>FORM8</v>
       </c>
       <c r="D241">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E241">
         <v>0</v>
       </c>
       <c r="F241">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G241">
         <v>0</v>
@@ -16939,13 +16939,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D242">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="E242">
         <v>0</v>
       </c>
       <c r="F242">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G242">
         <v>0</v>
@@ -16960,7 +16960,7 @@
         <v>0</v>
       </c>
       <c r="K242">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L242">
         <v>0</v>
@@ -16981,7 +16981,7 @@
         <v>253</v>
       </c>
       <c r="R242">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="S242">
         <v>0</v>
@@ -17010,7 +17010,7 @@
         <v>FORM6</v>
       </c>
       <c r="D243">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -17028,7 +17028,7 @@
         <v>0</v>
       </c>
       <c r="J243">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K243">
         <v>0</v>
@@ -17081,7 +17081,7 @@
         <v>FORM7</v>
       </c>
       <c r="D244">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -17120,7 +17120,7 @@
         <v>0</v>
       </c>
       <c r="Q244">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R244">
         <v>56</v>
@@ -17217,7 +17217,7 @@
         <v>AC Form Total</v>
       </c>
       <c r="D246">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -17235,7 +17235,7 @@
         <v>0</v>
       </c>
       <c r="J246">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K246">
         <v>0</v>
@@ -17256,7 +17256,7 @@
         <v>0</v>
       </c>
       <c r="Q246">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="R246">
         <v>692</v>
@@ -17315,7 +17315,7 @@
         <v>0</v>
       </c>
       <c r="M247">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N247">
         <v>24</v>
@@ -17330,7 +17330,7 @@
         <v>8</v>
       </c>
       <c r="R247">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="S247">
         <v>0</v>
@@ -17359,7 +17359,7 @@
         <v>FORM7</v>
       </c>
       <c r="D248">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -17380,7 +17380,7 @@
         <v>0</v>
       </c>
       <c r="K248">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -17401,7 +17401,7 @@
         <v>32</v>
       </c>
       <c r="R248">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="S248">
         <v>0</v>
@@ -17430,13 +17430,13 @@
         <v>FORM8</v>
       </c>
       <c r="D249">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E249">
         <v>0</v>
       </c>
       <c r="F249">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G249">
         <v>0</v>
@@ -17445,7 +17445,7 @@
         <v>0</v>
       </c>
       <c r="I249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J249">
         <v>0</v>
@@ -17460,7 +17460,7 @@
         <v>0</v>
       </c>
       <c r="N249">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O249">
         <v>0</v>
@@ -17495,13 +17495,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D250">
-        <v>3023</v>
+        <v>3025</v>
       </c>
       <c r="E250">
         <v>0</v>
       </c>
       <c r="F250">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G250">
         <v>12</v>
@@ -17510,22 +17510,22 @@
         <v>0</v>
       </c>
       <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
         <v>1</v>
       </c>
-      <c r="J250">
-        <v>0</v>
-      </c>
-      <c r="K250">
-        <v>10</v>
-      </c>
       <c r="L250">
         <v>0</v>
       </c>
       <c r="M250">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N250">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O250">
         <v>0</v>
@@ -17537,7 +17537,7 @@
         <v>47</v>
       </c>
       <c r="R250">
-        <v>2165</v>
+        <v>2179</v>
       </c>
       <c r="S250">
         <v>0</v>
@@ -17566,40 +17566,40 @@
         <v>FORM6</v>
       </c>
       <c r="D251">
-        <v>1698</v>
+        <v>1701</v>
       </c>
       <c r="E251">
         <v>0</v>
       </c>
       <c r="F251">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G251">
         <v>0</v>
       </c>
       <c r="H251">
+        <v>0</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>0</v>
+      </c>
+      <c r="L251">
+        <v>0</v>
+      </c>
+      <c r="M251">
+        <v>0</v>
+      </c>
+      <c r="N251">
         <v>53</v>
       </c>
-      <c r="I251">
-        <v>0</v>
-      </c>
-      <c r="J251">
-        <v>0</v>
-      </c>
-      <c r="K251">
-        <v>1</v>
-      </c>
-      <c r="L251">
-        <v>0</v>
-      </c>
-      <c r="M251">
-        <v>0</v>
-      </c>
-      <c r="N251">
-        <v>9</v>
-      </c>
       <c r="O251">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P251">
         <v>0</v>
@@ -17608,7 +17608,7 @@
         <v>69</v>
       </c>
       <c r="R251">
-        <v>1252</v>
+        <v>1266</v>
       </c>
       <c r="S251">
         <v>0</v>
@@ -17637,7 +17637,7 @@
         <v>FORM7</v>
       </c>
       <c r="D252">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -17646,7 +17646,7 @@
         <v>0</v>
       </c>
       <c r="G252">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -17667,7 +17667,7 @@
         <v>0</v>
       </c>
       <c r="N252">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O252">
         <v>0</v>
@@ -17676,10 +17676,10 @@
         <v>0</v>
       </c>
       <c r="Q252">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="R252">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="S252">
         <v>0</v>
@@ -17694,7 +17694,7 @@
         <v>0</v>
       </c>
       <c r="W252">
-        <v>777</v>
+        <v>790</v>
       </c>
     </row>
     <row r="253">
@@ -17708,13 +17708,13 @@
         <v>FORM8</v>
       </c>
       <c r="D253">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E253">
         <v>0</v>
       </c>
       <c r="F253">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G253">
         <v>0</v>
@@ -17738,7 +17738,7 @@
         <v>0</v>
       </c>
       <c r="N253">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O253">
         <v>0</v>
@@ -17750,7 +17750,7 @@
         <v>39</v>
       </c>
       <c r="R253">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="S253">
         <v>0</v>
@@ -17773,19 +17773,19 @@
         <v>AC Form Total</v>
       </c>
       <c r="D254">
-        <v>3637</v>
+        <v>3654</v>
       </c>
       <c r="E254">
         <v>0</v>
       </c>
       <c r="F254">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G254">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H254">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I254">
         <v>0</v>
@@ -17794,7 +17794,7 @@
         <v>0</v>
       </c>
       <c r="K254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L254">
         <v>0</v>
@@ -17803,19 +17803,19 @@
         <v>0</v>
       </c>
       <c r="N254">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="O254">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P254">
         <v>0</v>
       </c>
       <c r="Q254">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="R254">
-        <v>1504</v>
+        <v>1528</v>
       </c>
       <c r="S254">
         <v>0</v>
@@ -17830,7 +17830,7 @@
         <v>0</v>
       </c>
       <c r="W254">
-        <v>1476</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="255">
@@ -17844,16 +17844,16 @@
         <v>FORM6</v>
       </c>
       <c r="D255">
-        <v>2029</v>
+        <v>2041</v>
       </c>
       <c r="E255">
         <v>0</v>
       </c>
       <c r="F255">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="G255">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -17862,16 +17862,16 @@
         <v>0</v>
       </c>
       <c r="J255">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K255">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="L255">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M255">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="N255">
         <v>11</v>
@@ -17886,7 +17886,7 @@
         <v>21</v>
       </c>
       <c r="R255">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="S255">
         <v>0</v>
@@ -17924,23 +17924,23 @@
         <v>2</v>
       </c>
       <c r="G256">
+        <v>0</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+      <c r="J256">
+        <v>0</v>
+      </c>
+      <c r="K256">
+        <v>17</v>
+      </c>
+      <c r="L256">
         <v>7</v>
       </c>
-      <c r="H256">
-        <v>0</v>
-      </c>
-      <c r="I256">
-        <v>0</v>
-      </c>
-      <c r="J256">
-        <v>0</v>
-      </c>
-      <c r="K256">
-        <v>10</v>
-      </c>
-      <c r="L256">
-        <v>262</v>
-      </c>
       <c r="M256">
         <v>0</v>
       </c>
@@ -17954,10 +17954,10 @@
         <v>0</v>
       </c>
       <c r="Q256">
-        <v>352</v>
+        <v>573</v>
       </c>
       <c r="R256">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="S256">
         <v>0</v>
@@ -17986,16 +17986,16 @@
         <v>FORM8</v>
       </c>
       <c r="D257">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="E257">
         <v>0</v>
       </c>
       <c r="F257">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G257">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H257">
         <v>0</v>
@@ -18004,13 +18004,13 @@
         <v>0</v>
       </c>
       <c r="J257">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K257">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="L257">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M257">
         <v>26</v>
@@ -18025,10 +18025,10 @@
         <v>0</v>
       </c>
       <c r="Q257">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R257">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="S257">
         <v>0</v>
@@ -18051,16 +18051,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D258">
-        <v>6280</v>
+        <v>6304</v>
       </c>
       <c r="E258">
         <v>0</v>
       </c>
       <c r="F258">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="G258">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -18069,16 +18069,16 @@
         <v>0</v>
       </c>
       <c r="J258">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K258">
-        <v>29</v>
+        <v>230</v>
       </c>
       <c r="L258">
-        <v>290</v>
+        <v>22</v>
       </c>
       <c r="M258">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N258">
         <v>15</v>
@@ -18090,10 +18090,10 @@
         <v>0</v>
       </c>
       <c r="Q258">
-        <v>392</v>
+        <v>615</v>
       </c>
       <c r="R258">
-        <v>524</v>
+        <v>569</v>
       </c>
       <c r="S258">
         <v>0</v>
@@ -18122,16 +18122,16 @@
         <v>FORM6</v>
       </c>
       <c r="D259">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="E259">
         <v>0</v>
       </c>
       <c r="F259">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G259">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H259">
         <v>0</v>
@@ -18140,19 +18140,19 @@
         <v>0</v>
       </c>
       <c r="J259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K259">
-        <v>520</v>
+        <v>474</v>
       </c>
       <c r="L259">
         <v>1</v>
       </c>
       <c r="M259">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N259">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O259">
         <v>0</v>
@@ -18164,7 +18164,7 @@
         <v>6</v>
       </c>
       <c r="R259">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="S259">
         <v>0</v>
@@ -18173,7 +18173,7 @@
         <v>0</v>
       </c>
       <c r="U259">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V259">
         <v>0</v>
@@ -18193,7 +18193,7 @@
         <v>FORM7</v>
       </c>
       <c r="D260">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -18202,7 +18202,7 @@
         <v>4</v>
       </c>
       <c r="G260">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H260">
         <v>0</v>
@@ -18214,10 +18214,10 @@
         <v>0</v>
       </c>
       <c r="K260">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L260">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M260">
         <v>0</v>
@@ -18232,10 +18232,10 @@
         <v>0</v>
       </c>
       <c r="Q260">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="R260">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="S260">
         <v>0</v>
@@ -18273,7 +18273,7 @@
         <v>38</v>
       </c>
       <c r="G261">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H261">
         <v>0</v>
@@ -18285,7 +18285,7 @@
         <v>0</v>
       </c>
       <c r="K261">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="L261">
         <v>0</v>
@@ -18294,7 +18294,7 @@
         <v>0</v>
       </c>
       <c r="N261">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O261">
         <v>0</v>
@@ -18303,10 +18303,10 @@
         <v>0</v>
       </c>
       <c r="Q261">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R261">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="S261">
         <v>0</v>
@@ -18315,7 +18315,7 @@
         <v>0</v>
       </c>
       <c r="U261">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V261">
         <v>0</v>
@@ -18329,16 +18329,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D262">
-        <v>1669</v>
+        <v>1676</v>
       </c>
       <c r="E262">
         <v>0</v>
       </c>
       <c r="F262">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G262">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H262">
         <v>0</v>
@@ -18347,20 +18347,20 @@
         <v>0</v>
       </c>
       <c r="J262">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K262">
-        <v>648</v>
+        <v>523</v>
       </c>
       <c r="L262">
+        <v>17</v>
+      </c>
+      <c r="M262">
+        <v>0</v>
+      </c>
+      <c r="N262">
         <v>22</v>
       </c>
-      <c r="M262">
-        <v>3</v>
-      </c>
-      <c r="N262">
-        <v>24</v>
-      </c>
       <c r="O262">
         <v>0</v>
       </c>
@@ -18368,10 +18368,10 @@
         <v>0</v>
       </c>
       <c r="Q262">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="R262">
-        <v>194</v>
+        <v>322</v>
       </c>
       <c r="S262">
         <v>0</v>
@@ -18380,7 +18380,7 @@
         <v>0</v>
       </c>
       <c r="U262">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V262">
         <v>0</v>
@@ -18400,7 +18400,7 @@
         <v>FORM6</v>
       </c>
       <c r="D263">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -18412,28 +18412,28 @@
         <v>3</v>
       </c>
       <c r="H263">
+        <v>0</v>
+      </c>
+      <c r="I263">
+        <v>0</v>
+      </c>
+      <c r="J263">
+        <v>2</v>
+      </c>
+      <c r="K263">
+        <v>220</v>
+      </c>
+      <c r="L263">
+        <v>0</v>
+      </c>
+      <c r="M263">
         <v>1</v>
       </c>
-      <c r="I263">
-        <v>0</v>
-      </c>
-      <c r="J263">
-        <v>0</v>
-      </c>
-      <c r="K263">
-        <v>216</v>
-      </c>
-      <c r="L263">
-        <v>0</v>
-      </c>
-      <c r="M263">
-        <v>2</v>
-      </c>
       <c r="N263">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="O263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P263">
         <v>0</v>
@@ -18442,7 +18442,7 @@
         <v>6</v>
       </c>
       <c r="R263">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="S263">
         <v>0</v>
@@ -18501,16 +18501,16 @@
         <v>0</v>
       </c>
       <c r="N264">
+        <v>0</v>
+      </c>
+      <c r="O264">
+        <v>0</v>
+      </c>
+      <c r="P264">
+        <v>0</v>
+      </c>
+      <c r="Q264">
         <v>1</v>
-      </c>
-      <c r="O264">
-        <v>0</v>
-      </c>
-      <c r="P264">
-        <v>0</v>
-      </c>
-      <c r="Q264">
-        <v>0</v>
       </c>
       <c r="R264">
         <v>0</v>
@@ -18613,13 +18613,13 @@
         <v>FORM8</v>
       </c>
       <c r="D266">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E266">
         <v>0</v>
       </c>
       <c r="F266">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G266">
         <v>1</v>
@@ -18631,19 +18631,19 @@
         <v>0</v>
       </c>
       <c r="J266">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K266">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L266">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M266">
         <v>0</v>
       </c>
       <c r="N266">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O266">
         <v>0</v>
@@ -18652,10 +18652,10 @@
         <v>0</v>
       </c>
       <c r="Q266">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="R266">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="S266">
         <v>0</v>
@@ -18678,49 +18678,49 @@
         <v>AC Form Total</v>
       </c>
       <c r="D267">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="E267">
         <v>0</v>
       </c>
       <c r="F267">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G267">
         <v>4</v>
       </c>
       <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+      <c r="J267">
+        <v>5</v>
+      </c>
+      <c r="K267">
+        <v>220</v>
+      </c>
+      <c r="L267">
+        <v>2</v>
+      </c>
+      <c r="M267">
         <v>1</v>
       </c>
-      <c r="I267">
-        <v>0</v>
-      </c>
-      <c r="J267">
+      <c r="N267">
+        <v>153</v>
+      </c>
+      <c r="O267">
         <v>1</v>
       </c>
-      <c r="K267">
-        <v>222</v>
-      </c>
-      <c r="L267">
-        <v>7</v>
-      </c>
-      <c r="M267">
-        <v>2</v>
-      </c>
-      <c r="N267">
-        <v>166</v>
-      </c>
-      <c r="O267">
-        <v>0</v>
-      </c>
       <c r="P267">
         <v>0</v>
       </c>
       <c r="Q267">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="R267">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="S267">
         <v>0</v>
@@ -18749,16 +18749,16 @@
         <v>FORM6</v>
       </c>
       <c r="D268">
-        <v>5379</v>
+        <v>5376</v>
       </c>
       <c r="E268">
         <v>0</v>
       </c>
       <c r="F268">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="G268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H268">
         <v>0</v>
@@ -18773,25 +18773,25 @@
         <v>171</v>
       </c>
       <c r="L268">
-        <v>2591</v>
+        <v>2438</v>
       </c>
       <c r="M268">
         <v>0</v>
       </c>
       <c r="N268">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O268">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P268">
         <v>0</v>
       </c>
       <c r="Q268">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="R268">
-        <v>1590</v>
+        <v>1684</v>
       </c>
       <c r="S268">
         <v>0</v>
@@ -18800,7 +18800,7 @@
         <v>0</v>
       </c>
       <c r="U268">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="V268">
         <v>0</v>
@@ -18891,7 +18891,7 @@
         <v>FORM7</v>
       </c>
       <c r="D270">
-        <v>9249</v>
+        <v>9145</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -18912,10 +18912,10 @@
         <v>0</v>
       </c>
       <c r="K270">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="L270">
-        <v>6161</v>
+        <v>5174</v>
       </c>
       <c r="M270">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="Q270">
-        <v>1175</v>
+        <v>2036</v>
       </c>
       <c r="R270">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="S270">
         <v>0</v>
@@ -18962,16 +18962,16 @@
         <v>FORM8</v>
       </c>
       <c r="D271">
-        <v>2383</v>
+        <v>2388</v>
       </c>
       <c r="E271">
         <v>0</v>
       </c>
       <c r="F271">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G271">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H271">
         <v>0</v>
@@ -18980,19 +18980,19 @@
         <v>0</v>
       </c>
       <c r="J271">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K271">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="L271">
         <v>11</v>
       </c>
       <c r="M271">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N271">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O271">
         <v>0</v>
@@ -19027,16 +19027,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D272">
-        <v>17035</v>
+        <v>16933</v>
       </c>
       <c r="E272">
         <v>0</v>
       </c>
       <c r="F272">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="G272">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H272">
         <v>0</v>
@@ -19045,31 +19045,31 @@
         <v>0</v>
       </c>
       <c r="J272">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K272">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="L272">
-        <v>8773</v>
+        <v>7633</v>
       </c>
       <c r="M272">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N272">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="O272">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P272">
         <v>0</v>
       </c>
       <c r="Q272">
-        <v>1337</v>
+        <v>2237</v>
       </c>
       <c r="R272">
-        <v>2520</v>
+        <v>2645</v>
       </c>
       <c r="S272">
         <v>0</v>
@@ -19078,7 +19078,7 @@
         <v>0</v>
       </c>
       <c r="U272">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="V272">
         <v>0</v>
@@ -19098,16 +19098,16 @@
         <v>FORM6</v>
       </c>
       <c r="D273">
-        <v>4663</v>
+        <v>4683</v>
       </c>
       <c r="E273">
         <v>0</v>
       </c>
       <c r="F273">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="G273">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H273">
         <v>0</v>
@@ -19116,40 +19116,40 @@
         <v>0</v>
       </c>
       <c r="J273">
+        <v>0</v>
+      </c>
+      <c r="K273">
+        <v>474</v>
+      </c>
+      <c r="L273">
+        <v>108</v>
+      </c>
+      <c r="M273">
+        <v>0</v>
+      </c>
+      <c r="N273">
+        <v>239</v>
+      </c>
+      <c r="O273">
+        <v>0</v>
+      </c>
+      <c r="P273">
+        <v>0</v>
+      </c>
+      <c r="Q273">
+        <v>30</v>
+      </c>
+      <c r="R273">
+        <v>1810</v>
+      </c>
+      <c r="S273">
+        <v>0</v>
+      </c>
+      <c r="T273">
+        <v>0</v>
+      </c>
+      <c r="U273">
         <v>1</v>
-      </c>
-      <c r="K273">
-        <v>508</v>
-      </c>
-      <c r="L273">
-        <v>61</v>
-      </c>
-      <c r="M273">
-        <v>83</v>
-      </c>
-      <c r="N273">
-        <v>238</v>
-      </c>
-      <c r="O273">
-        <v>0</v>
-      </c>
-      <c r="P273">
-        <v>0</v>
-      </c>
-      <c r="Q273">
-        <v>20</v>
-      </c>
-      <c r="R273">
-        <v>1742</v>
-      </c>
-      <c r="S273">
-        <v>0</v>
-      </c>
-      <c r="T273">
-        <v>0</v>
-      </c>
-      <c r="U273">
-        <v>0</v>
       </c>
       <c r="V273">
         <v>0</v>
@@ -19190,28 +19190,28 @@
         <v>0</v>
       </c>
       <c r="K274">
+        <v>0</v>
+      </c>
+      <c r="L274">
+        <v>0</v>
+      </c>
+      <c r="M274">
+        <v>0</v>
+      </c>
+      <c r="N274">
+        <v>0</v>
+      </c>
+      <c r="O274">
+        <v>0</v>
+      </c>
+      <c r="P274">
+        <v>0</v>
+      </c>
+      <c r="Q274">
+        <v>0</v>
+      </c>
+      <c r="R274">
         <v>4</v>
-      </c>
-      <c r="L274">
-        <v>0</v>
-      </c>
-      <c r="M274">
-        <v>0</v>
-      </c>
-      <c r="N274">
-        <v>0</v>
-      </c>
-      <c r="O274">
-        <v>0</v>
-      </c>
-      <c r="P274">
-        <v>0</v>
-      </c>
-      <c r="Q274">
-        <v>0</v>
-      </c>
-      <c r="R274">
-        <v>0</v>
       </c>
       <c r="S274">
         <v>0</v>
@@ -19264,7 +19264,7 @@
         <v>0</v>
       </c>
       <c r="L275">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="M275">
         <v>0</v>
@@ -19279,10 +19279,10 @@
         <v>0</v>
       </c>
       <c r="Q275">
-        <v>916</v>
+        <v>972</v>
       </c>
       <c r="R275">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="S275">
         <v>0</v>
@@ -19311,37 +19311,37 @@
         <v>FORM8</v>
       </c>
       <c r="D276">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="E276">
         <v>0</v>
       </c>
       <c r="F276">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G276">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H276">
         <v>0</v>
       </c>
       <c r="I276">
+        <v>0</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276">
         <v>1</v>
       </c>
-      <c r="J276">
-        <v>0</v>
-      </c>
-      <c r="K276">
-        <v>2</v>
-      </c>
       <c r="L276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M276">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N276">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="O276">
         <v>0</v>
@@ -19350,10 +19350,10 @@
         <v>0</v>
       </c>
       <c r="Q276">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="R276">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="S276">
         <v>0</v>
@@ -19376,58 +19376,58 @@
         <v>AC Form Total</v>
       </c>
       <c r="D277">
-        <v>8572</v>
+        <v>8595</v>
       </c>
       <c r="E277">
         <v>0</v>
       </c>
       <c r="F277">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="G277">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H277">
         <v>0</v>
       </c>
       <c r="I277">
+        <v>0</v>
+      </c>
+      <c r="J277">
+        <v>0</v>
+      </c>
+      <c r="K277">
+        <v>475</v>
+      </c>
+      <c r="L277">
+        <v>152</v>
+      </c>
+      <c r="M277">
+        <v>0</v>
+      </c>
+      <c r="N277">
+        <v>328</v>
+      </c>
+      <c r="O277">
+        <v>0</v>
+      </c>
+      <c r="P277">
+        <v>0</v>
+      </c>
+      <c r="Q277">
+        <v>1108</v>
+      </c>
+      <c r="R277">
+        <v>2317</v>
+      </c>
+      <c r="S277">
+        <v>0</v>
+      </c>
+      <c r="T277">
+        <v>0</v>
+      </c>
+      <c r="U277">
         <v>1</v>
-      </c>
-      <c r="J277">
-        <v>1</v>
-      </c>
-      <c r="K277">
-        <v>514</v>
-      </c>
-      <c r="L277">
-        <v>185</v>
-      </c>
-      <c r="M277">
-        <v>94</v>
-      </c>
-      <c r="N277">
-        <v>322</v>
-      </c>
-      <c r="O277">
-        <v>0</v>
-      </c>
-      <c r="P277">
-        <v>0</v>
-      </c>
-      <c r="Q277">
-        <v>1037</v>
-      </c>
-      <c r="R277">
-        <v>2213</v>
-      </c>
-      <c r="S277">
-        <v>0</v>
-      </c>
-      <c r="T277">
-        <v>0</v>
-      </c>
-      <c r="U277">
-        <v>0</v>
       </c>
       <c r="V277">
         <v>0</v>
@@ -19447,16 +19447,16 @@
         <v>FORM6</v>
       </c>
       <c r="D278">
-        <v>2585</v>
+        <v>2597</v>
       </c>
       <c r="E278">
         <v>0</v>
       </c>
       <c r="F278">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="G278">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H278">
         <v>0</v>
@@ -19468,16 +19468,16 @@
         <v>0</v>
       </c>
       <c r="K278">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L278">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M278">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N278">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="O278">
         <v>0</v>
@@ -19486,10 +19486,10 @@
         <v>0</v>
       </c>
       <c r="Q278">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="R278">
-        <v>1529</v>
+        <v>1546</v>
       </c>
       <c r="S278">
         <v>0</v>
@@ -19610,10 +19610,10 @@
         <v>0</v>
       </c>
       <c r="K280">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L280">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="M280">
         <v>0</v>
@@ -19628,7 +19628,7 @@
         <v>0</v>
       </c>
       <c r="Q280">
-        <v>1584</v>
+        <v>1627</v>
       </c>
       <c r="R280">
         <v>53</v>
@@ -19660,16 +19660,16 @@
         <v>FORM8</v>
       </c>
       <c r="D281">
-        <v>1164</v>
+        <v>1169</v>
       </c>
       <c r="E281">
         <v>0</v>
       </c>
       <c r="F281">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G281">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H281">
         <v>0</v>
@@ -19681,16 +19681,16 @@
         <v>0</v>
       </c>
       <c r="K281">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L281">
         <v>0</v>
       </c>
       <c r="M281">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N281">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="O281">
         <v>0</v>
@@ -19699,10 +19699,10 @@
         <v>0</v>
       </c>
       <c r="Q281">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="R281">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="S281">
         <v>0</v>
@@ -19725,16 +19725,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D282">
-        <v>5968</v>
+        <v>5985</v>
       </c>
       <c r="E282">
         <v>0</v>
       </c>
       <c r="F282">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="G282">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H282">
         <v>0</v>
@@ -19746,16 +19746,16 @@
         <v>4</v>
       </c>
       <c r="K282">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L282">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="M282">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N282">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="O282">
         <v>0</v>
@@ -19764,10 +19764,10 @@
         <v>0</v>
       </c>
       <c r="Q282">
-        <v>1717</v>
+        <v>1787</v>
       </c>
       <c r="R282">
-        <v>2039</v>
+        <v>2064</v>
       </c>
       <c r="S282">
         <v>0</v>
@@ -19796,40 +19796,40 @@
         <v>FORM6</v>
       </c>
       <c r="D283">
-        <v>3507</v>
+        <v>3512</v>
       </c>
       <c r="E283">
         <v>0</v>
       </c>
       <c r="F283">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="G283">
-        <v>1580</v>
+        <v>1454</v>
       </c>
       <c r="H283">
         <v>0</v>
       </c>
       <c r="I283">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J283">
-        <v>809</v>
+        <v>948</v>
       </c>
       <c r="K283">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="L283">
         <v>31</v>
       </c>
       <c r="M283">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="O283">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="P283">
         <v>0</v>
@@ -19838,7 +19838,7 @@
         <v>71</v>
       </c>
       <c r="R283">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="S283">
         <v>0</v>
@@ -19888,13 +19888,13 @@
         <v>0</v>
       </c>
       <c r="K284">
+        <v>0</v>
+      </c>
+      <c r="L284">
+        <v>0</v>
+      </c>
+      <c r="M284">
         <v>1</v>
-      </c>
-      <c r="L284">
-        <v>0</v>
-      </c>
-      <c r="M284">
-        <v>0</v>
       </c>
       <c r="N284">
         <v>0</v>
@@ -19938,7 +19938,7 @@
         <v>FORM7</v>
       </c>
       <c r="D285">
-        <v>6493</v>
+        <v>7309</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -19947,22 +19947,22 @@
         <v>2900</v>
       </c>
       <c r="G285">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H285">
         <v>0</v>
       </c>
       <c r="I285">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J285">
         <v>0</v>
       </c>
       <c r="K285">
-        <v>138</v>
+        <v>3</v>
       </c>
       <c r="L285">
-        <v>2805</v>
+        <v>3763</v>
       </c>
       <c r="M285">
         <v>8</v>
@@ -20009,16 +20009,16 @@
         <v>FORM8</v>
       </c>
       <c r="D286">
-        <v>1366</v>
+        <v>1410</v>
       </c>
       <c r="E286">
         <v>0</v>
       </c>
       <c r="F286">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G286">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H286">
         <v>0</v>
@@ -20027,10 +20027,10 @@
         <v>134</v>
       </c>
       <c r="J286">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="K286">
-        <v>398</v>
+        <v>272</v>
       </c>
       <c r="L286">
         <v>0</v>
@@ -20048,10 +20048,10 @@
         <v>0</v>
       </c>
       <c r="Q286">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="R286">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="S286">
         <v>0</v>
@@ -20074,49 +20074,49 @@
         <v>AC Form Total</v>
       </c>
       <c r="D287">
-        <v>11378</v>
+        <v>12243</v>
       </c>
       <c r="E287">
         <v>0</v>
       </c>
       <c r="F287">
-        <v>3481</v>
+        <v>3497</v>
       </c>
       <c r="G287">
-        <v>1788</v>
+        <v>1652</v>
       </c>
       <c r="H287">
         <v>0</v>
       </c>
       <c r="I287">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="J287">
-        <v>1245</v>
+        <v>1391</v>
       </c>
       <c r="K287">
-        <v>663</v>
+        <v>325</v>
       </c>
       <c r="L287">
-        <v>2836</v>
+        <v>3794</v>
       </c>
       <c r="M287">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="N287">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="O287">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="P287">
         <v>0</v>
       </c>
       <c r="Q287">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="R287">
-        <v>292</v>
+        <v>458</v>
       </c>
       <c r="S287">
         <v>0</v>
@@ -20145,16 +20145,16 @@
         <v>FORM6</v>
       </c>
       <c r="D288">
-        <v>5490</v>
+        <v>5519</v>
       </c>
       <c r="E288">
         <v>0</v>
       </c>
       <c r="F288">
-        <v>770</v>
+        <v>794</v>
       </c>
       <c r="G288">
-        <v>980</v>
+        <v>912</v>
       </c>
       <c r="H288">
         <v>2</v>
@@ -20163,10 +20163,10 @@
         <v>69</v>
       </c>
       <c r="J288">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="K288">
-        <v>3590</v>
+        <v>3584</v>
       </c>
       <c r="L288">
         <v>0</v>
@@ -20175,10 +20175,10 @@
         <v>0</v>
       </c>
       <c r="N288">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="O288">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P288">
         <v>0</v>
@@ -20187,7 +20187,7 @@
         <v>5</v>
       </c>
       <c r="R288">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="S288">
         <v>0</v>
@@ -20296,7 +20296,7 @@
         <v>2</v>
       </c>
       <c r="G290">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H290">
         <v>0</v>
@@ -20305,13 +20305,13 @@
         <v>0</v>
       </c>
       <c r="J290">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K290">
-        <v>5905</v>
+        <v>4587</v>
       </c>
       <c r="L290">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M290">
         <v>0</v>
@@ -20326,7 +20326,7 @@
         <v>0</v>
       </c>
       <c r="Q290">
-        <v>0</v>
+        <v>1303</v>
       </c>
       <c r="R290">
         <v>0</v>
@@ -20358,16 +20358,16 @@
         <v>FORM8</v>
       </c>
       <c r="D291">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="E291">
         <v>0</v>
       </c>
       <c r="F291">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G291">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="H291">
         <v>0</v>
@@ -20376,7 +20376,7 @@
         <v>194</v>
       </c>
       <c r="J291">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K291">
         <v>1314</v>
@@ -20423,16 +20423,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D292">
-        <v>16421</v>
+        <v>16452</v>
       </c>
       <c r="E292">
         <v>0</v>
       </c>
       <c r="F292">
-        <v>1009</v>
+        <v>1035</v>
       </c>
       <c r="G292">
-        <v>1173</v>
+        <v>1091</v>
       </c>
       <c r="H292">
         <v>2</v>
@@ -20441,31 +20441,31 @@
         <v>264</v>
       </c>
       <c r="J292">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="K292">
-        <v>10809</v>
+        <v>9485</v>
       </c>
       <c r="L292">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M292">
         <v>0</v>
       </c>
       <c r="N292">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="O292">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P292">
         <v>0</v>
       </c>
       <c r="Q292">
-        <v>5</v>
+        <v>1308</v>
       </c>
       <c r="R292">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="S292">
         <v>0</v>
@@ -20494,28 +20494,28 @@
         <v>FORM6</v>
       </c>
       <c r="D293">
-        <v>3265</v>
+        <v>3281</v>
       </c>
       <c r="E293">
         <v>0</v>
       </c>
       <c r="F293">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="G293">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="H293">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I293">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J293">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="K293">
-        <v>1193</v>
+        <v>1121</v>
       </c>
       <c r="L293">
         <v>464</v>
@@ -20524,7 +20524,7 @@
         <v>5</v>
       </c>
       <c r="N293">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="O293">
         <v>0</v>
@@ -20536,7 +20536,7 @@
         <v>4</v>
       </c>
       <c r="R293">
-        <v>390</v>
+        <v>678</v>
       </c>
       <c r="S293">
         <v>0</v>
@@ -20645,7 +20645,7 @@
         <v>0</v>
       </c>
       <c r="G295">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H295">
         <v>0</v>
@@ -20657,10 +20657,10 @@
         <v>0</v>
       </c>
       <c r="K295">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L295">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="M295">
         <v>0</v>
@@ -20675,7 +20675,7 @@
         <v>0</v>
       </c>
       <c r="Q295">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="R295">
         <v>48</v>
@@ -20707,28 +20707,28 @@
         <v>FORM8</v>
       </c>
       <c r="D296">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="E296">
         <v>0</v>
       </c>
       <c r="F296">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G296">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H296">
         <v>0</v>
       </c>
       <c r="I296">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J296">
         <v>0</v>
       </c>
       <c r="K296">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="L296">
         <v>12</v>
@@ -20746,10 +20746,10 @@
         <v>0</v>
       </c>
       <c r="Q296">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="R296">
-        <v>851</v>
+        <v>895</v>
       </c>
       <c r="S296">
         <v>0</v>
@@ -20772,37 +20772,37 @@
         <v>AC Form Total</v>
       </c>
       <c r="D297">
-        <v>10816</v>
+        <v>10836</v>
       </c>
       <c r="E297">
         <v>0</v>
       </c>
       <c r="F297">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="G297">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="H297">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I297">
         <v>61</v>
       </c>
       <c r="J297">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="K297">
-        <v>1336</v>
+        <v>1211</v>
       </c>
       <c r="L297">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="M297">
         <v>5</v>
       </c>
       <c r="N297">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="O297">
         <v>0</v>
@@ -20811,10 +20811,10 @@
         <v>0</v>
       </c>
       <c r="Q297">
-        <v>2289</v>
+        <v>2299</v>
       </c>
       <c r="R297">
-        <v>1289</v>
+        <v>1621</v>
       </c>
       <c r="S297">
         <v>0</v>
@@ -20843,13 +20843,13 @@
         <v>FORM6</v>
       </c>
       <c r="D298">
-        <v>1318</v>
+        <v>1337</v>
       </c>
       <c r="E298">
         <v>0</v>
       </c>
       <c r="F298">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="G298">
         <v>0</v>
@@ -20864,7 +20864,7 @@
         <v>0</v>
       </c>
       <c r="K298">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="L298">
         <v>0</v>
@@ -20876,7 +20876,7 @@
         <v>3</v>
       </c>
       <c r="O298">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P298">
         <v>0</v>
@@ -20885,7 +20885,7 @@
         <v>1</v>
       </c>
       <c r="R298">
-        <v>909</v>
+        <v>929</v>
       </c>
       <c r="S298">
         <v>0</v>
@@ -20985,13 +20985,13 @@
         <v>FORM8</v>
       </c>
       <c r="D300">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="E300">
         <v>0</v>
       </c>
       <c r="F300">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G300">
         <v>0</v>
@@ -21050,13 +21050,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D301">
-        <v>7634</v>
+        <v>7657</v>
       </c>
       <c r="E301">
         <v>0</v>
       </c>
       <c r="F301">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="G301">
         <v>0</v>
@@ -21071,7 +21071,7 @@
         <v>0</v>
       </c>
       <c r="K301">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="L301">
         <v>690</v>
@@ -21083,7 +21083,7 @@
         <v>9</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P301">
         <v>0</v>
@@ -21092,7 +21092,7 @@
         <v>4336</v>
       </c>
       <c r="R301">
-        <v>1791</v>
+        <v>1811</v>
       </c>
       <c r="S301">
         <v>0</v>
@@ -21121,16 +21121,16 @@
         <v>FORM6</v>
       </c>
       <c r="D302">
-        <v>2853</v>
+        <v>2860</v>
       </c>
       <c r="E302">
         <v>0</v>
       </c>
       <c r="F302">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="G302">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H302">
         <v>0</v>
@@ -21139,19 +21139,19 @@
         <v>38</v>
       </c>
       <c r="J302">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K302">
-        <v>2307</v>
+        <v>2442</v>
       </c>
       <c r="L302">
         <v>0</v>
       </c>
       <c r="M302">
+        <v>0</v>
+      </c>
+      <c r="N302">
         <v>1</v>
-      </c>
-      <c r="N302">
-        <v>6</v>
       </c>
       <c r="O302">
         <v>0</v>
@@ -21272,7 +21272,7 @@
         <v>1</v>
       </c>
       <c r="G304">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H304">
         <v>0</v>
@@ -21281,10 +21281,10 @@
         <v>0</v>
       </c>
       <c r="J304">
+        <v>1</v>
+      </c>
+      <c r="K304">
         <v>101</v>
-      </c>
-      <c r="K304">
-        <v>1</v>
       </c>
       <c r="L304">
         <v>4966</v>
@@ -21305,7 +21305,7 @@
         <v>1891</v>
       </c>
       <c r="R304">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S304">
         <v>0</v>
@@ -21334,31 +21334,31 @@
         <v>FORM8</v>
       </c>
       <c r="D305">
-        <v>1382</v>
+        <v>1394</v>
       </c>
       <c r="E305">
         <v>0</v>
       </c>
       <c r="F305">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G305">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H305">
         <v>0</v>
       </c>
       <c r="I305">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J305">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K305">
         <v>50</v>
       </c>
       <c r="L305">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M305">
         <v>0</v>
@@ -21373,10 +21373,10 @@
         <v>0</v>
       </c>
       <c r="Q305">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="R305">
-        <v>1060</v>
+        <v>1088</v>
       </c>
       <c r="S305">
         <v>0</v>
@@ -21399,37 +21399,37 @@
         <v>AC Form Total</v>
       </c>
       <c r="D306">
-        <v>12838</v>
+        <v>12857</v>
       </c>
       <c r="E306">
         <v>0</v>
       </c>
       <c r="F306">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="G306">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="H306">
         <v>0</v>
       </c>
       <c r="I306">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="J306">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="K306">
-        <v>2359</v>
+        <v>2594</v>
       </c>
       <c r="L306">
-        <v>4966</v>
+        <v>4972</v>
       </c>
       <c r="M306">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N306">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O306">
         <v>0</v>
@@ -21438,10 +21438,10 @@
         <v>0</v>
       </c>
       <c r="Q306">
-        <v>1988</v>
+        <v>2006</v>
       </c>
       <c r="R306">
-        <v>1150</v>
+        <v>1179</v>
       </c>
       <c r="S306">
         <v>0</v>
@@ -21470,13 +21470,13 @@
         <v>FORM6</v>
       </c>
       <c r="D307">
-        <v>1718</v>
+        <v>1714</v>
       </c>
       <c r="E307">
         <v>0</v>
       </c>
       <c r="F307">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -21485,31 +21485,31 @@
         <v>0</v>
       </c>
       <c r="I307">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J307">
         <v>0</v>
       </c>
       <c r="K307">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="L307">
+        <v>0</v>
+      </c>
+      <c r="M307">
+        <v>0</v>
+      </c>
+      <c r="N307">
+        <v>0</v>
+      </c>
+      <c r="O307">
         <v>1</v>
       </c>
-      <c r="M307">
-        <v>0</v>
-      </c>
-      <c r="N307">
-        <v>0</v>
-      </c>
-      <c r="O307">
-        <v>22</v>
-      </c>
       <c r="P307">
         <v>0</v>
       </c>
       <c r="Q307">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R307">
         <v>1289</v>
@@ -21562,10 +21562,10 @@
         <v>0</v>
       </c>
       <c r="K308">
-        <v>932</v>
+        <v>445</v>
       </c>
       <c r="L308">
-        <v>5009</v>
+        <v>4940</v>
       </c>
       <c r="M308">
         <v>10</v>
@@ -21580,7 +21580,7 @@
         <v>0</v>
       </c>
       <c r="Q308">
-        <v>2563</v>
+        <v>3119</v>
       </c>
       <c r="R308">
         <v>1</v>
@@ -21612,13 +21612,13 @@
         <v>FORM8</v>
       </c>
       <c r="D309">
-        <v>1060</v>
+        <v>1111</v>
       </c>
       <c r="E309">
         <v>0</v>
       </c>
       <c r="F309">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G309">
         <v>0</v>
@@ -21627,13 +21627,13 @@
         <v>0</v>
       </c>
       <c r="I309">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="J309">
         <v>0</v>
       </c>
       <c r="K309">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="L309">
         <v>0</v>
@@ -21642,7 +21642,7 @@
         <v>0</v>
       </c>
       <c r="N309">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O309">
         <v>6</v>
@@ -21651,10 +21651,10 @@
         <v>0</v>
       </c>
       <c r="Q309">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="R309">
-        <v>794</v>
+        <v>885</v>
       </c>
       <c r="S309">
         <v>0</v>
@@ -21677,13 +21677,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D310">
-        <v>13500</v>
+        <v>13547</v>
       </c>
       <c r="E310">
         <v>0</v>
       </c>
       <c r="F310">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="G310">
         <v>0</v>
@@ -21692,34 +21692,34 @@
         <v>0</v>
       </c>
       <c r="I310">
-        <v>2272</v>
+        <v>2204</v>
       </c>
       <c r="J310">
         <v>0</v>
       </c>
       <c r="K310">
-        <v>1153</v>
+        <v>631</v>
       </c>
       <c r="L310">
-        <v>5010</v>
+        <v>4940</v>
       </c>
       <c r="M310">
         <v>10</v>
       </c>
       <c r="N310">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O310">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="P310">
         <v>0</v>
       </c>
       <c r="Q310">
-        <v>2579</v>
+        <v>3216</v>
       </c>
       <c r="R310">
-        <v>2084</v>
+        <v>2175</v>
       </c>
       <c r="S310">
         <v>0</v>
@@ -21748,28 +21748,28 @@
         <v>FORM6</v>
       </c>
       <c r="D311">
-        <v>2355</v>
+        <v>2372</v>
       </c>
       <c r="E311">
         <v>0</v>
       </c>
       <c r="F311">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="G311">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="H311">
         <v>2</v>
       </c>
       <c r="I311">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J311">
-        <v>25</v>
+        <v>191</v>
       </c>
       <c r="K311">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="L311">
         <v>16</v>
@@ -21778,22 +21778,22 @@
         <v>47</v>
       </c>
       <c r="N311">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O311">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P311">
         <v>0</v>
       </c>
       <c r="Q311">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R311">
-        <v>1532</v>
+        <v>1580</v>
       </c>
       <c r="S311">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T311">
         <v>0</v>
@@ -21819,7 +21819,7 @@
         <v>FORM7</v>
       </c>
       <c r="D312">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -21828,7 +21828,7 @@
         <v>0</v>
       </c>
       <c r="G312">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="H312">
         <v>0</v>
@@ -21837,7 +21837,7 @@
         <v>0</v>
       </c>
       <c r="J312">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="K312">
         <v>377</v>
@@ -21846,7 +21846,7 @@
         <v>876</v>
       </c>
       <c r="M312">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N312">
         <v>2</v>
@@ -21899,7 +21899,7 @@
         <v>109</v>
       </c>
       <c r="G313">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="H313">
         <v>0</v>
@@ -21908,7 +21908,7 @@
         <v>0</v>
       </c>
       <c r="J313">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="K313">
         <v>0</v>
@@ -21917,7 +21917,7 @@
         <v>0</v>
       </c>
       <c r="M313">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N313">
         <v>5</v>
@@ -21955,52 +21955,52 @@
         <v>AC Form Total</v>
       </c>
       <c r="D314">
-        <v>5808</v>
+        <v>5826</v>
       </c>
       <c r="E314">
         <v>0</v>
       </c>
       <c r="F314">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="G314">
-        <v>413</v>
+        <v>91</v>
       </c>
       <c r="H314">
         <v>2</v>
       </c>
       <c r="I314">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J314">
-        <v>246</v>
+        <v>555</v>
       </c>
       <c r="K314">
-        <v>567</v>
+        <v>536</v>
       </c>
       <c r="L314">
         <v>892</v>
       </c>
       <c r="M314">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N314">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O314">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P314">
         <v>0</v>
       </c>
       <c r="Q314">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="R314">
-        <v>2380</v>
+        <v>2428</v>
       </c>
       <c r="S314">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T314">
         <v>0</v>
@@ -22026,13 +22026,13 @@
         <v>FORM6</v>
       </c>
       <c r="D315">
-        <v>1668</v>
+        <v>1674</v>
       </c>
       <c r="E315">
         <v>0</v>
       </c>
       <c r="F315">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G315">
         <v>0</v>
@@ -22041,13 +22041,13 @@
         <v>0</v>
       </c>
       <c r="I315">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J315">
         <v>0</v>
       </c>
       <c r="K315">
-        <v>1009</v>
+        <v>522</v>
       </c>
       <c r="L315">
         <v>4</v>
@@ -22056,19 +22056,19 @@
         <v>0</v>
       </c>
       <c r="N315">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O315">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="P315">
         <v>0</v>
       </c>
       <c r="Q315">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R315">
-        <v>484</v>
+        <v>996</v>
       </c>
       <c r="S315">
         <v>0</v>
@@ -22106,19 +22106,19 @@
         <v>0</v>
       </c>
       <c r="G316">
+        <v>0</v>
+      </c>
+      <c r="H316">
+        <v>0</v>
+      </c>
+      <c r="I316">
+        <v>0</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316">
         <v>2</v>
-      </c>
-      <c r="H316">
-        <v>0</v>
-      </c>
-      <c r="I316">
-        <v>0</v>
-      </c>
-      <c r="J316">
-        <v>0</v>
-      </c>
-      <c r="K316">
-        <v>0</v>
       </c>
       <c r="L316">
         <v>323</v>
@@ -22168,13 +22168,13 @@
         <v>FORM8</v>
       </c>
       <c r="D317">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="E317">
         <v>0</v>
       </c>
       <c r="F317">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G317">
         <v>0</v>
@@ -22183,13 +22183,13 @@
         <v>0</v>
       </c>
       <c r="I317">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J317">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K317">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="L317">
         <v>0</v>
@@ -22198,19 +22198,19 @@
         <v>0</v>
       </c>
       <c r="N317">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="O317">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P317">
         <v>0</v>
       </c>
       <c r="Q317">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R317">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="S317">
         <v>0</v>
@@ -22233,28 +22233,28 @@
         <v>AC Form Total</v>
       </c>
       <c r="D318">
-        <v>5517</v>
+        <v>5531</v>
       </c>
       <c r="E318">
         <v>0</v>
       </c>
       <c r="F318">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="G318">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H318">
         <v>0</v>
       </c>
       <c r="I318">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J318">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K318">
-        <v>1031</v>
+        <v>602</v>
       </c>
       <c r="L318">
         <v>327</v>
@@ -22263,19 +22263,19 @@
         <v>0</v>
       </c>
       <c r="N318">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="O318">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="P318">
         <v>0</v>
       </c>
       <c r="Q318">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="R318">
-        <v>1085</v>
+        <v>1603</v>
       </c>
       <c r="S318">
         <v>0</v>
@@ -22304,28 +22304,28 @@
         <v>FORM6</v>
       </c>
       <c r="D319">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="E319">
         <v>0</v>
       </c>
       <c r="F319">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G319">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="H319">
         <v>0</v>
       </c>
       <c r="I319">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J319">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="K319">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L319">
         <v>0</v>
@@ -22334,7 +22334,7 @@
         <v>0</v>
       </c>
       <c r="N319">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="O319">
         <v>0</v>
@@ -22346,7 +22346,7 @@
         <v>2</v>
       </c>
       <c r="R319">
-        <v>506</v>
+        <v>617</v>
       </c>
       <c r="S319">
         <v>0</v>
@@ -22446,7 +22446,7 @@
         <v>FORM7</v>
       </c>
       <c r="D321">
-        <v>2286</v>
+        <v>2290</v>
       </c>
       <c r="E321">
         <v>0</v>
@@ -22464,10 +22464,10 @@
         <v>0</v>
       </c>
       <c r="J321">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K321">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L321">
         <v>845</v>
@@ -22485,7 +22485,7 @@
         <v>0</v>
       </c>
       <c r="Q321">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="R321">
         <v>1</v>
@@ -22503,7 +22503,7 @@
         <v>0</v>
       </c>
       <c r="W321">
-        <v>1082</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="322">
@@ -22517,16 +22517,16 @@
         <v>FORM8</v>
       </c>
       <c r="D322">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="E322">
         <v>0</v>
       </c>
       <c r="F322">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G322">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H322">
         <v>0</v>
@@ -22535,10 +22535,10 @@
         <v>0</v>
       </c>
       <c r="J322">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K322">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="L322">
         <v>0</v>
@@ -22556,10 +22556,10 @@
         <v>0</v>
       </c>
       <c r="Q322">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="R322">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="S322">
         <v>0</v>
@@ -22582,28 +22582,28 @@
         <v>AC Form Total</v>
       </c>
       <c r="D323">
-        <v>4243</v>
+        <v>4256</v>
       </c>
       <c r="E323">
         <v>0</v>
       </c>
       <c r="F323">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="G323">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="H323">
         <v>0</v>
       </c>
       <c r="I323">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J323">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="K323">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="L323">
         <v>845</v>
@@ -22612,7 +22612,7 @@
         <v>0</v>
       </c>
       <c r="N323">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="O323">
         <v>0</v>
@@ -22621,10 +22621,10 @@
         <v>0</v>
       </c>
       <c r="Q323">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="R323">
-        <v>920</v>
+        <v>1076</v>
       </c>
       <c r="S323">
         <v>0</v>
@@ -22639,7 +22639,7 @@
         <v>0</v>
       </c>
       <c r="W323">
-        <v>1082</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="324">
@@ -22647,58 +22647,58 @@
         <v>All AC Form-6 Total</v>
       </c>
       <c r="D324">
-        <v>161435</v>
+        <v>161779</v>
       </c>
       <c r="E324">
         <v>0</v>
       </c>
       <c r="F324">
-        <v>10871</v>
+        <v>11211</v>
       </c>
       <c r="G324">
-        <v>4956</v>
+        <v>4588</v>
       </c>
       <c r="H324">
-        <v>234</v>
+        <v>177</v>
       </c>
       <c r="I324">
-        <v>880</v>
+        <v>934</v>
       </c>
       <c r="J324">
-        <v>2952</v>
+        <v>2400</v>
       </c>
       <c r="K324">
-        <v>14822</v>
+        <v>14043</v>
       </c>
       <c r="L324">
-        <v>18435</v>
+        <v>17059</v>
       </c>
       <c r="M324">
-        <v>1944</v>
+        <v>1511</v>
       </c>
       <c r="N324">
-        <v>2788</v>
+        <v>2352</v>
       </c>
       <c r="O324">
-        <v>264</v>
+        <v>143</v>
       </c>
       <c r="P324">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q324">
-        <v>5650</v>
+        <v>6621</v>
       </c>
       <c r="R324">
-        <v>75587</v>
+        <v>78795</v>
       </c>
       <c r="S324">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T324">
         <v>0</v>
       </c>
       <c r="U324">
-        <v>705</v>
+        <v>591</v>
       </c>
       <c r="V324">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="F325">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G325">
         <v>13</v>
@@ -22733,16 +22733,16 @@
         <v>5</v>
       </c>
       <c r="K325">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L325">
         <v>11</v>
       </c>
       <c r="M325">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N325">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O325">
         <v>0</v>
@@ -22751,10 +22751,10 @@
         <v>0</v>
       </c>
       <c r="Q325">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R325">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="S325">
         <v>0</v>
@@ -22777,64 +22777,64 @@
         <v>All AC Form-7 Total</v>
       </c>
       <c r="D326">
-        <v>146867</v>
+        <v>147609</v>
       </c>
       <c r="E326">
         <v>0</v>
       </c>
       <c r="F326">
-        <v>3284</v>
+        <v>3285</v>
       </c>
       <c r="G326">
-        <v>518</v>
+        <v>453</v>
       </c>
       <c r="H326">
         <v>0</v>
       </c>
       <c r="I326">
-        <v>2341</v>
+        <v>2322</v>
       </c>
       <c r="J326">
-        <v>291</v>
+        <v>204</v>
       </c>
       <c r="K326">
-        <v>7942</v>
+        <v>6089</v>
       </c>
       <c r="L326">
-        <v>24853</v>
+        <v>24093</v>
       </c>
       <c r="M326">
+        <v>20</v>
+      </c>
+      <c r="N326">
+        <v>122</v>
+      </c>
+      <c r="O326">
+        <v>0</v>
+      </c>
+      <c r="P326">
+        <v>0</v>
+      </c>
+      <c r="Q326">
+        <v>53605</v>
+      </c>
+      <c r="R326">
+        <v>4934</v>
+      </c>
+      <c r="S326">
+        <v>0</v>
+      </c>
+      <c r="T326">
+        <v>0</v>
+      </c>
+      <c r="U326">
         <v>24</v>
       </c>
-      <c r="N326">
-        <v>140</v>
-      </c>
-      <c r="O326">
-        <v>0</v>
-      </c>
-      <c r="P326">
-        <v>0</v>
-      </c>
-      <c r="Q326">
-        <v>50281</v>
-      </c>
-      <c r="R326">
-        <v>4742</v>
-      </c>
-      <c r="S326">
-        <v>0</v>
-      </c>
-      <c r="T326">
-        <v>0</v>
-      </c>
-      <c r="U326">
-        <v>10</v>
-      </c>
       <c r="V326">
         <v>0</v>
       </c>
       <c r="W326">
-        <v>52441</v>
+        <v>52458</v>
       </c>
     </row>
     <row r="327">
@@ -22842,49 +22842,49 @@
         <v>All AC Form-8 Total</v>
       </c>
       <c r="D327">
-        <v>60468</v>
+        <v>60679</v>
       </c>
       <c r="E327">
         <v>0</v>
       </c>
       <c r="F327">
-        <v>5040</v>
+        <v>5133</v>
       </c>
       <c r="G327">
-        <v>860</v>
+        <v>649</v>
       </c>
       <c r="H327">
         <v>1</v>
       </c>
       <c r="I327">
-        <v>1603</v>
+        <v>960</v>
       </c>
       <c r="J327">
-        <v>589</v>
+        <v>679</v>
       </c>
       <c r="K327">
-        <v>4745</v>
+        <v>4508</v>
       </c>
       <c r="L327">
-        <v>419</v>
+        <v>367</v>
       </c>
       <c r="M327">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="N327">
-        <v>997</v>
+        <v>871</v>
       </c>
       <c r="O327">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="P327">
         <v>1</v>
       </c>
       <c r="Q327">
-        <v>3813</v>
+        <v>4091</v>
       </c>
       <c r="R327">
-        <v>28777</v>
+        <v>29831</v>
       </c>
       <c r="S327">
         <v>1</v>
@@ -22893,7 +22893,7 @@
         <v>0</v>
       </c>
       <c r="U327">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V327">
         <v>0</v>
@@ -22907,64 +22907,64 @@
         <v>All AC Form Total</v>
       </c>
       <c r="D328">
-        <v>368907</v>
+        <v>370204</v>
       </c>
       <c r="E328">
         <v>0</v>
       </c>
       <c r="F328">
-        <v>19219</v>
+        <v>19652</v>
       </c>
       <c r="G328">
-        <v>6347</v>
+        <v>5703</v>
       </c>
       <c r="H328">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="I328">
-        <v>4832</v>
+        <v>4224</v>
       </c>
       <c r="J328">
-        <v>3837</v>
+        <v>3288</v>
       </c>
       <c r="K328">
-        <v>27523</v>
+        <v>24650</v>
       </c>
       <c r="L328">
-        <v>43718</v>
+        <v>41530</v>
       </c>
       <c r="M328">
-        <v>2046</v>
+        <v>1581</v>
       </c>
       <c r="N328">
-        <v>3935</v>
+        <v>3354</v>
       </c>
       <c r="O328">
-        <v>283</v>
+        <v>154</v>
       </c>
       <c r="P328">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q328">
-        <v>59776</v>
+        <v>64350</v>
       </c>
       <c r="R328">
-        <v>109126</v>
+        <v>113584</v>
       </c>
       <c r="S328">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T328">
         <v>0</v>
       </c>
       <c r="U328">
-        <v>719</v>
+        <v>621</v>
       </c>
       <c r="V328">
         <v>0</v>
       </c>
       <c r="W328">
-        <v>87281</v>
+        <v>87298</v>
       </c>
     </row>
   </sheetData>

--- a/Form_Processing.xlsx
+++ b/Form_Processing.xlsx
@@ -411,7 +411,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>From - 15/07/2026       To - 21/09/2026</v>
+        <v>From - 15/07/2026       To - 22/09/2026</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>FORM6</v>
       </c>
       <c r="D6">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -510,7 +510,7 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>FORM8</v>
       </c>
       <c r="D8">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8">
         <v>9</v>
@@ -708,16 +708,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D9">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -779,13 +779,13 @@
         <v>FORM6</v>
       </c>
       <c r="D10">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -986,13 +986,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D13">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1057,13 +1057,13 @@
         <v>FORM6</v>
       </c>
       <c r="D14">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1199,13 +1199,13 @@
         <v>FORM8</v>
       </c>
       <c r="D16">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D17">
-        <v>2748</v>
+        <v>2750</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R18">
         <v>745</v>
@@ -1634,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="R22">
         <v>1140</v>
@@ -1962,13 +1962,13 @@
         <v>FORM6</v>
       </c>
       <c r="D27">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -2125,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="R29">
         <v>131</v>
@@ -2175,13 +2175,13 @@
         <v>FORM8</v>
       </c>
       <c r="D30">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -2240,13 +2240,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D31">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2279,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="R31">
         <v>181</v>
@@ -2311,13 +2311,13 @@
         <v>FORM6</v>
       </c>
       <c r="D32">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -2524,13 +2524,13 @@
         <v>FORM8</v>
       </c>
       <c r="D35">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -2589,13 +2589,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D36">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -2660,13 +2660,13 @@
         <v>FORM6</v>
       </c>
       <c r="D37">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -2802,13 +2802,13 @@
         <v>FORM8</v>
       </c>
       <c r="D39">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -2867,13 +2867,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D40">
-        <v>1853</v>
+        <v>1856</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2938,13 +2938,13 @@
         <v>FORM6</v>
       </c>
       <c r="D41">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D44">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>FORM6</v>
       </c>
       <c r="D45">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -3358,13 +3358,13 @@
         <v>FORM8</v>
       </c>
       <c r="D47">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -3423,13 +3423,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D48">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -3494,13 +3494,13 @@
         <v>FORM6</v>
       </c>
       <c r="D49">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -3707,13 +3707,13 @@
         <v>FORM8</v>
       </c>
       <c r="D52">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E52">
         <v>0</v>
       </c>
       <c r="F52">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -3772,13 +3772,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D53">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -3985,13 +3985,13 @@
         <v>FORM8</v>
       </c>
       <c r="D56">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -4050,13 +4050,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D57">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="E57">
         <v>0</v>
       </c>
       <c r="F57">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -4121,13 +4121,13 @@
         <v>FORM6</v>
       </c>
       <c r="D58">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -4334,13 +4334,13 @@
         <v>FORM8</v>
       </c>
       <c r="D61">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="F61">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -4399,13 +4399,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D62">
-        <v>1830</v>
+        <v>1834</v>
       </c>
       <c r="E62">
         <v>0</v>
       </c>
       <c r="F62">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -4683,13 +4683,13 @@
         <v>FORM8</v>
       </c>
       <c r="D66">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E66">
         <v>0</v>
       </c>
       <c r="F66">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -4748,13 +4748,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D67">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E67">
         <v>0</v>
       </c>
       <c r="F67">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -4819,13 +4819,13 @@
         <v>FORM6</v>
       </c>
       <c r="D68">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="E68">
         <v>0</v>
       </c>
       <c r="F68">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -4890,7 +4890,7 @@
         <v>FORM7</v>
       </c>
       <c r="D69">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4947,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="W69">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="70">
@@ -5026,13 +5026,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D71">
-        <v>4501</v>
+        <v>4505</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="W71">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
     <row r="72">
@@ -5097,13 +5097,13 @@
         <v>FORM6</v>
       </c>
       <c r="D72">
-        <v>3721</v>
+        <v>3723</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G72">
         <v>6</v>
@@ -5310,13 +5310,13 @@
         <v>FORM8</v>
       </c>
       <c r="D75">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="E75">
         <v>0</v>
       </c>
       <c r="F75">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -5331,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -5349,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="R75">
         <v>1038</v>
@@ -5375,13 +5375,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D76">
-        <v>6628</v>
+        <v>6631</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G76">
         <v>6</v>
@@ -5396,7 +5396,7 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -5414,7 +5414,7 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="R76">
         <v>3931</v>
@@ -5446,13 +5446,13 @@
         <v>FORM6</v>
       </c>
       <c r="D77">
-        <v>4811</v>
+        <v>4816</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="Q77">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="R77">
         <v>3448</v>
@@ -5588,7 +5588,7 @@
         <v>FORM7</v>
       </c>
       <c r="D79">
-        <v>979</v>
+        <v>2059</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5645,7 +5645,7 @@
         <v>0</v>
       </c>
       <c r="W79">
-        <v>31</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="80">
@@ -5659,13 +5659,13 @@
         <v>FORM8</v>
       </c>
       <c r="D80">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="E80">
         <v>0</v>
       </c>
       <c r="F80">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -5724,13 +5724,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D81">
-        <v>7337</v>
+        <v>8426</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="F81">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -5745,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="Q81">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="R81">
         <v>4854</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="W81">
-        <v>34</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="82">
@@ -5795,13 +5795,13 @@
         <v>FORM6</v>
       </c>
       <c r="D82">
-        <v>9752</v>
+        <v>9765</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82">
-        <v>720</v>
+        <v>733</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>FORM7</v>
       </c>
       <c r="D84">
-        <v>1106</v>
+        <v>4549</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5994,7 +5994,7 @@
         <v>0</v>
       </c>
       <c r="W84">
-        <v>71</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="85">
@@ -6008,13 +6008,13 @@
         <v>FORM8</v>
       </c>
       <c r="D85">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -6073,13 +6073,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D86">
-        <v>13397</v>
+        <v>16857</v>
       </c>
       <c r="E86">
         <v>0</v>
       </c>
       <c r="F86">
-        <v>947</v>
+        <v>964</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -6130,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="W86">
-        <v>84</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="87">
@@ -6144,16 +6144,16 @@
         <v>FORM6</v>
       </c>
       <c r="D87">
-        <v>4929</v>
+        <v>4934</v>
       </c>
       <c r="E87">
         <v>0</v>
       </c>
       <c r="F87">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="G87">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="N87">
-        <v>311</v>
+        <v>533</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -6183,10 +6183,10 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="R87">
-        <v>3005</v>
+        <v>3010</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -6286,7 +6286,7 @@
         <v>FORM7</v>
       </c>
       <c r="D89">
-        <v>2124</v>
+        <v>2139</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="W89">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90">
@@ -6357,13 +6357,13 @@
         <v>FORM8</v>
       </c>
       <c r="D90">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
       <c r="F90">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -6422,16 +6422,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D91">
-        <v>8825</v>
+        <v>8847</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="G91">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="N91">
-        <v>314</v>
+        <v>536</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -6461,10 +6461,10 @@
         <v>0</v>
       </c>
       <c r="Q91">
-        <v>2940</v>
+        <v>2935</v>
       </c>
       <c r="R91">
-        <v>4544</v>
+        <v>4549</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -6479,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="W91">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
@@ -6493,13 +6493,13 @@
         <v>FORM6</v>
       </c>
       <c r="D92">
-        <v>4020</v>
+        <v>4021</v>
       </c>
       <c r="E92">
         <v>0</v>
       </c>
       <c r="F92">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -6706,13 +6706,13 @@
         <v>FORM8</v>
       </c>
       <c r="D95">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="E95">
         <v>0</v>
       </c>
       <c r="F95">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -6771,13 +6771,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D96">
-        <v>8994</v>
+        <v>8996</v>
       </c>
       <c r="E96">
         <v>0</v>
       </c>
       <c r="F96">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -6842,13 +6842,13 @@
         <v>FORM6</v>
       </c>
       <c r="D97">
-        <v>3501</v>
+        <v>3505</v>
       </c>
       <c r="E97">
         <v>0</v>
       </c>
       <c r="F97">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -6984,7 +6984,7 @@
         <v>FORM7</v>
       </c>
       <c r="D99">
-        <v>2261</v>
+        <v>2339</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -7041,7 +7041,7 @@
         <v>0</v>
       </c>
       <c r="W99">
-        <v>1750</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="100">
@@ -7055,13 +7055,13 @@
         <v>FORM8</v>
       </c>
       <c r="D100">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="E100">
         <v>0</v>
       </c>
       <c r="F100">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -7120,13 +7120,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D101">
-        <v>7109</v>
+        <v>7192</v>
       </c>
       <c r="E101">
         <v>0</v>
       </c>
       <c r="F101">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -7177,7 +7177,7 @@
         <v>0</v>
       </c>
       <c r="W101">
-        <v>2323</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="102">
@@ -7191,13 +7191,13 @@
         <v>FORM6</v>
       </c>
       <c r="D102">
-        <v>4939</v>
+        <v>4944</v>
       </c>
       <c r="E102">
         <v>0</v>
       </c>
       <c r="F102">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -7212,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="R102">
-        <v>2694</v>
+        <v>2698</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>0</v>
       </c>
       <c r="U102">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V102">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>FORM8</v>
       </c>
       <c r="D105">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="E105">
         <v>0</v>
       </c>
       <c r="F105">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -7449,13 +7449,13 @@
         <v>933</v>
       </c>
       <c r="S105">
+        <v>0</v>
+      </c>
+      <c r="T105">
+        <v>0</v>
+      </c>
+      <c r="U105">
         <v>2</v>
-      </c>
-      <c r="T105">
-        <v>0</v>
-      </c>
-      <c r="U105">
-        <v>0</v>
       </c>
       <c r="V105">
         <v>0</v>
@@ -7469,13 +7469,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D106">
-        <v>10491</v>
+        <v>10500</v>
       </c>
       <c r="E106">
         <v>0</v>
       </c>
       <c r="F106">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -7508,19 +7508,19 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>2354</v>
+        <v>2352</v>
       </c>
       <c r="R106">
-        <v>3747</v>
+        <v>3751</v>
       </c>
       <c r="S106">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T106">
         <v>0</v>
       </c>
       <c r="U106">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V106">
         <v>0</v>
@@ -7540,13 +7540,13 @@
         <v>FORM6</v>
       </c>
       <c r="D107">
-        <v>5226</v>
+        <v>5232</v>
       </c>
       <c r="E107">
         <v>0</v>
       </c>
       <c r="F107">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>FORM8</v>
       </c>
       <c r="D110">
-        <v>2151</v>
+        <v>2157</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="F110">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -7818,13 +7818,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D111">
-        <v>12259</v>
+        <v>12271</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111">
-        <v>1039</v>
+        <v>1051</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -7889,13 +7889,13 @@
         <v>FORM6</v>
       </c>
       <c r="D112">
-        <v>5228</v>
+        <v>5244</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
       <c r="F112">
-        <v>712</v>
+        <v>728</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -7928,10 +7928,10 @@
         <v>0</v>
       </c>
       <c r="Q112">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="R112">
-        <v>2807</v>
+        <v>2818</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -8031,7 +8031,7 @@
         <v>FORM7</v>
       </c>
       <c r="D114">
-        <v>1577</v>
+        <v>3471</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -8088,7 +8088,7 @@
         <v>0</v>
       </c>
       <c r="W114">
-        <v>476</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="115">
@@ -8102,13 +8102,13 @@
         <v>FORM8</v>
       </c>
       <c r="D115">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -8132,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="N115">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -8144,7 +8144,7 @@
         <v>135</v>
       </c>
       <c r="R115">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="S115">
         <v>0</v>
@@ -8167,13 +8167,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D116">
-        <v>8221</v>
+        <v>10133</v>
       </c>
       <c r="E116">
         <v>0</v>
       </c>
       <c r="F116">
-        <v>1045</v>
+        <v>1063</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -8197,7 +8197,7 @@
         <v>0</v>
       </c>
       <c r="N116">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="O116">
         <v>0</v>
@@ -8206,10 +8206,10 @@
         <v>0</v>
       </c>
       <c r="Q116">
-        <v>1590</v>
+        <v>1579</v>
       </c>
       <c r="R116">
-        <v>3904</v>
+        <v>3914</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -8224,7 +8224,7 @@
         <v>0</v>
       </c>
       <c r="W116">
-        <v>608</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="117">
@@ -8238,13 +8238,13 @@
         <v>FORM6</v>
       </c>
       <c r="D117">
-        <v>5718</v>
+        <v>5730</v>
       </c>
       <c r="E117">
         <v>0</v>
       </c>
       <c r="F117">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -8380,13 +8380,13 @@
         <v>FORM8</v>
       </c>
       <c r="D119">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
       <c r="F119">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -8445,13 +8445,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D120">
-        <v>6930</v>
+        <v>6944</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="G120">
         <v>4</v>
@@ -8516,13 +8516,13 @@
         <v>FORM6</v>
       </c>
       <c r="D121">
-        <v>4496</v>
+        <v>4507</v>
       </c>
       <c r="E121">
         <v>0</v>
       </c>
       <c r="F121">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -8729,13 +8729,13 @@
         <v>FORM8</v>
       </c>
       <c r="D124">
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="E124">
         <v>0</v>
       </c>
       <c r="F124">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -8794,13 +8794,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D125">
-        <v>8247</v>
+        <v>8261</v>
       </c>
       <c r="E125">
         <v>0</v>
       </c>
       <c r="F125">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="G125">
         <v>7</v>
@@ -8865,20 +8865,20 @@
         <v>FORM6</v>
       </c>
       <c r="D126">
-        <v>2437</v>
+        <v>2444</v>
       </c>
       <c r="E126">
         <v>0</v>
       </c>
       <c r="F126">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
         <v>3</v>
       </c>
-      <c r="H126">
-        <v>0</v>
-      </c>
       <c r="I126">
         <v>0</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>0</v>
       </c>
       <c r="L126">
-        <v>804</v>
+        <v>503</v>
       </c>
       <c r="M126">
         <v>1</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="Q126">
-        <v>654</v>
+        <v>773</v>
       </c>
       <c r="R126">
-        <v>588</v>
+        <v>770</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="L128">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M128">
         <v>0</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="Q128">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="R128">
         <v>100</v>
@@ -9078,13 +9078,13 @@
         <v>FORM8</v>
       </c>
       <c r="D129">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="E129">
         <v>0</v>
       </c>
       <c r="F129">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -9143,19 +9143,19 @@
         <v>AC Form Total</v>
       </c>
       <c r="D130">
-        <v>6304</v>
+        <v>6317</v>
       </c>
       <c r="E130">
         <v>0</v>
       </c>
       <c r="F130">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="G130">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H130">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I130">
         <v>2</v>
@@ -9167,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="L130">
-        <v>806</v>
+        <v>503</v>
       </c>
       <c r="M130">
         <v>1</v>
@@ -9182,10 +9182,10 @@
         <v>0</v>
       </c>
       <c r="Q130">
-        <v>2926</v>
+        <v>3047</v>
       </c>
       <c r="R130">
-        <v>1300</v>
+        <v>1482</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>FORM6</v>
       </c>
       <c r="D131">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="E131">
         <v>0</v>
       </c>
       <c r="F131">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G131">
         <v>98</v>
@@ -9253,7 +9253,7 @@
         <v>0</v>
       </c>
       <c r="Q131">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="R131">
         <v>930</v>
@@ -9265,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="U131">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V131">
         <v>0</v>
@@ -9285,7 +9285,7 @@
         <v>FORM7</v>
       </c>
       <c r="D132">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -9324,7 +9324,7 @@
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="R132">
         <v>55</v>
@@ -9356,13 +9356,13 @@
         <v>FORM8</v>
       </c>
       <c r="D133">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="E133">
         <v>0</v>
       </c>
       <c r="F133">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G133">
         <v>6</v>
@@ -9421,13 +9421,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D134">
-        <v>4843</v>
+        <v>4850</v>
       </c>
       <c r="E134">
         <v>0</v>
       </c>
       <c r="F134">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="G134">
         <v>105</v>
@@ -9460,7 +9460,7 @@
         <v>0</v>
       </c>
       <c r="Q134">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="R134">
         <v>1683</v>
@@ -9472,7 +9472,7 @@
         <v>0</v>
       </c>
       <c r="U134">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V134">
         <v>0</v>
@@ -9492,13 +9492,13 @@
         <v>FORM6</v>
       </c>
       <c r="D135">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="E135">
         <v>0</v>
       </c>
       <c r="F135">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G135">
         <v>27</v>
@@ -9705,13 +9705,13 @@
         <v>FORM8</v>
       </c>
       <c r="D138">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="E138">
         <v>0</v>
       </c>
       <c r="F138">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -9770,13 +9770,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D139">
-        <v>8860</v>
+        <v>8867</v>
       </c>
       <c r="E139">
         <v>0</v>
       </c>
       <c r="F139">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="G139">
         <v>27</v>
@@ -9841,13 +9841,13 @@
         <v>FORM6</v>
       </c>
       <c r="D140">
-        <v>2385</v>
+        <v>2394</v>
       </c>
       <c r="E140">
         <v>0</v>
       </c>
       <c r="F140">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G140">
         <v>88</v>
@@ -9983,16 +9983,16 @@
         <v>FORM8</v>
       </c>
       <c r="D142">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E142">
         <v>0</v>
       </c>
       <c r="F142">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G142">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -10001,7 +10001,7 @@
         <v>0</v>
       </c>
       <c r="J142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K142">
         <v>0</v>
@@ -10048,16 +10048,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D143">
-        <v>6511</v>
+        <v>6522</v>
       </c>
       <c r="E143">
         <v>0</v>
       </c>
       <c r="F143">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="G143">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -10066,7 +10066,7 @@
         <v>0</v>
       </c>
       <c r="J143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K143">
         <v>0</v>
@@ -10119,25 +10119,25 @@
         <v>FORM6</v>
       </c>
       <c r="D144">
-        <v>2993</v>
+        <v>2999</v>
       </c>
       <c r="E144">
         <v>0</v>
       </c>
       <c r="F144">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G144">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="H144">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I144">
         <v>0</v>
       </c>
       <c r="J144">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K144">
         <v>0</v>
@@ -10146,10 +10146,10 @@
         <v>0</v>
       </c>
       <c r="M144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N144">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O144">
         <v>0</v>
@@ -10332,22 +10332,22 @@
         <v>FORM8</v>
       </c>
       <c r="D147">
-        <v>1538</v>
+        <v>1545</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="G147">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147">
         <v>0</v>
@@ -10362,7 +10362,7 @@
         <v>0</v>
       </c>
       <c r="N147">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O147">
         <v>0</v>
@@ -10371,7 +10371,7 @@
         <v>0</v>
       </c>
       <c r="Q147">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R147">
         <v>247</v>
@@ -10397,25 +10397,25 @@
         <v>AC Form Total</v>
       </c>
       <c r="D148">
-        <v>6390</v>
+        <v>6403</v>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
       <c r="F148">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="G148">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="H148">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K148">
         <v>0</v>
@@ -10424,10 +10424,10 @@
         <v>0</v>
       </c>
       <c r="M148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N148">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O148">
         <v>0</v>
@@ -10436,7 +10436,7 @@
         <v>0</v>
       </c>
       <c r="Q148">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="R148">
         <v>2082</v>
@@ -10468,13 +10468,13 @@
         <v>FORM6</v>
       </c>
       <c r="D149">
-        <v>2441</v>
+        <v>2444</v>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
       <c r="F149">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -10681,13 +10681,13 @@
         <v>FORM8</v>
       </c>
       <c r="D152">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="E152">
         <v>0</v>
       </c>
       <c r="F152">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -10746,13 +10746,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D153">
-        <v>6509</v>
+        <v>6514</v>
       </c>
       <c r="E153">
         <v>0</v>
       </c>
       <c r="F153">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -10817,13 +10817,13 @@
         <v>FORM6</v>
       </c>
       <c r="D154">
-        <v>3207</v>
+        <v>3215</v>
       </c>
       <c r="E154">
         <v>0</v>
       </c>
       <c r="F154">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -10838,16 +10838,16 @@
         <v>0</v>
       </c>
       <c r="K154">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L154">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="M154">
         <v>0</v>
       </c>
       <c r="N154">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O154">
         <v>0</v>
@@ -10856,10 +10856,10 @@
         <v>0</v>
       </c>
       <c r="Q154">
-        <v>1345</v>
+        <v>1466</v>
       </c>
       <c r="R154">
-        <v>1075</v>
+        <v>1171</v>
       </c>
       <c r="S154">
         <v>0</v>
@@ -10959,13 +10959,13 @@
         <v>FORM8</v>
       </c>
       <c r="D156">
-        <v>1236</v>
+        <v>1245</v>
       </c>
       <c r="E156">
         <v>0</v>
       </c>
       <c r="F156">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -10974,13 +10974,13 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J156">
         <v>0</v>
       </c>
       <c r="K156">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -10998,10 +10998,10 @@
         <v>0</v>
       </c>
       <c r="Q156">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="R156">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="S156">
         <v>0</v>
@@ -11024,13 +11024,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D157">
-        <v>7409</v>
+        <v>7426</v>
       </c>
       <c r="E157">
         <v>0</v>
       </c>
       <c r="F157">
-        <v>612</v>
+        <v>625</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -11039,22 +11039,22 @@
         <v>89</v>
       </c>
       <c r="I157">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J157">
         <v>0</v>
       </c>
       <c r="K157">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L157">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="M157">
         <v>0</v>
       </c>
       <c r="N157">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O157">
         <v>0</v>
@@ -11063,10 +11063,10 @@
         <v>0</v>
       </c>
       <c r="Q157">
-        <v>3440</v>
+        <v>3573</v>
       </c>
       <c r="R157">
-        <v>1885</v>
+        <v>1982</v>
       </c>
       <c r="S157">
         <v>0</v>
@@ -11095,13 +11095,13 @@
         <v>FORM6</v>
       </c>
       <c r="D158">
-        <v>1992</v>
+        <v>2000</v>
       </c>
       <c r="E158">
         <v>0</v>
       </c>
       <c r="F158">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -11237,13 +11237,13 @@
         <v>FORM8</v>
       </c>
       <c r="D160">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="E160">
         <v>0</v>
       </c>
       <c r="F160">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G160">
         <v>13</v>
@@ -11302,13 +11302,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D161">
-        <v>6850</v>
+        <v>6860</v>
       </c>
       <c r="E161">
         <v>0</v>
       </c>
       <c r="F161">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="G161">
         <v>14</v>
@@ -11373,13 +11373,13 @@
         <v>FORM6</v>
       </c>
       <c r="D162">
-        <v>3612</v>
+        <v>3623</v>
       </c>
       <c r="E162">
         <v>0</v>
       </c>
       <c r="F162">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="G162">
         <v>0</v>
@@ -11397,7 +11397,7 @@
         <v>0</v>
       </c>
       <c r="L162">
-        <v>1483</v>
+        <v>866</v>
       </c>
       <c r="M162">
         <v>34</v>
@@ -11412,10 +11412,10 @@
         <v>0</v>
       </c>
       <c r="Q162">
-        <v>194</v>
+        <v>505</v>
       </c>
       <c r="R162">
-        <v>1373</v>
+        <v>1679</v>
       </c>
       <c r="S162">
         <v>0</v>
@@ -11515,13 +11515,13 @@
         <v>FORM8</v>
       </c>
       <c r="D164">
-        <v>1019</v>
+        <v>1028</v>
       </c>
       <c r="E164">
         <v>0</v>
       </c>
       <c r="F164">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -11580,13 +11580,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D165">
-        <v>8876</v>
+        <v>8896</v>
       </c>
       <c r="E165">
         <v>0</v>
       </c>
       <c r="F165">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="G165">
         <v>7</v>
@@ -11604,7 +11604,7 @@
         <v>57</v>
       </c>
       <c r="L165">
-        <v>1555</v>
+        <v>938</v>
       </c>
       <c r="M165">
         <v>34</v>
@@ -11619,10 +11619,10 @@
         <v>0</v>
       </c>
       <c r="Q165">
-        <v>2377</v>
+        <v>2688</v>
       </c>
       <c r="R165">
-        <v>1890</v>
+        <v>2196</v>
       </c>
       <c r="S165">
         <v>0</v>
@@ -11651,13 +11651,13 @@
         <v>FORM6</v>
       </c>
       <c r="D166">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="E166">
         <v>0</v>
       </c>
       <c r="F166">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G166">
         <v>40</v>
@@ -11858,13 +11858,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D169">
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="E169">
         <v>0</v>
       </c>
       <c r="F169">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G169">
         <v>40</v>
@@ -11929,13 +11929,13 @@
         <v>FORM6</v>
       </c>
       <c r="D170">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E170">
         <v>0</v>
       </c>
       <c r="F170">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G170">
         <v>5</v>
@@ -12142,13 +12142,13 @@
         <v>FORM8</v>
       </c>
       <c r="D173">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E173">
         <v>0</v>
       </c>
       <c r="F173">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G173">
         <v>5</v>
@@ -12207,13 +12207,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D174">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="E174">
         <v>0</v>
       </c>
       <c r="F174">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G174">
         <v>10</v>
@@ -12278,16 +12278,16 @@
         <v>FORM6</v>
       </c>
       <c r="D175">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="E175">
         <v>0</v>
       </c>
       <c r="F175">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G175">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -12296,7 +12296,7 @@
         <v>0</v>
       </c>
       <c r="J175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K175">
         <v>0</v>
@@ -12420,13 +12420,13 @@
         <v>FORM8</v>
       </c>
       <c r="D177">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E177">
         <v>0</v>
       </c>
       <c r="F177">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G177">
         <v>3</v>
@@ -12485,16 +12485,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D178">
-        <v>3487</v>
+        <v>3491</v>
       </c>
       <c r="E178">
         <v>0</v>
       </c>
       <c r="F178">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G178">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H178">
         <v>0</v>
@@ -12503,7 +12503,7 @@
         <v>0</v>
       </c>
       <c r="J178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K178">
         <v>0</v>
@@ -12556,13 +12556,13 @@
         <v>FORM6</v>
       </c>
       <c r="D179">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E179">
         <v>0</v>
       </c>
       <c r="F179">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G179">
         <v>0</v>
@@ -12763,13 +12763,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D182">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E182">
         <v>0</v>
       </c>
       <c r="F182">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G182">
         <v>22</v>
@@ -12997,7 +12997,7 @@
         <v>0</v>
       </c>
       <c r="K185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L185">
         <v>0</v>
@@ -13018,7 +13018,7 @@
         <v>37</v>
       </c>
       <c r="R185">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -13062,7 +13062,7 @@
         <v>0</v>
       </c>
       <c r="K186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L186">
         <v>0</v>
@@ -13083,7 +13083,7 @@
         <v>333</v>
       </c>
       <c r="R186">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -13112,13 +13112,13 @@
         <v>FORM6</v>
       </c>
       <c r="D187">
-        <v>2686</v>
+        <v>2687</v>
       </c>
       <c r="E187">
         <v>0</v>
       </c>
       <c r="F187">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G187">
         <v>0</v>
@@ -13133,7 +13133,7 @@
         <v>0</v>
       </c>
       <c r="K187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L187">
         <v>0</v>
@@ -13151,7 +13151,7 @@
         <v>0</v>
       </c>
       <c r="Q187">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="R187">
         <v>2187</v>
@@ -13254,7 +13254,7 @@
         <v>FORM7</v>
       </c>
       <c r="D189">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -13275,7 +13275,7 @@
         <v>0</v>
       </c>
       <c r="K189">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L189">
         <v>0</v>
@@ -13293,7 +13293,7 @@
         <v>0</v>
       </c>
       <c r="Q189">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="R189">
         <v>108</v>
@@ -13311,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="W189">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="190">
@@ -13325,13 +13325,13 @@
         <v>FORM8</v>
       </c>
       <c r="D190">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="E190">
         <v>0</v>
       </c>
       <c r="F190">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G190">
         <v>0</v>
@@ -13346,7 +13346,7 @@
         <v>0</v>
       </c>
       <c r="K190">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L190">
         <v>0</v>
@@ -13364,7 +13364,7 @@
         <v>0</v>
       </c>
       <c r="Q190">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="R190">
         <v>716</v>
@@ -13390,13 +13390,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D191">
-        <v>4812</v>
+        <v>4818</v>
       </c>
       <c r="E191">
         <v>0</v>
       </c>
       <c r="F191">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G191">
         <v>0</v>
@@ -13411,7 +13411,7 @@
         <v>0</v>
       </c>
       <c r="K191">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L191">
         <v>0</v>
@@ -13429,7 +13429,7 @@
         <v>0</v>
       </c>
       <c r="Q191">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="R191">
         <v>3011</v>
@@ -13447,7 +13447,7 @@
         <v>0</v>
       </c>
       <c r="W191">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="192">
@@ -13461,13 +13461,13 @@
         <v>FORM6</v>
       </c>
       <c r="D192">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="E192">
         <v>0</v>
       </c>
       <c r="F192">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G192">
         <v>0</v>
@@ -13603,13 +13603,13 @@
         <v>FORM8</v>
       </c>
       <c r="D194">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E194">
         <v>0</v>
       </c>
       <c r="F194">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G194">
         <v>0</v>
@@ -13668,13 +13668,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D195">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="E195">
         <v>0</v>
       </c>
       <c r="F195">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G195">
         <v>0</v>
@@ -13881,13 +13881,13 @@
         <v>FORM8</v>
       </c>
       <c r="D198">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E198">
         <v>0</v>
       </c>
       <c r="F198">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G198">
         <v>0</v>
@@ -13946,13 +13946,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D199">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="E199">
         <v>0</v>
       </c>
       <c r="F199">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G199">
         <v>0</v>
@@ -14017,13 +14017,13 @@
         <v>FORM6</v>
       </c>
       <c r="D200">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="E200">
         <v>0</v>
       </c>
       <c r="F200">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G200">
         <v>0</v>
@@ -14230,13 +14230,13 @@
         <v>FORM8</v>
       </c>
       <c r="D203">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E203">
         <v>0</v>
       </c>
       <c r="F203">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G203">
         <v>0</v>
@@ -14295,13 +14295,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D204">
-        <v>3023</v>
+        <v>3027</v>
       </c>
       <c r="E204">
         <v>0</v>
       </c>
       <c r="F204">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G204">
         <v>0</v>
@@ -14366,13 +14366,13 @@
         <v>FORM6</v>
       </c>
       <c r="D205">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E205">
         <v>0</v>
       </c>
       <c r="F205">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G205">
         <v>0</v>
@@ -14508,13 +14508,13 @@
         <v>FORM8</v>
       </c>
       <c r="D207">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E207">
         <v>0</v>
       </c>
       <c r="F207">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G207">
         <v>0</v>
@@ -14573,13 +14573,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D208">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="E208">
         <v>0</v>
       </c>
       <c r="F208">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G208">
         <v>0</v>
@@ -14922,13 +14922,13 @@
         <v>FORM6</v>
       </c>
       <c r="D213">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="E213">
         <v>0</v>
       </c>
       <c r="F213">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G213">
         <v>3</v>
@@ -15129,13 +15129,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D216">
-        <v>3634</v>
+        <v>3635</v>
       </c>
       <c r="E216">
         <v>0</v>
       </c>
       <c r="F216">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G216">
         <v>5</v>
@@ -15200,13 +15200,13 @@
         <v>FORM6</v>
       </c>
       <c r="D217">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="E217">
         <v>0</v>
       </c>
       <c r="F217">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G217">
         <v>1</v>
@@ -15342,13 +15342,13 @@
         <v>FORM8</v>
       </c>
       <c r="D219">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E219">
         <v>0</v>
       </c>
       <c r="F219">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G219">
         <v>1</v>
@@ -15407,13 +15407,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D220">
-        <v>1889</v>
+        <v>1896</v>
       </c>
       <c r="E220">
         <v>0</v>
       </c>
       <c r="F220">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G220">
         <v>6</v>
@@ -15827,13 +15827,13 @@
         <v>FORM6</v>
       </c>
       <c r="D226">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="E226">
         <v>0</v>
       </c>
       <c r="F226">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G226">
         <v>26</v>
@@ -16040,13 +16040,13 @@
         <v>FORM8</v>
       </c>
       <c r="D229">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E229">
         <v>0</v>
       </c>
       <c r="F229">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G229">
         <v>8</v>
@@ -16105,13 +16105,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D230">
-        <v>2448</v>
+        <v>2451</v>
       </c>
       <c r="E230">
         <v>0</v>
       </c>
       <c r="F230">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G230">
         <v>36</v>
@@ -16176,13 +16176,13 @@
         <v>FORM6</v>
       </c>
       <c r="D231">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="E231">
         <v>0</v>
       </c>
       <c r="F231">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G231">
         <v>6</v>
@@ -16318,13 +16318,13 @@
         <v>FORM8</v>
       </c>
       <c r="D233">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E233">
         <v>0</v>
       </c>
       <c r="F233">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G233">
         <v>3</v>
@@ -16383,13 +16383,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D234">
-        <v>1831</v>
+        <v>1835</v>
       </c>
       <c r="E234">
         <v>0</v>
       </c>
       <c r="F234">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G234">
         <v>11</v>
@@ -16667,13 +16667,13 @@
         <v>FORM8</v>
       </c>
       <c r="D238">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E238">
         <v>0</v>
       </c>
       <c r="F238">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G238">
         <v>0</v>
@@ -16732,13 +16732,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D239">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="E239">
         <v>0</v>
       </c>
       <c r="F239">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G239">
         <v>0</v>
@@ -16803,13 +16803,13 @@
         <v>FORM6</v>
       </c>
       <c r="D240">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E240">
         <v>0</v>
       </c>
       <c r="F240">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G240">
         <v>1</v>
@@ -16945,13 +16945,13 @@
         <v>FORM8</v>
       </c>
       <c r="D242">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E242">
         <v>0</v>
       </c>
       <c r="F242">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G242">
         <v>0</v>
@@ -17010,13 +17010,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D243">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="E243">
         <v>0</v>
       </c>
       <c r="F243">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G243">
         <v>1</v>
@@ -17223,13 +17223,13 @@
         <v>FORM8</v>
       </c>
       <c r="D246">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E246">
         <v>0</v>
       </c>
       <c r="F246">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G246">
         <v>0</v>
@@ -17288,13 +17288,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D247">
-        <v>3036</v>
+        <v>3039</v>
       </c>
       <c r="E247">
         <v>0</v>
       </c>
       <c r="F247">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G247">
         <v>0</v>
@@ -17359,13 +17359,13 @@
         <v>FORM6</v>
       </c>
       <c r="D248">
-        <v>1723</v>
+        <v>1726</v>
       </c>
       <c r="E248">
         <v>0</v>
       </c>
       <c r="F248">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G248">
         <v>0</v>
@@ -17501,13 +17501,13 @@
         <v>FORM8</v>
       </c>
       <c r="D250">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E250">
         <v>0</v>
       </c>
       <c r="F250">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G250">
         <v>0</v>
@@ -17566,13 +17566,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D251">
-        <v>3695</v>
+        <v>3699</v>
       </c>
       <c r="E251">
         <v>0</v>
       </c>
       <c r="F251">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G251">
         <v>0</v>
@@ -17637,13 +17637,13 @@
         <v>FORM6</v>
       </c>
       <c r="D252">
-        <v>2093</v>
+        <v>2103</v>
       </c>
       <c r="E252">
         <v>0</v>
       </c>
       <c r="F252">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="G252">
         <v>0</v>
@@ -17779,13 +17779,13 @@
         <v>FORM8</v>
       </c>
       <c r="D254">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="E254">
         <v>0</v>
       </c>
       <c r="F254">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G254">
         <v>0</v>
@@ -17844,13 +17844,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D255">
-        <v>6394</v>
+        <v>6413</v>
       </c>
       <c r="E255">
         <v>0</v>
       </c>
       <c r="F255">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="G255">
         <v>0</v>
@@ -18057,13 +18057,13 @@
         <v>FORM8</v>
       </c>
       <c r="D258">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E258">
         <v>0</v>
       </c>
       <c r="F258">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G258">
         <v>0</v>
@@ -18122,13 +18122,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D259">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="E259">
         <v>0</v>
       </c>
       <c r="F259">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G259">
         <v>0</v>
@@ -18193,13 +18193,13 @@
         <v>FORM6</v>
       </c>
       <c r="D260">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E260">
         <v>0</v>
       </c>
       <c r="F260">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G260">
         <v>0</v>
@@ -18406,13 +18406,13 @@
         <v>FORM8</v>
       </c>
       <c r="D263">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E263">
         <v>0</v>
       </c>
       <c r="F263">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G263">
         <v>0</v>
@@ -18471,13 +18471,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D264">
-        <v>2212</v>
+        <v>2216</v>
       </c>
       <c r="E264">
         <v>0</v>
       </c>
       <c r="F264">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G264">
         <v>0</v>
@@ -18542,13 +18542,13 @@
         <v>FORM6</v>
       </c>
       <c r="D265">
-        <v>5561</v>
+        <v>5571</v>
       </c>
       <c r="E265">
         <v>0</v>
       </c>
       <c r="F265">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="G265">
         <v>0</v>
@@ -18572,7 +18572,7 @@
         <v>0</v>
       </c>
       <c r="N265">
-        <v>627</v>
+        <v>662</v>
       </c>
       <c r="O265">
         <v>0</v>
@@ -18584,7 +18584,7 @@
         <v>858</v>
       </c>
       <c r="R265">
-        <v>3370</v>
+        <v>3335</v>
       </c>
       <c r="S265">
         <v>0</v>
@@ -18714,7 +18714,7 @@
         <v>0</v>
       </c>
       <c r="N267">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O267">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>7156</v>
       </c>
       <c r="R267">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="S267">
         <v>0</v>
@@ -18755,13 +18755,13 @@
         <v>FORM8</v>
       </c>
       <c r="D268">
-        <v>2466</v>
+        <v>2474</v>
       </c>
       <c r="E268">
         <v>0</v>
       </c>
       <c r="F268">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G268">
         <v>0</v>
@@ -18820,13 +18820,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D269">
-        <v>17319</v>
+        <v>17337</v>
       </c>
       <c r="E269">
         <v>0</v>
       </c>
       <c r="F269">
-        <v>725</v>
+        <v>743</v>
       </c>
       <c r="G269">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>0</v>
       </c>
       <c r="N269">
-        <v>811</v>
+        <v>848</v>
       </c>
       <c r="O269">
         <v>0</v>
@@ -18862,7 +18862,7 @@
         <v>8151</v>
       </c>
       <c r="R269">
-        <v>4799</v>
+        <v>4762</v>
       </c>
       <c r="S269">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         <v>FORM6</v>
       </c>
       <c r="D270">
-        <v>4837</v>
+        <v>4855</v>
       </c>
       <c r="E270">
         <v>0</v>
       </c>
       <c r="F270">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="G270">
         <v>0</v>
@@ -19104,13 +19104,13 @@
         <v>FORM8</v>
       </c>
       <c r="D273">
-        <v>1988</v>
+        <v>1996</v>
       </c>
       <c r="E273">
         <v>0</v>
       </c>
       <c r="F273">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G273">
         <v>0</v>
@@ -19169,13 +19169,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D274">
-        <v>8819</v>
+        <v>8845</v>
       </c>
       <c r="E274">
         <v>0</v>
       </c>
       <c r="F274">
-        <v>721</v>
+        <v>747</v>
       </c>
       <c r="G274">
         <v>0</v>
@@ -19240,13 +19240,13 @@
         <v>FORM6</v>
       </c>
       <c r="D275">
-        <v>2653</v>
+        <v>2661</v>
       </c>
       <c r="E275">
         <v>0</v>
       </c>
       <c r="F275">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="G275">
         <v>0</v>
@@ -19264,7 +19264,7 @@
         <v>0</v>
       </c>
       <c r="L275">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M275">
         <v>0</v>
@@ -19279,10 +19279,10 @@
         <v>0</v>
       </c>
       <c r="Q275">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="R275">
-        <v>1605</v>
+        <v>1613</v>
       </c>
       <c r="S275">
         <v>0</v>
@@ -19453,13 +19453,13 @@
         <v>FORM8</v>
       </c>
       <c r="D278">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="E278">
         <v>0</v>
       </c>
       <c r="F278">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G278">
         <v>0</v>
@@ -19518,13 +19518,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D279">
-        <v>6069</v>
+        <v>6081</v>
       </c>
       <c r="E279">
         <v>0</v>
       </c>
       <c r="F279">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="G279">
         <v>0</v>
@@ -19542,7 +19542,7 @@
         <v>0</v>
       </c>
       <c r="L279">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M279">
         <v>0</v>
@@ -19557,10 +19557,10 @@
         <v>0</v>
       </c>
       <c r="Q279">
-        <v>1888</v>
+        <v>1894</v>
       </c>
       <c r="R279">
-        <v>2118</v>
+        <v>2126</v>
       </c>
       <c r="S279">
         <v>0</v>
@@ -19589,16 +19589,16 @@
         <v>FORM6</v>
       </c>
       <c r="D280">
-        <v>3655</v>
+        <v>3666</v>
       </c>
       <c r="E280">
         <v>0</v>
       </c>
       <c r="F280">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="G280">
-        <v>241</v>
+        <v>110</v>
       </c>
       <c r="H280">
         <v>0</v>
@@ -19607,19 +19607,19 @@
         <v>0</v>
       </c>
       <c r="J280">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K280">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="L280">
         <v>0</v>
       </c>
       <c r="M280">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N280">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="O280">
         <v>0</v>
@@ -19628,19 +19628,19 @@
         <v>0</v>
       </c>
       <c r="Q280">
-        <v>917</v>
+        <v>931</v>
       </c>
       <c r="R280">
-        <v>1732</v>
+        <v>1873</v>
       </c>
       <c r="S280">
+        <v>0</v>
+      </c>
+      <c r="T280">
+        <v>0</v>
+      </c>
+      <c r="U280">
         <v>2</v>
-      </c>
-      <c r="T280">
-        <v>0</v>
-      </c>
-      <c r="U280">
-        <v>0</v>
       </c>
       <c r="V280">
         <v>0</v>
@@ -19731,7 +19731,7 @@
         <v>FORM7</v>
       </c>
       <c r="D282">
-        <v>8032</v>
+        <v>8082</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -19755,7 +19755,7 @@
         <v>13</v>
       </c>
       <c r="L282">
-        <v>2486</v>
+        <v>1483</v>
       </c>
       <c r="M282">
         <v>0</v>
@@ -19770,10 +19770,10 @@
         <v>0</v>
       </c>
       <c r="Q282">
-        <v>1249</v>
+        <v>2184</v>
       </c>
       <c r="R282">
-        <v>138</v>
+        <v>256</v>
       </c>
       <c r="S282">
         <v>0</v>
@@ -19802,16 +19802,16 @@
         <v>FORM8</v>
       </c>
       <c r="D283">
-        <v>1486</v>
+        <v>1494</v>
       </c>
       <c r="E283">
         <v>0</v>
       </c>
       <c r="F283">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G283">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H283">
         <v>0</v>
@@ -19823,7 +19823,7 @@
         <v>0</v>
       </c>
       <c r="K283">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L283">
         <v>0</v>
@@ -19832,7 +19832,7 @@
         <v>0</v>
       </c>
       <c r="N283">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O283">
         <v>0</v>
@@ -19844,7 +19844,7 @@
         <v>177</v>
       </c>
       <c r="R283">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="S283">
         <v>0</v>
@@ -19867,16 +19867,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D284">
-        <v>13186</v>
+        <v>13255</v>
       </c>
       <c r="E284">
         <v>0</v>
       </c>
       <c r="F284">
-        <v>3457</v>
+        <v>3473</v>
       </c>
       <c r="G284">
-        <v>268</v>
+        <v>130</v>
       </c>
       <c r="H284">
         <v>0</v>
@@ -19885,19 +19885,19 @@
         <v>193</v>
       </c>
       <c r="J284">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K284">
         <v>117</v>
       </c>
       <c r="L284">
-        <v>2486</v>
+        <v>1483</v>
       </c>
       <c r="M284">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N284">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="O284">
         <v>0</v>
@@ -19906,19 +19906,19 @@
         <v>0</v>
       </c>
       <c r="Q284">
-        <v>2351</v>
+        <v>3300</v>
       </c>
       <c r="R284">
-        <v>2982</v>
+        <v>3248</v>
       </c>
       <c r="S284">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T284">
         <v>0</v>
       </c>
       <c r="U284">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V284">
         <v>0</v>
@@ -19938,13 +19938,13 @@
         <v>FORM6</v>
       </c>
       <c r="D285">
-        <v>5871</v>
+        <v>5906</v>
       </c>
       <c r="E285">
         <v>0</v>
       </c>
       <c r="F285">
-        <v>1007</v>
+        <v>1042</v>
       </c>
       <c r="G285">
         <v>0</v>
@@ -19962,7 +19962,7 @@
         <v>0</v>
       </c>
       <c r="L285">
-        <v>896</v>
+        <v>468</v>
       </c>
       <c r="M285">
         <v>0</v>
@@ -19977,10 +19977,10 @@
         <v>0</v>
       </c>
       <c r="Q285">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="R285">
-        <v>3887</v>
+        <v>4180</v>
       </c>
       <c r="S285">
         <v>0</v>
@@ -20151,13 +20151,13 @@
         <v>FORM8</v>
       </c>
       <c r="D288">
-        <v>2157</v>
+        <v>2165</v>
       </c>
       <c r="E288">
         <v>0</v>
       </c>
       <c r="F288">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G288">
         <v>0</v>
@@ -20216,13 +20216,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D289">
-        <v>17977</v>
+        <v>18020</v>
       </c>
       <c r="E289">
         <v>0</v>
       </c>
       <c r="F289">
-        <v>1176</v>
+        <v>1219</v>
       </c>
       <c r="G289">
         <v>0</v>
@@ -20240,7 +20240,7 @@
         <v>0</v>
       </c>
       <c r="L289">
-        <v>896</v>
+        <v>468</v>
       </c>
       <c r="M289">
         <v>0</v>
@@ -20255,10 +20255,10 @@
         <v>0</v>
       </c>
       <c r="Q289">
-        <v>7189</v>
+        <v>7324</v>
       </c>
       <c r="R289">
-        <v>5620</v>
+        <v>5913</v>
       </c>
       <c r="S289">
         <v>0</v>
@@ -20287,13 +20287,13 @@
         <v>FORM6</v>
       </c>
       <c r="D290">
-        <v>3419</v>
+        <v>3437</v>
       </c>
       <c r="E290">
         <v>0</v>
       </c>
       <c r="F290">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="G290">
         <v>0</v>
@@ -20500,13 +20500,13 @@
         <v>FORM8</v>
       </c>
       <c r="D293">
-        <v>1269</v>
+        <v>1279</v>
       </c>
       <c r="E293">
         <v>0</v>
       </c>
       <c r="F293">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="G293">
         <v>0</v>
@@ -20565,13 +20565,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D294">
-        <v>11016</v>
+        <v>11044</v>
       </c>
       <c r="E294">
         <v>0</v>
       </c>
       <c r="F294">
-        <v>642</v>
+        <v>670</v>
       </c>
       <c r="G294">
         <v>0</v>
@@ -20636,13 +20636,13 @@
         <v>FORM6</v>
       </c>
       <c r="D295">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="E295">
         <v>0</v>
       </c>
       <c r="F295">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="G295">
         <v>0</v>
@@ -20654,19 +20654,19 @@
         <v>0</v>
       </c>
       <c r="J295">
+        <v>0</v>
+      </c>
+      <c r="K295">
+        <v>0</v>
+      </c>
+      <c r="L295">
+        <v>0</v>
+      </c>
+      <c r="M295">
+        <v>0</v>
+      </c>
+      <c r="N295">
         <v>1</v>
-      </c>
-      <c r="K295">
-        <v>0</v>
-      </c>
-      <c r="L295">
-        <v>0</v>
-      </c>
-      <c r="M295">
-        <v>0</v>
-      </c>
-      <c r="N295">
-        <v>0</v>
       </c>
       <c r="O295">
         <v>0</v>
@@ -20707,7 +20707,7 @@
         <v>FORM7</v>
       </c>
       <c r="D296">
-        <v>6997</v>
+        <v>8784</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -20764,7 +20764,7 @@
         <v>0</v>
       </c>
       <c r="W296">
-        <v>1567</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="297">
@@ -20778,13 +20778,13 @@
         <v>FORM8</v>
       </c>
       <c r="D297">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="E297">
         <v>0</v>
       </c>
       <c r="F297">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="G297">
         <v>0</v>
@@ -20843,13 +20843,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D298">
-        <v>9306</v>
+        <v>11106</v>
       </c>
       <c r="E298">
         <v>0</v>
       </c>
       <c r="F298">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="G298">
         <v>0</v>
@@ -20861,7 +20861,7 @@
         <v>0</v>
       </c>
       <c r="J298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K298">
         <v>291</v>
@@ -20873,7 +20873,7 @@
         <v>0</v>
       </c>
       <c r="N298">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O298">
         <v>0</v>
@@ -20900,7 +20900,7 @@
         <v>0</v>
       </c>
       <c r="W298">
-        <v>1567</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="299">
@@ -20914,13 +20914,13 @@
         <v>FORM6</v>
       </c>
       <c r="D299">
-        <v>2967</v>
+        <v>2972</v>
       </c>
       <c r="E299">
         <v>0</v>
       </c>
       <c r="F299">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G299">
         <v>0</v>
@@ -21080,7 +21080,7 @@
         <v>120</v>
       </c>
       <c r="L301">
-        <v>2902</v>
+        <v>1791</v>
       </c>
       <c r="M301">
         <v>0</v>
@@ -21095,10 +21095,10 @@
         <v>0</v>
       </c>
       <c r="Q301">
-        <v>3955</v>
+        <v>4932</v>
       </c>
       <c r="R301">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="S301">
         <v>0</v>
@@ -21127,13 +21127,13 @@
         <v>FORM8</v>
       </c>
       <c r="D302">
-        <v>1434</v>
+        <v>1441</v>
       </c>
       <c r="E302">
         <v>0</v>
       </c>
       <c r="F302">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="G302">
         <v>0</v>
@@ -21192,13 +21192,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D303">
-        <v>13004</v>
+        <v>13016</v>
       </c>
       <c r="E303">
         <v>0</v>
       </c>
       <c r="F303">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="G303">
         <v>0</v>
@@ -21216,7 +21216,7 @@
         <v>120</v>
       </c>
       <c r="L303">
-        <v>2902</v>
+        <v>1791</v>
       </c>
       <c r="M303">
         <v>0</v>
@@ -21231,10 +21231,10 @@
         <v>0</v>
       </c>
       <c r="Q303">
-        <v>4101</v>
+        <v>5078</v>
       </c>
       <c r="R303">
-        <v>3734</v>
+        <v>3868</v>
       </c>
       <c r="S303">
         <v>0</v>
@@ -21263,13 +21263,13 @@
         <v>FORM6</v>
       </c>
       <c r="D304">
-        <v>1782</v>
+        <v>1791</v>
       </c>
       <c r="E304">
         <v>0</v>
       </c>
       <c r="F304">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="G304">
         <v>0</v>
@@ -21296,7 +21296,7 @@
         <v>0</v>
       </c>
       <c r="O304">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P304">
         <v>0</v>
@@ -21305,7 +21305,7 @@
         <v>14</v>
       </c>
       <c r="R304">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="S304">
         <v>0</v>
@@ -21405,13 +21405,13 @@
         <v>FORM8</v>
       </c>
       <c r="D306">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="E306">
         <v>0</v>
       </c>
       <c r="F306">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G306">
         <v>0</v>
@@ -21470,13 +21470,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D307">
-        <v>17315</v>
+        <v>17332</v>
       </c>
       <c r="E307">
         <v>0</v>
       </c>
       <c r="F307">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -21503,7 +21503,7 @@
         <v>2</v>
       </c>
       <c r="O307">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P307">
         <v>0</v>
@@ -21512,7 +21512,7 @@
         <v>3233</v>
       </c>
       <c r="R307">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="S307">
         <v>0</v>
@@ -21541,13 +21541,13 @@
         <v>FORM6</v>
       </c>
       <c r="D308">
-        <v>2414</v>
+        <v>2423</v>
       </c>
       <c r="E308">
         <v>0</v>
       </c>
       <c r="F308">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="G308">
         <v>0</v>
@@ -21683,13 +21683,13 @@
         <v>FORM8</v>
       </c>
       <c r="D310">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="E310">
         <v>0</v>
       </c>
       <c r="F310">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G310">
         <v>0</v>
@@ -21748,13 +21748,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D311">
-        <v>6666</v>
+        <v>6682</v>
       </c>
       <c r="E311">
         <v>0</v>
       </c>
       <c r="F311">
-        <v>535</v>
+        <v>551</v>
       </c>
       <c r="G311">
         <v>0</v>
@@ -21819,13 +21819,13 @@
         <v>FORM6</v>
       </c>
       <c r="D312">
-        <v>1708</v>
+        <v>1716</v>
       </c>
       <c r="E312">
         <v>0</v>
       </c>
       <c r="F312">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G312">
         <v>0</v>
@@ -21961,13 +21961,13 @@
         <v>FORM8</v>
       </c>
       <c r="D314">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="E314">
         <v>0</v>
       </c>
       <c r="F314">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G314">
         <v>0</v>
@@ -22026,13 +22026,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D315">
-        <v>5616</v>
+        <v>5626</v>
       </c>
       <c r="E315">
         <v>0</v>
       </c>
       <c r="F315">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G315">
         <v>0</v>
@@ -22097,16 +22097,16 @@
         <v>FORM6</v>
       </c>
       <c r="D316">
-        <v>1343</v>
+        <v>1355</v>
       </c>
       <c r="E316">
         <v>0</v>
       </c>
       <c r="F316">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G316">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="H316">
         <v>0</v>
@@ -22115,7 +22115,7 @@
         <v>0</v>
       </c>
       <c r="J316">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K316">
         <v>0</v>
@@ -22127,7 +22127,7 @@
         <v>0</v>
       </c>
       <c r="N316">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O316">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>4</v>
       </c>
       <c r="R316">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="S316">
         <v>0</v>
@@ -22310,13 +22310,13 @@
         <v>FORM8</v>
       </c>
       <c r="D319">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="E319">
         <v>0</v>
       </c>
       <c r="F319">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G319">
         <v>18</v>
@@ -22375,16 +22375,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D320">
-        <v>4391</v>
+        <v>4406</v>
       </c>
       <c r="E320">
         <v>0</v>
       </c>
       <c r="F320">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="G320">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H320">
         <v>0</v>
@@ -22393,7 +22393,7 @@
         <v>0</v>
       </c>
       <c r="J320">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K320">
         <v>0</v>
@@ -22405,7 +22405,7 @@
         <v>0</v>
       </c>
       <c r="N320">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O320">
         <v>0</v>
@@ -22417,7 +22417,7 @@
         <v>789</v>
       </c>
       <c r="R320">
-        <v>1610</v>
+        <v>1616</v>
       </c>
       <c r="S320">
         <v>0</v>
@@ -22440,58 +22440,58 @@
         <v>All AC Form-6 Total</v>
       </c>
       <c r="D321">
-        <v>164625</v>
+        <v>164964</v>
       </c>
       <c r="E321">
         <v>0</v>
       </c>
       <c r="F321">
-        <v>13574</v>
+        <v>13911</v>
       </c>
       <c r="G321">
-        <v>906</v>
+        <v>567</v>
       </c>
       <c r="H321">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I321">
         <v>1</v>
       </c>
       <c r="J321">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="K321">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L321">
-        <v>3409</v>
+        <v>1843</v>
       </c>
       <c r="M321">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="N321">
-        <v>7519</v>
+        <v>7785</v>
       </c>
       <c r="O321">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P321">
         <v>0</v>
       </c>
       <c r="Q321">
-        <v>15128</v>
+        <v>15815</v>
       </c>
       <c r="R321">
-        <v>102372</v>
+        <v>103391</v>
       </c>
       <c r="S321">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T321">
         <v>0</v>
       </c>
       <c r="U321">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V321">
         <v>0</v>
@@ -22570,7 +22570,7 @@
         <v>All AC Form-7 Total</v>
       </c>
       <c r="D323">
-        <v>158146</v>
+        <v>166500</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -22591,16 +22591,16 @@
         <v>0</v>
       </c>
       <c r="K323">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="L323">
-        <v>11125</v>
+        <v>9009</v>
       </c>
       <c r="M323">
         <v>1</v>
       </c>
       <c r="N323">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O323">
         <v>0</v>
@@ -22609,10 +22609,10 @@
         <v>0</v>
       </c>
       <c r="Q323">
-        <v>72036</v>
+        <v>73947</v>
       </c>
       <c r="R323">
-        <v>5708</v>
+        <v>5958</v>
       </c>
       <c r="S323">
         <v>0</v>
@@ -22627,7 +22627,7 @@
         <v>0</v>
       </c>
       <c r="W323">
-        <v>61940</v>
+        <v>70242</v>
       </c>
     </row>
     <row r="324">
@@ -22635,28 +22635,28 @@
         <v>All AC Form-8 Total</v>
       </c>
       <c r="D324">
-        <v>62469</v>
+        <v>62685</v>
       </c>
       <c r="E324">
         <v>0</v>
       </c>
       <c r="F324">
-        <v>6378</v>
+        <v>6587</v>
       </c>
       <c r="G324">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H324">
         <v>0</v>
       </c>
       <c r="I324">
+        <v>0</v>
+      </c>
+      <c r="J324">
         <v>8</v>
       </c>
-      <c r="J324">
-        <v>7</v>
-      </c>
       <c r="K324">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L324">
         <v>10</v>
@@ -22665,7 +22665,7 @@
         <v>1</v>
       </c>
       <c r="N324">
-        <v>1533</v>
+        <v>1521</v>
       </c>
       <c r="O324">
         <v>2</v>
@@ -22674,19 +22674,19 @@
         <v>0</v>
       </c>
       <c r="Q324">
-        <v>5329</v>
+        <v>5337</v>
       </c>
       <c r="R324">
-        <v>35444</v>
+        <v>35450</v>
       </c>
       <c r="S324">
+        <v>0</v>
+      </c>
+      <c r="T324">
+        <v>0</v>
+      </c>
+      <c r="U324">
         <v>2</v>
-      </c>
-      <c r="T324">
-        <v>0</v>
-      </c>
-      <c r="U324">
-        <v>0</v>
       </c>
       <c r="V324">
         <v>0</v>
@@ -22700,64 +22700,64 @@
         <v>All AC Form Total</v>
       </c>
       <c r="D325">
-        <v>385382</v>
+        <v>394291</v>
       </c>
       <c r="E325">
         <v>0</v>
       </c>
       <c r="F325">
-        <v>23067</v>
+        <v>23613</v>
       </c>
       <c r="G325">
-        <v>1353</v>
+        <v>1027</v>
       </c>
       <c r="H325">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="I325">
-        <v>2406</v>
+        <v>2398</v>
       </c>
       <c r="J325">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K325">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="L325">
-        <v>14544</v>
+        <v>10862</v>
       </c>
       <c r="M325">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="N325">
-        <v>9268</v>
+        <v>9524</v>
       </c>
       <c r="O325">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P325">
         <v>0</v>
       </c>
       <c r="Q325">
-        <v>92559</v>
+        <v>95165</v>
       </c>
       <c r="R325">
-        <v>143568</v>
+        <v>144843</v>
       </c>
       <c r="S325">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T325">
         <v>0</v>
       </c>
       <c r="U325">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="V325">
         <v>0</v>
       </c>
       <c r="W325">
-        <v>96780</v>
+        <v>105082</v>
       </c>
     </row>
   </sheetData>

--- a/Form_Processing.xlsx
+++ b/Form_Processing.xlsx
@@ -411,7 +411,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>From - 15/07/2026       To - 22/09/2026</v>
+        <v>From - 15/07/2026       To - 24/09/2026</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R6">
         <v>40</v>
@@ -717,7 +717,7 @@
         <v>27</v>
       </c>
       <c r="G9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -747,7 +747,7 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R9">
         <v>71</v>
@@ -779,13 +779,13 @@
         <v>FORM6</v>
       </c>
       <c r="D10">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -921,13 +921,13 @@
         <v>FORM8</v>
       </c>
       <c r="D12">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -986,13 +986,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D13">
-        <v>1364</v>
+        <v>1369</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1057,13 +1057,13 @@
         <v>FORM6</v>
       </c>
       <c r="D14">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1199,13 +1199,13 @@
         <v>FORM8</v>
       </c>
       <c r="D16">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D17">
-        <v>2750</v>
+        <v>2756</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>FORM7</v>
       </c>
       <c r="D20">
-        <v>837</v>
+        <v>1121</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="W20">
-        <v>97</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21">
@@ -1548,13 +1548,13 @@
         <v>FORM8</v>
       </c>
       <c r="D21">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1569,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1590,7 +1590,7 @@
         <v>15</v>
       </c>
       <c r="R21">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D22">
-        <v>3403</v>
+        <v>3688</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -1634,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1655,7 +1655,7 @@
         <v>635</v>
       </c>
       <c r="R22">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="W22">
-        <v>1543</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="23">
@@ -1684,13 +1684,13 @@
         <v>FORM6</v>
       </c>
       <c r="D23">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1755,7 +1755,7 @@
         <v>FORM7</v>
       </c>
       <c r="D24">
-        <v>507</v>
+        <v>596</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="W24">
-        <v>53</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25">
@@ -1826,13 +1826,13 @@
         <v>FORM8</v>
       </c>
       <c r="D25">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D26">
-        <v>3465</v>
+        <v>3559</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="W26">
-        <v>1974</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="27">
@@ -1962,13 +1962,13 @@
         <v>FORM6</v>
       </c>
       <c r="D27">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -2104,7 +2104,7 @@
         <v>FORM7</v>
       </c>
       <c r="D29">
-        <v>369</v>
+        <v>607</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2161,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="W29">
-        <v>52</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30">
@@ -2175,13 +2175,13 @@
         <v>FORM8</v>
       </c>
       <c r="D30">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -2240,13 +2240,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D31">
-        <v>2264</v>
+        <v>2506</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="W31">
-        <v>1747</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="32">
@@ -2311,13 +2311,13 @@
         <v>FORM6</v>
       </c>
       <c r="D32">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>FORM7</v>
       </c>
       <c r="D34">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="W34">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
@@ -2589,13 +2589,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D36">
-        <v>1387</v>
+        <v>1400</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="W36">
-        <v>576</v>
+        <v>586</v>
       </c>
     </row>
     <row r="37">
@@ -2660,13 +2660,13 @@
         <v>FORM6</v>
       </c>
       <c r="D37">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -2731,7 +2731,7 @@
         <v>FORM7</v>
       </c>
       <c r="D38">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -2773,7 +2773,7 @@
         <v>157</v>
       </c>
       <c r="R38">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="W38">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39">
@@ -2802,13 +2802,13 @@
         <v>FORM8</v>
       </c>
       <c r="D39">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -2867,13 +2867,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D40">
-        <v>1856</v>
+        <v>1890</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2888,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2909,7 +2909,7 @@
         <v>198</v>
       </c>
       <c r="R40">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="W40">
-        <v>908</v>
+        <v>939</v>
       </c>
     </row>
     <row r="41">
@@ -3080,13 +3080,13 @@
         <v>FORM8</v>
       </c>
       <c r="D43">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D44">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>FORM6</v>
       </c>
       <c r="D45">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -3358,13 +3358,13 @@
         <v>FORM8</v>
       </c>
       <c r="D47">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -3379,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R47">
         <v>253</v>
@@ -3423,13 +3423,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D48">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -3444,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -3462,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R48">
         <v>620</v>
@@ -3494,13 +3494,13 @@
         <v>FORM6</v>
       </c>
       <c r="D49">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -3707,13 +3707,13 @@
         <v>FORM8</v>
       </c>
       <c r="D52">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E52">
         <v>0</v>
       </c>
       <c r="F52">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -3772,13 +3772,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D53">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -3843,13 +3843,13 @@
         <v>FORM6</v>
       </c>
       <c r="D54">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
       <c r="F54">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -3985,13 +3985,13 @@
         <v>FORM8</v>
       </c>
       <c r="D56">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -4050,13 +4050,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D57">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="E57">
         <v>0</v>
       </c>
       <c r="F57">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -4334,13 +4334,13 @@
         <v>FORM8</v>
       </c>
       <c r="D61">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="F61">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -4399,13 +4399,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D62">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="E62">
         <v>0</v>
       </c>
       <c r="F62">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -4470,13 +4470,13 @@
         <v>FORM6</v>
       </c>
       <c r="D63">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E63">
         <v>0</v>
       </c>
       <c r="F63">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -4612,7 +4612,7 @@
         <v>FORM7</v>
       </c>
       <c r="D65">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="W65">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66">
@@ -4683,13 +4683,13 @@
         <v>FORM8</v>
       </c>
       <c r="D66">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E66">
         <v>0</v>
       </c>
       <c r="F66">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -4748,13 +4748,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D67">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="E67">
         <v>0</v>
       </c>
       <c r="F67">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -4805,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="W67">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="68">
@@ -4819,13 +4819,13 @@
         <v>FORM6</v>
       </c>
       <c r="D68">
-        <v>2924</v>
+        <v>2928</v>
       </c>
       <c r="E68">
         <v>0</v>
       </c>
       <c r="F68">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -4840,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -4861,7 +4861,7 @@
         <v>79</v>
       </c>
       <c r="R68">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -4961,13 +4961,13 @@
         <v>FORM8</v>
       </c>
       <c r="D70">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D71">
-        <v>4505</v>
+        <v>4511</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -5068,7 +5068,7 @@
         <v>251</v>
       </c>
       <c r="R71">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -5097,13 +5097,13 @@
         <v>FORM6</v>
       </c>
       <c r="D72">
-        <v>3723</v>
+        <v>3725</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G72">
         <v>6</v>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="K74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>1353</v>
       </c>
       <c r="R74">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -5310,13 +5310,13 @@
         <v>FORM8</v>
       </c>
       <c r="D75">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="E75">
         <v>0</v>
       </c>
       <c r="F75">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -5331,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -5352,7 +5352,7 @@
         <v>80</v>
       </c>
       <c r="R75">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -5375,13 +5375,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D76">
-        <v>6631</v>
+        <v>6637</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="G76">
         <v>6</v>
@@ -5396,7 +5396,7 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -5417,7 +5417,7 @@
         <v>1887</v>
       </c>
       <c r="R76">
-        <v>3931</v>
+        <v>3934</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -5446,13 +5446,13 @@
         <v>FORM6</v>
       </c>
       <c r="D77">
-        <v>4816</v>
+        <v>4828</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -5467,16 +5467,16 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L77">
         <v>0</v>
       </c>
       <c r="M77">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N77">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -5588,7 +5588,7 @@
         <v>FORM7</v>
       </c>
       <c r="D79">
-        <v>2059</v>
+        <v>3485</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5645,7 +5645,7 @@
         <v>0</v>
       </c>
       <c r="W79">
-        <v>1111</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="80">
@@ -5659,13 +5659,13 @@
         <v>FORM8</v>
       </c>
       <c r="D80">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="E80">
         <v>0</v>
       </c>
       <c r="F80">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -5724,13 +5724,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D81">
-        <v>8426</v>
+        <v>9868</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="F81">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -5745,16 +5745,16 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81">
         <v>0</v>
       </c>
       <c r="M81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N81">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="W81">
-        <v>1114</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="82">
@@ -5795,13 +5795,13 @@
         <v>FORM6</v>
       </c>
       <c r="D82">
-        <v>9765</v>
+        <v>9810</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82">
-        <v>733</v>
+        <v>778</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -6008,13 +6008,13 @@
         <v>FORM8</v>
       </c>
       <c r="D85">
-        <v>2534</v>
+        <v>2543</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -6073,13 +6073,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D86">
-        <v>16857</v>
+        <v>16911</v>
       </c>
       <c r="E86">
         <v>0</v>
       </c>
       <c r="F86">
-        <v>964</v>
+        <v>1018</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -6144,13 +6144,13 @@
         <v>FORM6</v>
       </c>
       <c r="D87">
-        <v>4934</v>
+        <v>4950</v>
       </c>
       <c r="E87">
         <v>0</v>
       </c>
       <c r="F87">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -6165,7 +6165,7 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -6183,10 +6183,10 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="R87">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -6195,7 +6195,7 @@
         <v>0</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V87">
         <v>0</v>
@@ -6286,7 +6286,7 @@
         <v>FORM7</v>
       </c>
       <c r="D89">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="W89">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90">
@@ -6357,13 +6357,13 @@
         <v>FORM8</v>
       </c>
       <c r="D90">
-        <v>1768</v>
+        <v>1776</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
       <c r="F90">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -6422,13 +6422,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D91">
-        <v>8847</v>
+        <v>8875</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91">
-        <v>778</v>
+        <v>802</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -6443,7 +6443,7 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -6461,10 +6461,10 @@
         <v>0</v>
       </c>
       <c r="Q91">
-        <v>2935</v>
+        <v>2933</v>
       </c>
       <c r="R91">
-        <v>4549</v>
+        <v>4548</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -6473,13 +6473,13 @@
         <v>0</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V91">
         <v>0</v>
       </c>
       <c r="W91">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92">
@@ -6493,13 +6493,13 @@
         <v>FORM6</v>
       </c>
       <c r="D92">
-        <v>4021</v>
+        <v>4025</v>
       </c>
       <c r="E92">
         <v>0</v>
       </c>
       <c r="F92">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -6656,7 +6656,7 @@
         <v>0</v>
       </c>
       <c r="K94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -6677,7 +6677,7 @@
         <v>1079</v>
       </c>
       <c r="R94">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -6706,13 +6706,13 @@
         <v>FORM8</v>
       </c>
       <c r="D95">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="E95">
         <v>0</v>
       </c>
       <c r="F95">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -6771,13 +6771,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D96">
-        <v>8996</v>
+        <v>9004</v>
       </c>
       <c r="E96">
         <v>0</v>
       </c>
       <c r="F96">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         <v>0</v>
       </c>
       <c r="K96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -6813,7 +6813,7 @@
         <v>1585</v>
       </c>
       <c r="R96">
-        <v>3962</v>
+        <v>3963</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -6842,13 +6842,13 @@
         <v>FORM6</v>
       </c>
       <c r="D97">
-        <v>3505</v>
+        <v>3513</v>
       </c>
       <c r="E97">
         <v>0</v>
       </c>
       <c r="F97">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -6984,7 +6984,7 @@
         <v>FORM7</v>
       </c>
       <c r="D99">
-        <v>2339</v>
+        <v>3592</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -7041,7 +7041,7 @@
         <v>0</v>
       </c>
       <c r="W99">
-        <v>1828</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="100">
@@ -7055,13 +7055,13 @@
         <v>FORM8</v>
       </c>
       <c r="D100">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="E100">
         <v>0</v>
       </c>
       <c r="F100">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -7076,7 +7076,7 @@
         <v>0</v>
       </c>
       <c r="K100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>101</v>
       </c>
       <c r="R100">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -7120,13 +7120,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D101">
-        <v>7192</v>
+        <v>8459</v>
       </c>
       <c r="E101">
         <v>0</v>
       </c>
       <c r="F101">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -7141,7 +7141,7 @@
         <v>0</v>
       </c>
       <c r="K101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -7162,7 +7162,7 @@
         <v>655</v>
       </c>
       <c r="R101">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -7177,7 +7177,7 @@
         <v>0</v>
       </c>
       <c r="W101">
-        <v>2401</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="102">
@@ -7191,13 +7191,13 @@
         <v>FORM6</v>
       </c>
       <c r="D102">
-        <v>4944</v>
+        <v>4952</v>
       </c>
       <c r="E102">
         <v>0</v>
       </c>
       <c r="F102">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -7212,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="R102">
-        <v>2698</v>
+        <v>2704</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>0</v>
       </c>
       <c r="U102">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V102">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>FORM8</v>
       </c>
       <c r="D105">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="E105">
         <v>0</v>
       </c>
       <c r="F105">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -7469,13 +7469,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D106">
-        <v>10500</v>
+        <v>10514</v>
       </c>
       <c r="E106">
         <v>0</v>
       </c>
       <c r="F106">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="K106">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -7508,10 +7508,10 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>2352</v>
+        <v>2346</v>
       </c>
       <c r="R106">
-        <v>3751</v>
+        <v>3757</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -7520,7 +7520,7 @@
         <v>0</v>
       </c>
       <c r="U106">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V106">
         <v>0</v>
@@ -7540,13 +7540,13 @@
         <v>FORM6</v>
       </c>
       <c r="D107">
-        <v>5232</v>
+        <v>5258</v>
       </c>
       <c r="E107">
         <v>0</v>
       </c>
       <c r="F107">
-        <v>802</v>
+        <v>828</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>0</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -7582,7 +7582,7 @@
         <v>710</v>
       </c>
       <c r="R107">
-        <v>3630</v>
+        <v>3632</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -7591,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="U107">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V107">
         <v>0</v>
@@ -7632,28 +7632,28 @@
         <v>0</v>
       </c>
       <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>0</v>
+      </c>
+      <c r="R108">
         <v>2</v>
-      </c>
-      <c r="L108">
-        <v>0</v>
-      </c>
-      <c r="M108">
-        <v>0</v>
-      </c>
-      <c r="N108">
-        <v>0</v>
-      </c>
-      <c r="O108">
-        <v>0</v>
-      </c>
-      <c r="P108">
-        <v>0</v>
-      </c>
-      <c r="Q108">
-        <v>0</v>
-      </c>
-      <c r="R108">
-        <v>0</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>FORM8</v>
       </c>
       <c r="D110">
-        <v>2157</v>
+        <v>2165</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="F110">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -7818,13 +7818,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D111">
-        <v>12271</v>
+        <v>12305</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111">
-        <v>1051</v>
+        <v>1085</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -7860,7 +7860,7 @@
         <v>2021</v>
       </c>
       <c r="R111">
-        <v>5617</v>
+        <v>5621</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -7869,7 +7869,7 @@
         <v>0</v>
       </c>
       <c r="U111">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V111">
         <v>0</v>
@@ -7889,13 +7889,13 @@
         <v>FORM6</v>
       </c>
       <c r="D112">
-        <v>5244</v>
+        <v>5269</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
       <c r="F112">
-        <v>728</v>
+        <v>753</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -7928,10 +7928,10 @@
         <v>0</v>
       </c>
       <c r="Q112">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="R112">
-        <v>2818</v>
+        <v>2822</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -8031,7 +8031,7 @@
         <v>FORM7</v>
       </c>
       <c r="D114">
-        <v>3471</v>
+        <v>4412</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -8088,7 +8088,7 @@
         <v>0</v>
       </c>
       <c r="W114">
-        <v>2370</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="115">
@@ -8102,13 +8102,13 @@
         <v>FORM8</v>
       </c>
       <c r="D115">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -8167,13 +8167,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D116">
-        <v>10133</v>
+        <v>11104</v>
       </c>
       <c r="E116">
         <v>0</v>
       </c>
       <c r="F116">
-        <v>1063</v>
+        <v>1093</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -8206,10 +8206,10 @@
         <v>0</v>
       </c>
       <c r="Q116">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="R116">
-        <v>3914</v>
+        <v>3918</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -8224,7 +8224,7 @@
         <v>0</v>
       </c>
       <c r="W116">
-        <v>2502</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="117">
@@ -8238,16 +8238,16 @@
         <v>FORM6</v>
       </c>
       <c r="D117">
-        <v>5730</v>
+        <v>5745</v>
       </c>
       <c r="E117">
         <v>0</v>
       </c>
       <c r="F117">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -8259,7 +8259,7 @@
         <v>0</v>
       </c>
       <c r="K117">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L117">
         <v>0</v>
@@ -8271,7 +8271,7 @@
         <v>0</v>
       </c>
       <c r="O117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P117">
         <v>0</v>
@@ -8309,13 +8309,13 @@
         <v>FORM7</v>
       </c>
       <c r="D118">
-        <v>345</v>
+        <v>1156</v>
       </c>
       <c r="E118">
         <v>0</v>
       </c>
       <c r="F118">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G118">
         <v>4</v>
@@ -8366,7 +8366,7 @@
         <v>0</v>
       </c>
       <c r="W118">
-        <v>22</v>
+        <v>832</v>
       </c>
     </row>
     <row r="119">
@@ -8380,13 +8380,13 @@
         <v>FORM8</v>
       </c>
       <c r="D119">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
       <c r="F119">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -8445,16 +8445,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D120">
-        <v>6944</v>
+        <v>7774</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="G120">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -8466,7 +8466,7 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L120">
         <v>0</v>
@@ -8478,7 +8478,7 @@
         <v>0</v>
       </c>
       <c r="O120">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -8502,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="W120">
-        <v>107</v>
+        <v>917</v>
       </c>
     </row>
     <row r="121">
@@ -8516,16 +8516,16 @@
         <v>FORM6</v>
       </c>
       <c r="D121">
-        <v>4507</v>
+        <v>4520</v>
       </c>
       <c r="E121">
         <v>0</v>
       </c>
       <c r="F121">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H121">
         <v>0</v>
@@ -8546,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="N121">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -8658,7 +8658,7 @@
         <v>FORM7</v>
       </c>
       <c r="D123">
-        <v>2196</v>
+        <v>2727</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -8715,7 +8715,7 @@
         <v>0</v>
       </c>
       <c r="W123">
-        <v>7</v>
+        <v>538</v>
       </c>
     </row>
     <row r="124">
@@ -8729,13 +8729,13 @@
         <v>FORM8</v>
       </c>
       <c r="D124">
-        <v>1553</v>
+        <v>1559</v>
       </c>
       <c r="E124">
         <v>0</v>
       </c>
       <c r="F124">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -8794,16 +8794,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D125">
-        <v>8261</v>
+        <v>8811</v>
       </c>
       <c r="E125">
         <v>0</v>
       </c>
       <c r="F125">
-        <v>613</v>
+        <v>632</v>
       </c>
       <c r="G125">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -8824,7 +8824,7 @@
         <v>0</v>
       </c>
       <c r="N125">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O125">
         <v>0</v>
@@ -8851,7 +8851,7 @@
         <v>0</v>
       </c>
       <c r="W125">
-        <v>10</v>
+        <v>541</v>
       </c>
     </row>
     <row r="126">
@@ -8865,13 +8865,13 @@
         <v>FORM6</v>
       </c>
       <c r="D126">
-        <v>2444</v>
+        <v>2453</v>
       </c>
       <c r="E126">
         <v>0</v>
       </c>
       <c r="F126">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -8889,13 +8889,13 @@
         <v>0</v>
       </c>
       <c r="L126">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="M126">
         <v>1</v>
       </c>
       <c r="N126">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="O126">
         <v>2</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="Q126">
-        <v>773</v>
+        <v>959</v>
       </c>
       <c r="R126">
-        <v>770</v>
+        <v>1078</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -9078,13 +9078,13 @@
         <v>FORM8</v>
       </c>
       <c r="D129">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="E129">
         <v>0</v>
       </c>
       <c r="F129">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -9143,13 +9143,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D130">
-        <v>6317</v>
+        <v>6332</v>
       </c>
       <c r="E130">
         <v>0</v>
       </c>
       <c r="F130">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="G130">
         <v>210</v>
@@ -9167,13 +9167,13 @@
         <v>0</v>
       </c>
       <c r="L130">
-        <v>503</v>
+        <v>11</v>
       </c>
       <c r="M130">
         <v>1</v>
       </c>
       <c r="N130">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O130">
         <v>4</v>
@@ -9182,10 +9182,10 @@
         <v>0</v>
       </c>
       <c r="Q130">
-        <v>3047</v>
+        <v>3233</v>
       </c>
       <c r="R130">
-        <v>1482</v>
+        <v>1790</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>FORM6</v>
       </c>
       <c r="D131">
-        <v>1574</v>
+        <v>1583</v>
       </c>
       <c r="E131">
         <v>0</v>
       </c>
       <c r="F131">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G131">
         <v>98</v>
@@ -9235,7 +9235,7 @@
         <v>1</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131">
         <v>0</v>
@@ -9253,7 +9253,7 @@
         <v>0</v>
       </c>
       <c r="Q131">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="R131">
         <v>930</v>
@@ -9356,13 +9356,13 @@
         <v>FORM8</v>
       </c>
       <c r="D133">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="E133">
         <v>0</v>
       </c>
       <c r="F133">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G133">
         <v>6</v>
@@ -9421,13 +9421,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D134">
-        <v>4850</v>
+        <v>4865</v>
       </c>
       <c r="E134">
         <v>0</v>
       </c>
       <c r="F134">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="G134">
         <v>105</v>
@@ -9442,7 +9442,7 @@
         <v>1</v>
       </c>
       <c r="K134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134">
         <v>0</v>
@@ -9460,7 +9460,7 @@
         <v>0</v>
       </c>
       <c r="Q134">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="R134">
         <v>1683</v>
@@ -9492,13 +9492,13 @@
         <v>FORM6</v>
       </c>
       <c r="D135">
-        <v>1690</v>
+        <v>1702</v>
       </c>
       <c r="E135">
         <v>0</v>
       </c>
       <c r="F135">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="G135">
         <v>27</v>
@@ -9634,7 +9634,7 @@
         <v>FORM7</v>
       </c>
       <c r="D137">
-        <v>6259</v>
+        <v>6340</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -9691,7 +9691,7 @@
         <v>0</v>
       </c>
       <c r="W137">
-        <v>1800</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="138">
@@ -9705,13 +9705,13 @@
         <v>FORM8</v>
       </c>
       <c r="D138">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="E138">
         <v>0</v>
       </c>
       <c r="F138">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -9770,13 +9770,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D139">
-        <v>8867</v>
+        <v>8966</v>
       </c>
       <c r="E139">
         <v>0</v>
       </c>
       <c r="F139">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="G139">
         <v>27</v>
@@ -9827,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="W139">
-        <v>1800</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="140">
@@ -9841,16 +9841,16 @@
         <v>FORM6</v>
       </c>
       <c r="D140">
-        <v>2394</v>
+        <v>2405</v>
       </c>
       <c r="E140">
         <v>0</v>
       </c>
       <c r="F140">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="G140">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -9862,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140">
         <v>0</v>
@@ -9871,7 +9871,7 @@
         <v>0</v>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O140">
         <v>0</v>
@@ -9880,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="Q140">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="R140">
         <v>986</v>
@@ -9983,16 +9983,16 @@
         <v>FORM8</v>
       </c>
       <c r="D142">
-        <v>1255</v>
+        <v>1267</v>
       </c>
       <c r="E142">
         <v>0</v>
       </c>
       <c r="F142">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G142">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -10001,7 +10001,7 @@
         <v>0</v>
       </c>
       <c r="J142">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K142">
         <v>0</v>
@@ -10048,16 +10048,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D143">
-        <v>6522</v>
+        <v>6545</v>
       </c>
       <c r="E143">
         <v>0</v>
       </c>
       <c r="F143">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="G143">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -10066,11 +10066,11 @@
         <v>0</v>
       </c>
       <c r="J143">
+        <v>4</v>
+      </c>
+      <c r="K143">
         <v>1</v>
       </c>
-      <c r="K143">
-        <v>0</v>
-      </c>
       <c r="L143">
         <v>0</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>0</v>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O143">
         <v>0</v>
@@ -10087,7 +10087,7 @@
         <v>0</v>
       </c>
       <c r="Q143">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="R143">
         <v>1531</v>
@@ -10119,16 +10119,16 @@
         <v>FORM6</v>
       </c>
       <c r="D144">
-        <v>2999</v>
+        <v>3008</v>
       </c>
       <c r="E144">
         <v>0</v>
       </c>
       <c r="F144">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="G144">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H144">
         <v>0</v>
@@ -10137,7 +10137,7 @@
         <v>0</v>
       </c>
       <c r="J144">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K144">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O144">
         <v>0</v>
@@ -10190,16 +10190,16 @@
         <v>FORM6A</v>
       </c>
       <c r="D145">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E145">
         <v>0</v>
       </c>
       <c r="F145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -10332,16 +10332,16 @@
         <v>FORM8</v>
       </c>
       <c r="D147">
-        <v>1545</v>
+        <v>1551</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="G147">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -10350,7 +10350,7 @@
         <v>0</v>
       </c>
       <c r="J147">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K147">
         <v>0</v>
@@ -10397,16 +10397,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D148">
-        <v>6403</v>
+        <v>6419</v>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
       <c r="F148">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="G148">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -10415,7 +10415,7 @@
         <v>0</v>
       </c>
       <c r="J148">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K148">
         <v>0</v>
@@ -10427,7 +10427,7 @@
         <v>0</v>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O148">
         <v>0</v>
@@ -10436,7 +10436,7 @@
         <v>0</v>
       </c>
       <c r="Q148">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="R148">
         <v>2082</v>
@@ -10468,13 +10468,13 @@
         <v>FORM6</v>
       </c>
       <c r="D149">
-        <v>2444</v>
+        <v>2458</v>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
       <c r="F149">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -10681,13 +10681,13 @@
         <v>FORM8</v>
       </c>
       <c r="D152">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="E152">
         <v>0</v>
       </c>
       <c r="F152">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -10746,13 +10746,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D153">
-        <v>6514</v>
+        <v>6535</v>
       </c>
       <c r="E153">
         <v>0</v>
       </c>
       <c r="F153">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -10817,13 +10817,13 @@
         <v>FORM6</v>
       </c>
       <c r="D154">
-        <v>3215</v>
+        <v>3227</v>
       </c>
       <c r="E154">
         <v>0</v>
       </c>
       <c r="F154">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -10909,7 +10909,7 @@
         <v>0</v>
       </c>
       <c r="K155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -10930,7 +10930,7 @@
         <v>1862</v>
       </c>
       <c r="R155">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S155">
         <v>0</v>
@@ -10959,13 +10959,13 @@
         <v>FORM8</v>
       </c>
       <c r="D156">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="E156">
         <v>0</v>
       </c>
       <c r="F156">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -11024,13 +11024,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D157">
-        <v>7426</v>
+        <v>7446</v>
       </c>
       <c r="E157">
         <v>0</v>
       </c>
       <c r="F157">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -11045,7 +11045,7 @@
         <v>0</v>
       </c>
       <c r="K157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>3573</v>
       </c>
       <c r="R157">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="S157">
         <v>0</v>
@@ -11095,13 +11095,13 @@
         <v>FORM6</v>
       </c>
       <c r="D158">
-        <v>2000</v>
+        <v>2013</v>
       </c>
       <c r="E158">
         <v>0</v>
       </c>
       <c r="F158">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -11237,13 +11237,13 @@
         <v>FORM8</v>
       </c>
       <c r="D160">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="E160">
         <v>0</v>
       </c>
       <c r="F160">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G160">
         <v>13</v>
@@ -11258,7 +11258,7 @@
         <v>0</v>
       </c>
       <c r="K160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>35</v>
       </c>
       <c r="R160">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S160">
         <v>0</v>
@@ -11302,13 +11302,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D161">
-        <v>6860</v>
+        <v>6880</v>
       </c>
       <c r="E161">
         <v>0</v>
       </c>
       <c r="F161">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="G161">
         <v>14</v>
@@ -11323,7 +11323,7 @@
         <v>0</v>
       </c>
       <c r="K161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -11344,7 +11344,7 @@
         <v>837</v>
       </c>
       <c r="R161">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -11373,13 +11373,13 @@
         <v>FORM6</v>
       </c>
       <c r="D162">
-        <v>3623</v>
+        <v>3637</v>
       </c>
       <c r="E162">
         <v>0</v>
       </c>
       <c r="F162">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="G162">
         <v>0</v>
@@ -11397,13 +11397,13 @@
         <v>0</v>
       </c>
       <c r="L162">
-        <v>866</v>
+        <v>120</v>
       </c>
       <c r="M162">
         <v>34</v>
       </c>
       <c r="N162">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="O162">
         <v>0</v>
@@ -11412,10 +11412,10 @@
         <v>0</v>
       </c>
       <c r="Q162">
-        <v>505</v>
+        <v>847</v>
       </c>
       <c r="R162">
-        <v>1679</v>
+        <v>2080</v>
       </c>
       <c r="S162">
         <v>0</v>
@@ -11515,13 +11515,13 @@
         <v>FORM8</v>
       </c>
       <c r="D164">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="E164">
         <v>0</v>
       </c>
       <c r="F164">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -11536,7 +11536,7 @@
         <v>0</v>
       </c>
       <c r="K164">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L164">
         <v>10</v>
@@ -11557,7 +11557,7 @@
         <v>421</v>
       </c>
       <c r="R164">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -11580,13 +11580,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D165">
-        <v>8896</v>
+        <v>8922</v>
       </c>
       <c r="E165">
         <v>0</v>
       </c>
       <c r="F165">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="G165">
         <v>7</v>
@@ -11601,16 +11601,16 @@
         <v>62</v>
       </c>
       <c r="K165">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L165">
-        <v>938</v>
+        <v>192</v>
       </c>
       <c r="M165">
         <v>34</v>
       </c>
       <c r="N165">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="O165">
         <v>0</v>
@@ -11619,10 +11619,10 @@
         <v>0</v>
       </c>
       <c r="Q165">
-        <v>2688</v>
+        <v>3030</v>
       </c>
       <c r="R165">
-        <v>2196</v>
+        <v>2598</v>
       </c>
       <c r="S165">
         <v>0</v>
@@ -11651,13 +11651,13 @@
         <v>FORM6</v>
       </c>
       <c r="D166">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="E166">
         <v>0</v>
       </c>
       <c r="F166">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G166">
         <v>40</v>
@@ -11722,7 +11722,7 @@
         <v>FORM7</v>
       </c>
       <c r="D167">
-        <v>1119</v>
+        <v>1230</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -11779,7 +11779,7 @@
         <v>0</v>
       </c>
       <c r="W167">
-        <v>431</v>
+        <v>542</v>
       </c>
     </row>
     <row r="168">
@@ -11793,13 +11793,13 @@
         <v>FORM8</v>
       </c>
       <c r="D168">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="E168">
         <v>0</v>
       </c>
       <c r="F168">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G168">
         <v>0</v>
@@ -11858,13 +11858,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D169">
-        <v>2739</v>
+        <v>2861</v>
       </c>
       <c r="E169">
         <v>0</v>
       </c>
       <c r="F169">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G169">
         <v>40</v>
@@ -11915,7 +11915,7 @@
         <v>0</v>
       </c>
       <c r="W169">
-        <v>1262</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="170">
@@ -11929,13 +11929,13 @@
         <v>FORM6</v>
       </c>
       <c r="D170">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="E170">
         <v>0</v>
       </c>
       <c r="F170">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G170">
         <v>5</v>
@@ -12142,13 +12142,13 @@
         <v>FORM8</v>
       </c>
       <c r="D173">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E173">
         <v>0</v>
       </c>
       <c r="F173">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G173">
         <v>5</v>
@@ -12207,13 +12207,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D174">
-        <v>1550</v>
+        <v>1559</v>
       </c>
       <c r="E174">
         <v>0</v>
       </c>
       <c r="F174">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G174">
         <v>10</v>
@@ -12278,16 +12278,16 @@
         <v>FORM6</v>
       </c>
       <c r="D175">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="E175">
         <v>0</v>
       </c>
       <c r="F175">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G175">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -12320,7 +12320,7 @@
         <v>114</v>
       </c>
       <c r="R175">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -12349,7 +12349,7 @@
         <v>FORM7</v>
       </c>
       <c r="D176">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -12406,7 +12406,7 @@
         <v>0</v>
       </c>
       <c r="W176">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="177">
@@ -12420,13 +12420,13 @@
         <v>FORM8</v>
       </c>
       <c r="D177">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E177">
         <v>0</v>
       </c>
       <c r="F177">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G177">
         <v>3</v>
@@ -12485,16 +12485,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D178">
-        <v>3491</v>
+        <v>3499</v>
       </c>
       <c r="E178">
         <v>0</v>
       </c>
       <c r="F178">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G178">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H178">
         <v>0</v>
@@ -12527,7 +12527,7 @@
         <v>1052</v>
       </c>
       <c r="R178">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="S178">
         <v>0</v>
@@ -12542,7 +12542,7 @@
         <v>0</v>
       </c>
       <c r="W178">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="179">
@@ -12556,13 +12556,13 @@
         <v>FORM6</v>
       </c>
       <c r="D179">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E179">
         <v>0</v>
       </c>
       <c r="F179">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G179">
         <v>0</v>
@@ -12698,13 +12698,13 @@
         <v>FORM8</v>
       </c>
       <c r="D181">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E181">
         <v>0</v>
       </c>
       <c r="F181">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G181">
         <v>0</v>
@@ -12763,13 +12763,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D182">
-        <v>1467</v>
+        <v>1478</v>
       </c>
       <c r="E182">
         <v>0</v>
       </c>
       <c r="F182">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G182">
         <v>22</v>
@@ -12834,13 +12834,13 @@
         <v>FORM6</v>
       </c>
       <c r="D183">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E183">
         <v>0</v>
       </c>
       <c r="F183">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G183">
         <v>0</v>
@@ -12976,13 +12976,13 @@
         <v>FORM8</v>
       </c>
       <c r="D185">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E185">
         <v>0</v>
       </c>
       <c r="F185">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G185">
         <v>0</v>
@@ -12997,7 +12997,7 @@
         <v>0</v>
       </c>
       <c r="K185">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L185">
         <v>0</v>
@@ -13018,7 +13018,7 @@
         <v>37</v>
       </c>
       <c r="R185">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -13041,13 +13041,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D186">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="E186">
         <v>0</v>
       </c>
       <c r="F186">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G186">
         <v>0</v>
@@ -13062,7 +13062,7 @@
         <v>0</v>
       </c>
       <c r="K186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L186">
         <v>0</v>
@@ -13083,7 +13083,7 @@
         <v>333</v>
       </c>
       <c r="R186">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -13112,13 +13112,13 @@
         <v>FORM6</v>
       </c>
       <c r="D187">
-        <v>2687</v>
+        <v>2696</v>
       </c>
       <c r="E187">
         <v>0</v>
       </c>
       <c r="F187">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G187">
         <v>0</v>
@@ -13133,7 +13133,7 @@
         <v>0</v>
       </c>
       <c r="K187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L187">
         <v>0</v>
@@ -13154,7 +13154,7 @@
         <v>381</v>
       </c>
       <c r="R187">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -13254,7 +13254,7 @@
         <v>FORM7</v>
       </c>
       <c r="D189">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -13275,7 +13275,7 @@
         <v>0</v>
       </c>
       <c r="K189">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L189">
         <v>0</v>
@@ -13293,7 +13293,7 @@
         <v>0</v>
       </c>
       <c r="Q189">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R189">
         <v>108</v>
@@ -13311,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="W189">
-        <v>891</v>
+        <v>896</v>
       </c>
     </row>
     <row r="190">
@@ -13325,13 +13325,13 @@
         <v>FORM8</v>
       </c>
       <c r="D190">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="E190">
         <v>0</v>
       </c>
       <c r="F190">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G190">
         <v>0</v>
@@ -13346,7 +13346,7 @@
         <v>0</v>
       </c>
       <c r="K190">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L190">
         <v>0</v>
@@ -13364,10 +13364,10 @@
         <v>0</v>
       </c>
       <c r="Q190">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="R190">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -13390,13 +13390,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D191">
-        <v>4818</v>
+        <v>4836</v>
       </c>
       <c r="E191">
         <v>0</v>
       </c>
       <c r="F191">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G191">
         <v>0</v>
@@ -13411,7 +13411,7 @@
         <v>0</v>
       </c>
       <c r="K191">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L191">
         <v>0</v>
@@ -13429,10 +13429,10 @@
         <v>0</v>
       </c>
       <c r="Q191">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="R191">
-        <v>3011</v>
+        <v>3013</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -13447,7 +13447,7 @@
         <v>0</v>
       </c>
       <c r="W191">
-        <v>892</v>
+        <v>897</v>
       </c>
     </row>
     <row r="192">
@@ -13461,13 +13461,13 @@
         <v>FORM6</v>
       </c>
       <c r="D192">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E192">
         <v>0</v>
       </c>
       <c r="F192">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G192">
         <v>0</v>
@@ -13482,7 +13482,7 @@
         <v>0</v>
       </c>
       <c r="K192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L192">
         <v>0</v>
@@ -13500,7 +13500,7 @@
         <v>0</v>
       </c>
       <c r="Q192">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R192">
         <v>411</v>
@@ -13603,13 +13603,13 @@
         <v>FORM8</v>
       </c>
       <c r="D194">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E194">
         <v>0</v>
       </c>
       <c r="F194">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G194">
         <v>0</v>
@@ -13668,13 +13668,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D195">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="E195">
         <v>0</v>
       </c>
       <c r="F195">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G195">
         <v>0</v>
@@ -13689,7 +13689,7 @@
         <v>0</v>
       </c>
       <c r="K195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L195">
         <v>0</v>
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R195">
         <v>462</v>
@@ -13739,13 +13739,13 @@
         <v>FORM6</v>
       </c>
       <c r="D196">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="E196">
         <v>0</v>
       </c>
       <c r="F196">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G196">
         <v>0</v>
@@ -13810,7 +13810,7 @@
         <v>FORM7</v>
       </c>
       <c r="D197">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -13867,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="W197">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="198">
@@ -13881,13 +13881,13 @@
         <v>FORM8</v>
       </c>
       <c r="D198">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E198">
         <v>0</v>
       </c>
       <c r="F198">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G198">
         <v>0</v>
@@ -13946,13 +13946,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D199">
-        <v>2338</v>
+        <v>2344</v>
       </c>
       <c r="E199">
         <v>0</v>
       </c>
       <c r="F199">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G199">
         <v>0</v>
@@ -14003,7 +14003,7 @@
         <v>0</v>
       </c>
       <c r="W199">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="200">
@@ -14017,13 +14017,13 @@
         <v>FORM6</v>
       </c>
       <c r="D200">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="E200">
         <v>0</v>
       </c>
       <c r="F200">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G200">
         <v>0</v>
@@ -14159,7 +14159,7 @@
         <v>FORM7</v>
       </c>
       <c r="D202">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -14180,7 +14180,7 @@
         <v>0</v>
       </c>
       <c r="K202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L202">
         <v>0</v>
@@ -14201,7 +14201,7 @@
         <v>344</v>
       </c>
       <c r="R202">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -14216,7 +14216,7 @@
         <v>0</v>
       </c>
       <c r="W202">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="203">
@@ -14230,13 +14230,13 @@
         <v>FORM8</v>
       </c>
       <c r="D203">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="E203">
         <v>0</v>
       </c>
       <c r="F203">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G203">
         <v>0</v>
@@ -14295,13 +14295,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D204">
-        <v>3027</v>
+        <v>3037</v>
       </c>
       <c r="E204">
         <v>0</v>
       </c>
       <c r="F204">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G204">
         <v>0</v>
@@ -14316,7 +14316,7 @@
         <v>0</v>
       </c>
       <c r="K204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L204">
         <v>0</v>
@@ -14337,7 +14337,7 @@
         <v>416</v>
       </c>
       <c r="R204">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -14352,7 +14352,7 @@
         <v>0</v>
       </c>
       <c r="W204">
-        <v>1334</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="205">
@@ -14366,13 +14366,13 @@
         <v>FORM6</v>
       </c>
       <c r="D205">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="E205">
         <v>0</v>
       </c>
       <c r="F205">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G205">
         <v>0</v>
@@ -14437,7 +14437,7 @@
         <v>FORM7</v>
       </c>
       <c r="D206">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -14494,7 +14494,7 @@
         <v>0</v>
       </c>
       <c r="W206">
-        <v>201</v>
+        <v>217</v>
       </c>
     </row>
     <row r="207">
@@ -14508,13 +14508,13 @@
         <v>FORM8</v>
       </c>
       <c r="D207">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E207">
         <v>0</v>
       </c>
       <c r="F207">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G207">
         <v>0</v>
@@ -14573,13 +14573,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D208">
-        <v>1457</v>
+        <v>1482</v>
       </c>
       <c r="E208">
         <v>0</v>
       </c>
       <c r="F208">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G208">
         <v>0</v>
@@ -14630,7 +14630,7 @@
         <v>0</v>
       </c>
       <c r="W208">
-        <v>352</v>
+        <v>368</v>
       </c>
     </row>
     <row r="209">
@@ -14644,13 +14644,13 @@
         <v>FORM6</v>
       </c>
       <c r="D209">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="E209">
         <v>0</v>
       </c>
       <c r="F209">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G209">
         <v>3</v>
@@ -14786,13 +14786,13 @@
         <v>FORM8</v>
       </c>
       <c r="D211">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E211">
         <v>0</v>
       </c>
       <c r="F211">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G211">
         <v>0</v>
@@ -14851,13 +14851,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D212">
-        <v>3838</v>
+        <v>3840</v>
       </c>
       <c r="E212">
         <v>0</v>
       </c>
       <c r="F212">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G212">
         <v>3</v>
@@ -14922,13 +14922,13 @@
         <v>FORM6</v>
       </c>
       <c r="D213">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="E213">
         <v>0</v>
       </c>
       <c r="F213">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G213">
         <v>3</v>
@@ -15064,13 +15064,13 @@
         <v>FORM8</v>
       </c>
       <c r="D215">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E215">
         <v>0</v>
       </c>
       <c r="F215">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G215">
         <v>1</v>
@@ -15129,13 +15129,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D216">
-        <v>3635</v>
+        <v>3637</v>
       </c>
       <c r="E216">
         <v>0</v>
       </c>
       <c r="F216">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G216">
         <v>5</v>
@@ -15200,13 +15200,13 @@
         <v>FORM6</v>
       </c>
       <c r="D217">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="E217">
         <v>0</v>
       </c>
       <c r="F217">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G217">
         <v>1</v>
@@ -15342,13 +15342,13 @@
         <v>FORM8</v>
       </c>
       <c r="D219">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E219">
         <v>0</v>
       </c>
       <c r="F219">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G219">
         <v>1</v>
@@ -15407,13 +15407,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D220">
-        <v>1896</v>
+        <v>1900</v>
       </c>
       <c r="E220">
         <v>0</v>
       </c>
       <c r="F220">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G220">
         <v>6</v>
@@ -15478,13 +15478,13 @@
         <v>FORM6</v>
       </c>
       <c r="D221">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="E221">
         <v>0</v>
       </c>
       <c r="F221">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G221">
         <v>17</v>
@@ -15620,7 +15620,7 @@
         <v>FORM7</v>
       </c>
       <c r="D223">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -15677,7 +15677,7 @@
         <v>0</v>
       </c>
       <c r="W223">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="224">
@@ -15691,13 +15691,13 @@
         <v>FORM8</v>
       </c>
       <c r="D224">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E224">
         <v>0</v>
       </c>
       <c r="F224">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G224">
         <v>9</v>
@@ -15756,13 +15756,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D225">
-        <v>2247</v>
+        <v>2256</v>
       </c>
       <c r="E225">
         <v>0</v>
       </c>
       <c r="F225">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G225">
         <v>27</v>
@@ -15813,7 +15813,7 @@
         <v>0</v>
       </c>
       <c r="W225">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="226">
@@ -15827,13 +15827,13 @@
         <v>FORM6</v>
       </c>
       <c r="D226">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="E226">
         <v>0</v>
       </c>
       <c r="F226">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G226">
         <v>26</v>
@@ -15848,7 +15848,7 @@
         <v>0</v>
       </c>
       <c r="K226">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L226">
         <v>0</v>
@@ -15866,10 +15866,10 @@
         <v>0</v>
       </c>
       <c r="Q226">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R226">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -16040,13 +16040,13 @@
         <v>FORM8</v>
       </c>
       <c r="D229">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E229">
         <v>0</v>
       </c>
       <c r="F229">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G229">
         <v>8</v>
@@ -16105,13 +16105,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D230">
-        <v>2451</v>
+        <v>2457</v>
       </c>
       <c r="E230">
         <v>0</v>
       </c>
       <c r="F230">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G230">
         <v>36</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="K230">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L230">
         <v>0</v>
@@ -16144,10 +16144,10 @@
         <v>0</v>
       </c>
       <c r="Q230">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="R230">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="S230">
         <v>0</v>
@@ -16197,7 +16197,7 @@
         <v>0</v>
       </c>
       <c r="K231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L231">
         <v>0</v>
@@ -16218,7 +16218,7 @@
         <v>1</v>
       </c>
       <c r="R231">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="S231">
         <v>0</v>
@@ -16247,7 +16247,7 @@
         <v>FORM7</v>
       </c>
       <c r="D232">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -16304,7 +16304,7 @@
         <v>0</v>
       </c>
       <c r="W232">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="233">
@@ -16318,13 +16318,13 @@
         <v>FORM8</v>
       </c>
       <c r="D233">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E233">
         <v>0</v>
       </c>
       <c r="F233">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G233">
         <v>3</v>
@@ -16383,13 +16383,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D234">
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="E234">
         <v>0</v>
       </c>
       <c r="F234">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G234">
         <v>11</v>
@@ -16404,7 +16404,7 @@
         <v>0</v>
       </c>
       <c r="K234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L234">
         <v>0</v>
@@ -16425,7 +16425,7 @@
         <v>197</v>
       </c>
       <c r="R234">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="S234">
         <v>0</v>
@@ -16440,7 +16440,7 @@
         <v>0</v>
       </c>
       <c r="W234">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="235">
@@ -16667,13 +16667,13 @@
         <v>FORM8</v>
       </c>
       <c r="D238">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E238">
         <v>0</v>
       </c>
       <c r="F238">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G238">
         <v>0</v>
@@ -16732,13 +16732,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D239">
-        <v>2550</v>
+        <v>2553</v>
       </c>
       <c r="E239">
         <v>0</v>
       </c>
       <c r="F239">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G239">
         <v>0</v>
@@ -16824,7 +16824,7 @@
         <v>0</v>
       </c>
       <c r="K240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -16842,7 +16842,7 @@
         <v>0</v>
       </c>
       <c r="Q240">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R240">
         <v>513</v>
@@ -16945,13 +16945,13 @@
         <v>FORM8</v>
       </c>
       <c r="D242">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E242">
         <v>0</v>
       </c>
       <c r="F242">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G242">
         <v>0</v>
@@ -17010,13 +17010,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D243">
-        <v>1640</v>
+        <v>1645</v>
       </c>
       <c r="E243">
         <v>0</v>
       </c>
       <c r="F243">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G243">
         <v>1</v>
@@ -17031,7 +17031,7 @@
         <v>0</v>
       </c>
       <c r="K243">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L243">
         <v>0</v>
@@ -17049,7 +17049,7 @@
         <v>0</v>
       </c>
       <c r="Q243">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R243">
         <v>692</v>
@@ -17081,13 +17081,13 @@
         <v>FORM6</v>
       </c>
       <c r="D244">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="E244">
         <v>0</v>
       </c>
       <c r="F244">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G244">
         <v>0</v>
@@ -17223,13 +17223,13 @@
         <v>FORM8</v>
       </c>
       <c r="D246">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E246">
         <v>0</v>
       </c>
       <c r="F246">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G246">
         <v>0</v>
@@ -17288,13 +17288,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D247">
-        <v>3039</v>
+        <v>3042</v>
       </c>
       <c r="E247">
         <v>0</v>
       </c>
       <c r="F247">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G247">
         <v>0</v>
@@ -17359,13 +17359,13 @@
         <v>FORM6</v>
       </c>
       <c r="D248">
-        <v>1726</v>
+        <v>1732</v>
       </c>
       <c r="E248">
         <v>0</v>
       </c>
       <c r="F248">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G248">
         <v>0</v>
@@ -17430,7 +17430,7 @@
         <v>FORM7</v>
       </c>
       <c r="D249">
-        <v>1242</v>
+        <v>1304</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -17487,7 +17487,7 @@
         <v>0</v>
       </c>
       <c r="W249">
-        <v>790</v>
+        <v>852</v>
       </c>
     </row>
     <row r="250">
@@ -17501,13 +17501,13 @@
         <v>FORM8</v>
       </c>
       <c r="D250">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E250">
         <v>0</v>
       </c>
       <c r="F250">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G250">
         <v>0</v>
@@ -17566,13 +17566,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D251">
-        <v>3699</v>
+        <v>3769</v>
       </c>
       <c r="E251">
         <v>0</v>
       </c>
       <c r="F251">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="G251">
         <v>0</v>
@@ -17623,7 +17623,7 @@
         <v>0</v>
       </c>
       <c r="W251">
-        <v>1489</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="252">
@@ -17637,13 +17637,13 @@
         <v>FORM6</v>
       </c>
       <c r="D252">
-        <v>2103</v>
+        <v>2120</v>
       </c>
       <c r="E252">
         <v>0</v>
       </c>
       <c r="F252">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="G252">
         <v>0</v>
@@ -17708,7 +17708,7 @@
         <v>FORM7</v>
       </c>
       <c r="D253">
-        <v>3439</v>
+        <v>3462</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -17765,7 +17765,7 @@
         <v>0</v>
       </c>
       <c r="W253">
-        <v>2803</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="254">
@@ -17779,13 +17779,13 @@
         <v>FORM8</v>
       </c>
       <c r="D254">
-        <v>871</v>
+        <v>881</v>
       </c>
       <c r="E254">
         <v>0</v>
       </c>
       <c r="F254">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G254">
         <v>0</v>
@@ -17844,13 +17844,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D255">
-        <v>6413</v>
+        <v>6463</v>
       </c>
       <c r="E255">
         <v>0</v>
       </c>
       <c r="F255">
-        <v>514</v>
+        <v>541</v>
       </c>
       <c r="G255">
         <v>0</v>
@@ -17901,7 +17901,7 @@
         <v>0</v>
       </c>
       <c r="W255">
-        <v>4423</v>
+        <v>4446</v>
       </c>
     </row>
     <row r="256">
@@ -17915,13 +17915,13 @@
         <v>FORM6</v>
       </c>
       <c r="D256">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="E256">
         <v>0</v>
       </c>
       <c r="F256">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G256">
         <v>0</v>
@@ -17986,7 +17986,7 @@
         <v>FORM7</v>
       </c>
       <c r="D257">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -18043,7 +18043,7 @@
         <v>0</v>
       </c>
       <c r="W257">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="258">
@@ -18057,13 +18057,13 @@
         <v>FORM8</v>
       </c>
       <c r="D258">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E258">
         <v>0</v>
       </c>
       <c r="F258">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G258">
         <v>0</v>
@@ -18122,13 +18122,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D259">
-        <v>1709</v>
+        <v>1725</v>
       </c>
       <c r="E259">
         <v>0</v>
       </c>
       <c r="F259">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="G259">
         <v>0</v>
@@ -18179,7 +18179,7 @@
         <v>0</v>
       </c>
       <c r="W259">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="260">
@@ -18193,13 +18193,13 @@
         <v>FORM6</v>
       </c>
       <c r="D260">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="E260">
         <v>0</v>
       </c>
       <c r="F260">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G260">
         <v>0</v>
@@ -18214,7 +18214,7 @@
         <v>0</v>
       </c>
       <c r="K260">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L260">
         <v>0</v>
@@ -18235,7 +18235,7 @@
         <v>18</v>
       </c>
       <c r="R260">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="S260">
         <v>0</v>
@@ -18335,7 +18335,7 @@
         <v>FORM7</v>
       </c>
       <c r="D262">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E262">
         <v>0</v>
@@ -18392,7 +18392,7 @@
         <v>0</v>
       </c>
       <c r="W262">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="263">
@@ -18406,13 +18406,13 @@
         <v>FORM8</v>
       </c>
       <c r="D263">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E263">
         <v>0</v>
       </c>
       <c r="F263">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G263">
         <v>0</v>
@@ -18471,13 +18471,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D264">
-        <v>2216</v>
+        <v>2226</v>
       </c>
       <c r="E264">
         <v>0</v>
       </c>
       <c r="F264">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G264">
         <v>0</v>
@@ -18492,7 +18492,7 @@
         <v>0</v>
       </c>
       <c r="K264">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L264">
         <v>0</v>
@@ -18513,7 +18513,7 @@
         <v>525</v>
       </c>
       <c r="R264">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="S264">
         <v>0</v>
@@ -18528,7 +18528,7 @@
         <v>0</v>
       </c>
       <c r="W264">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="265">
@@ -18542,13 +18542,13 @@
         <v>FORM6</v>
       </c>
       <c r="D265">
-        <v>5571</v>
+        <v>5590</v>
       </c>
       <c r="E265">
         <v>0</v>
       </c>
       <c r="F265">
-        <v>533</v>
+        <v>552</v>
       </c>
       <c r="G265">
         <v>0</v>
@@ -18684,7 +18684,7 @@
         <v>FORM7</v>
       </c>
       <c r="D267">
-        <v>9267</v>
+        <v>9354</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -18705,7 +18705,7 @@
         <v>0</v>
       </c>
       <c r="K267">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L267">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>7156</v>
       </c>
       <c r="R267">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="S267">
         <v>0</v>
@@ -18741,7 +18741,7 @@
         <v>0</v>
       </c>
       <c r="W267">
-        <v>1850</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="268">
@@ -18755,13 +18755,13 @@
         <v>FORM8</v>
       </c>
       <c r="D268">
-        <v>2474</v>
+        <v>2485</v>
       </c>
       <c r="E268">
         <v>0</v>
       </c>
       <c r="F268">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="G268">
         <v>0</v>
@@ -18820,13 +18820,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D269">
-        <v>17337</v>
+        <v>17454</v>
       </c>
       <c r="E269">
         <v>0</v>
       </c>
       <c r="F269">
-        <v>743</v>
+        <v>773</v>
       </c>
       <c r="G269">
         <v>0</v>
@@ -18841,7 +18841,7 @@
         <v>0</v>
       </c>
       <c r="K269">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -18862,7 +18862,7 @@
         <v>8151</v>
       </c>
       <c r="R269">
-        <v>4762</v>
+        <v>4763</v>
       </c>
       <c r="S269">
         <v>0</v>
@@ -18877,7 +18877,7 @@
         <v>0</v>
       </c>
       <c r="W269">
-        <v>2832</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="270">
@@ -18891,13 +18891,13 @@
         <v>FORM6</v>
       </c>
       <c r="D270">
-        <v>4855</v>
+        <v>4880</v>
       </c>
       <c r="E270">
         <v>0</v>
       </c>
       <c r="F270">
-        <v>545</v>
+        <v>570</v>
       </c>
       <c r="G270">
         <v>0</v>
@@ -19104,13 +19104,13 @@
         <v>FORM8</v>
       </c>
       <c r="D273">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="E273">
         <v>0</v>
       </c>
       <c r="F273">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="G273">
         <v>0</v>
@@ -19169,13 +19169,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D274">
-        <v>8845</v>
+        <v>8885</v>
       </c>
       <c r="E274">
         <v>0</v>
       </c>
       <c r="F274">
-        <v>747</v>
+        <v>787</v>
       </c>
       <c r="G274">
         <v>0</v>
@@ -19240,13 +19240,13 @@
         <v>FORM6</v>
       </c>
       <c r="D275">
-        <v>2661</v>
+        <v>2676</v>
       </c>
       <c r="E275">
         <v>0</v>
       </c>
       <c r="F275">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="G275">
         <v>0</v>
@@ -19261,10 +19261,10 @@
         <v>0</v>
       </c>
       <c r="K275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L275">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M275">
         <v>0</v>
@@ -19282,7 +19282,7 @@
         <v>168</v>
       </c>
       <c r="R275">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="S275">
         <v>0</v>
@@ -19382,7 +19382,7 @@
         <v>FORM7</v>
       </c>
       <c r="D277">
-        <v>2218</v>
+        <v>2221</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -19439,7 +19439,7 @@
         <v>0</v>
       </c>
       <c r="W277">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="278">
@@ -19453,13 +19453,13 @@
         <v>FORM8</v>
       </c>
       <c r="D278">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="E278">
         <v>0</v>
       </c>
       <c r="F278">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="G278">
         <v>0</v>
@@ -19518,13 +19518,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D279">
-        <v>6081</v>
+        <v>6112</v>
       </c>
       <c r="E279">
         <v>0</v>
       </c>
       <c r="F279">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="G279">
         <v>0</v>
@@ -19539,10 +19539,10 @@
         <v>0</v>
       </c>
       <c r="K279">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L279">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M279">
         <v>0</v>
@@ -19560,7 +19560,7 @@
         <v>1894</v>
       </c>
       <c r="R279">
-        <v>2126</v>
+        <v>2131</v>
       </c>
       <c r="S279">
         <v>0</v>
@@ -19575,7 +19575,7 @@
         <v>0</v>
       </c>
       <c r="W279">
-        <v>1323</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="280">
@@ -19589,37 +19589,37 @@
         <v>FORM6</v>
       </c>
       <c r="D280">
-        <v>3666</v>
+        <v>3696</v>
       </c>
       <c r="E280">
         <v>0</v>
       </c>
       <c r="F280">
-        <v>602</v>
+        <v>619</v>
       </c>
       <c r="G280">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="H280">
         <v>0</v>
       </c>
       <c r="I280">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J280">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K280">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L280">
         <v>0</v>
       </c>
       <c r="M280">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N280">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="O280">
         <v>0</v>
@@ -19628,10 +19628,10 @@
         <v>0</v>
       </c>
       <c r="Q280">
-        <v>931</v>
+        <v>1068</v>
       </c>
       <c r="R280">
-        <v>1873</v>
+        <v>1981</v>
       </c>
       <c r="S280">
         <v>0</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="U280">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V280">
         <v>0</v>
@@ -19681,7 +19681,7 @@
         <v>0</v>
       </c>
       <c r="K281">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L281">
         <v>0</v>
@@ -19699,10 +19699,10 @@
         <v>0</v>
       </c>
       <c r="Q281">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R281">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S281">
         <v>0</v>
@@ -19731,31 +19731,31 @@
         <v>FORM7</v>
       </c>
       <c r="D282">
-        <v>8082</v>
+        <v>8527</v>
       </c>
       <c r="E282">
         <v>0</v>
       </c>
       <c r="F282">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="G282">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H282">
         <v>0</v>
       </c>
       <c r="I282">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="J282">
         <v>0</v>
       </c>
       <c r="K282">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L282">
-        <v>1483</v>
+        <v>0</v>
       </c>
       <c r="M282">
         <v>0</v>
@@ -19770,10 +19770,10 @@
         <v>0</v>
       </c>
       <c r="Q282">
-        <v>2184</v>
+        <v>6273</v>
       </c>
       <c r="R282">
-        <v>256</v>
+        <v>563</v>
       </c>
       <c r="S282">
         <v>0</v>
@@ -19788,7 +19788,7 @@
         <v>0</v>
       </c>
       <c r="W282">
-        <v>1245</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="283">
@@ -19802,16 +19802,16 @@
         <v>FORM8</v>
       </c>
       <c r="D283">
-        <v>1494</v>
+        <v>1504</v>
       </c>
       <c r="E283">
         <v>0</v>
       </c>
       <c r="F283">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G283">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H283">
         <v>0</v>
@@ -19823,7 +19823,7 @@
         <v>0</v>
       </c>
       <c r="K283">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L283">
         <v>0</v>
@@ -19832,7 +19832,7 @@
         <v>0</v>
       </c>
       <c r="N283">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O283">
         <v>0</v>
@@ -19841,10 +19841,10 @@
         <v>0</v>
       </c>
       <c r="Q283">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="R283">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="S283">
         <v>0</v>
@@ -19867,37 +19867,37 @@
         <v>AC Form Total</v>
       </c>
       <c r="D284">
-        <v>13255</v>
+        <v>13740</v>
       </c>
       <c r="E284">
         <v>0</v>
       </c>
       <c r="F284">
-        <v>3473</v>
+        <v>801</v>
       </c>
       <c r="G284">
-        <v>130</v>
+        <v>5</v>
       </c>
       <c r="H284">
         <v>0</v>
       </c>
       <c r="I284">
-        <v>193</v>
+        <v>1</v>
       </c>
       <c r="J284">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K284">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="L284">
-        <v>1483</v>
+        <v>0</v>
       </c>
       <c r="M284">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N284">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="O284">
         <v>0</v>
@@ -19906,10 +19906,10 @@
         <v>0</v>
       </c>
       <c r="Q284">
-        <v>3300</v>
+        <v>7532</v>
       </c>
       <c r="R284">
-        <v>3248</v>
+        <v>3672</v>
       </c>
       <c r="S284">
         <v>0</v>
@@ -19918,13 +19918,13 @@
         <v>0</v>
       </c>
       <c r="U284">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V284">
         <v>0</v>
       </c>
       <c r="W284">
-        <v>1245</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="285">
@@ -19938,13 +19938,13 @@
         <v>FORM6</v>
       </c>
       <c r="D285">
-        <v>5906</v>
+        <v>5964</v>
       </c>
       <c r="E285">
         <v>0</v>
       </c>
       <c r="F285">
-        <v>1042</v>
+        <v>1100</v>
       </c>
       <c r="G285">
         <v>0</v>
@@ -19962,7 +19962,7 @@
         <v>0</v>
       </c>
       <c r="L285">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="M285">
         <v>0</v>
@@ -19977,10 +19977,10 @@
         <v>0</v>
       </c>
       <c r="Q285">
-        <v>211</v>
+        <v>373</v>
       </c>
       <c r="R285">
-        <v>4180</v>
+        <v>4486</v>
       </c>
       <c r="S285">
         <v>0</v>
@@ -20080,7 +20080,7 @@
         <v>FORM7</v>
       </c>
       <c r="D287">
-        <v>9945</v>
+        <v>10416</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -20137,7 +20137,7 @@
         <v>0</v>
       </c>
       <c r="W287">
-        <v>3045</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="288">
@@ -20151,13 +20151,13 @@
         <v>FORM8</v>
       </c>
       <c r="D288">
-        <v>2165</v>
+        <v>2184</v>
       </c>
       <c r="E288">
         <v>0</v>
       </c>
       <c r="F288">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="G288">
         <v>0</v>
@@ -20216,13 +20216,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D289">
-        <v>18020</v>
+        <v>18568</v>
       </c>
       <c r="E289">
         <v>0</v>
       </c>
       <c r="F289">
-        <v>1219</v>
+        <v>1296</v>
       </c>
       <c r="G289">
         <v>0</v>
@@ -20240,7 +20240,7 @@
         <v>0</v>
       </c>
       <c r="L289">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="M289">
         <v>0</v>
@@ -20255,10 +20255,10 @@
         <v>0</v>
       </c>
       <c r="Q289">
-        <v>7324</v>
+        <v>7486</v>
       </c>
       <c r="R289">
-        <v>5913</v>
+        <v>6219</v>
       </c>
       <c r="S289">
         <v>0</v>
@@ -20273,7 +20273,7 @@
         <v>0</v>
       </c>
       <c r="W289">
-        <v>3050</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="290">
@@ -20287,13 +20287,13 @@
         <v>FORM6</v>
       </c>
       <c r="D290">
-        <v>3437</v>
+        <v>3464</v>
       </c>
       <c r="E290">
         <v>0</v>
       </c>
       <c r="F290">
-        <v>529</v>
+        <v>556</v>
       </c>
       <c r="G290">
         <v>0</v>
@@ -20429,7 +20429,7 @@
         <v>FORM7</v>
       </c>
       <c r="D292">
-        <v>6326</v>
+        <v>6881</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -20486,7 +20486,7 @@
         <v>0</v>
       </c>
       <c r="W292">
-        <v>4014</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="293">
@@ -20500,13 +20500,13 @@
         <v>FORM8</v>
       </c>
       <c r="D293">
-        <v>1279</v>
+        <v>1286</v>
       </c>
       <c r="E293">
         <v>0</v>
       </c>
       <c r="F293">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G293">
         <v>0</v>
@@ -20565,13 +20565,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D294">
-        <v>11044</v>
+        <v>11633</v>
       </c>
       <c r="E294">
         <v>0</v>
       </c>
       <c r="F294">
-        <v>670</v>
+        <v>704</v>
       </c>
       <c r="G294">
         <v>0</v>
@@ -20622,7 +20622,7 @@
         <v>0</v>
       </c>
       <c r="W294">
-        <v>4014</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="295">
@@ -20636,13 +20636,13 @@
         <v>FORM6</v>
       </c>
       <c r="D295">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="E295">
         <v>0</v>
       </c>
       <c r="F295">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G295">
         <v>0</v>
@@ -20778,13 +20778,13 @@
         <v>FORM8</v>
       </c>
       <c r="D297">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="E297">
         <v>0</v>
       </c>
       <c r="F297">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G297">
         <v>0</v>
@@ -20843,13 +20843,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D298">
-        <v>11106</v>
+        <v>11123</v>
       </c>
       <c r="E298">
         <v>0</v>
       </c>
       <c r="F298">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="G298">
         <v>0</v>
@@ -20914,13 +20914,13 @@
         <v>FORM6</v>
       </c>
       <c r="D299">
-        <v>2972</v>
+        <v>2988</v>
       </c>
       <c r="E299">
         <v>0</v>
       </c>
       <c r="F299">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="G299">
         <v>0</v>
@@ -21056,7 +21056,7 @@
         <v>FORM7</v>
       </c>
       <c r="D301">
-        <v>8602</v>
+        <v>8724</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -21077,10 +21077,10 @@
         <v>0</v>
       </c>
       <c r="K301">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L301">
-        <v>1791</v>
+        <v>590</v>
       </c>
       <c r="M301">
         <v>0</v>
@@ -21095,13 +21095,13 @@
         <v>0</v>
       </c>
       <c r="Q301">
-        <v>4932</v>
+        <v>6064</v>
       </c>
       <c r="R301">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T301">
         <v>0</v>
@@ -21113,7 +21113,7 @@
         <v>0</v>
       </c>
       <c r="W301">
-        <v>1623</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="302">
@@ -21127,13 +21127,13 @@
         <v>FORM8</v>
       </c>
       <c r="D302">
-        <v>1441</v>
+        <v>1453</v>
       </c>
       <c r="E302">
         <v>0</v>
       </c>
       <c r="F302">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="G302">
         <v>0</v>
@@ -21192,13 +21192,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D303">
-        <v>13016</v>
+        <v>13166</v>
       </c>
       <c r="E303">
         <v>0</v>
       </c>
       <c r="F303">
-        <v>494</v>
+        <v>522</v>
       </c>
       <c r="G303">
         <v>0</v>
@@ -21213,10 +21213,10 @@
         <v>0</v>
       </c>
       <c r="K303">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L303">
-        <v>1791</v>
+        <v>590</v>
       </c>
       <c r="M303">
         <v>0</v>
@@ -21231,13 +21231,13 @@
         <v>0</v>
       </c>
       <c r="Q303">
-        <v>5078</v>
+        <v>6210</v>
       </c>
       <c r="R303">
-        <v>3868</v>
+        <v>3935</v>
       </c>
       <c r="S303">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T303">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>0</v>
       </c>
       <c r="W303">
-        <v>1659</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="304">
@@ -21263,13 +21263,13 @@
         <v>FORM6</v>
       </c>
       <c r="D304">
-        <v>1791</v>
+        <v>1811</v>
       </c>
       <c r="E304">
         <v>0</v>
       </c>
       <c r="F304">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="G304">
         <v>0</v>
@@ -21334,7 +21334,7 @@
         <v>FORM7</v>
       </c>
       <c r="D305">
-        <v>14405</v>
+        <v>14307</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -21349,16 +21349,16 @@
         <v>0</v>
       </c>
       <c r="I305">
-        <v>2202</v>
+        <v>1959</v>
       </c>
       <c r="J305">
         <v>0</v>
       </c>
       <c r="K305">
-        <v>445</v>
+        <v>1</v>
       </c>
       <c r="L305">
-        <v>4939</v>
+        <v>3799</v>
       </c>
       <c r="M305">
         <v>0</v>
@@ -21373,7 +21373,7 @@
         <v>0</v>
       </c>
       <c r="Q305">
-        <v>3130</v>
+        <v>4859</v>
       </c>
       <c r="R305">
         <v>1</v>
@@ -21405,13 +21405,13 @@
         <v>FORM8</v>
       </c>
       <c r="D306">
-        <v>1136</v>
+        <v>1150</v>
       </c>
       <c r="E306">
         <v>0</v>
       </c>
       <c r="F306">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="G306">
         <v>0</v>
@@ -21470,13 +21470,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D307">
-        <v>17332</v>
+        <v>17268</v>
       </c>
       <c r="E307">
         <v>0</v>
       </c>
       <c r="F307">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -21485,16 +21485,16 @@
         <v>0</v>
       </c>
       <c r="I307">
-        <v>2202</v>
+        <v>1959</v>
       </c>
       <c r="J307">
         <v>0</v>
       </c>
       <c r="K307">
-        <v>445</v>
+        <v>1</v>
       </c>
       <c r="L307">
-        <v>4939</v>
+        <v>3799</v>
       </c>
       <c r="M307">
         <v>0</v>
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="Q307">
-        <v>3233</v>
+        <v>4962</v>
       </c>
       <c r="R307">
         <v>2371</v>
@@ -21541,13 +21541,13 @@
         <v>FORM6</v>
       </c>
       <c r="D308">
-        <v>2423</v>
+        <v>2440</v>
       </c>
       <c r="E308">
         <v>0</v>
       </c>
       <c r="F308">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="G308">
         <v>0</v>
@@ -21612,7 +21612,7 @@
         <v>FORM7</v>
       </c>
       <c r="D309">
-        <v>3008</v>
+        <v>3113</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -21669,7 +21669,7 @@
         <v>0</v>
       </c>
       <c r="W309">
-        <v>1131</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="310">
@@ -21683,13 +21683,13 @@
         <v>FORM8</v>
       </c>
       <c r="D310">
-        <v>1251</v>
+        <v>1266</v>
       </c>
       <c r="E310">
         <v>0</v>
       </c>
       <c r="F310">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="G310">
         <v>0</v>
@@ -21748,13 +21748,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D311">
-        <v>6682</v>
+        <v>6819</v>
       </c>
       <c r="E311">
         <v>0</v>
       </c>
       <c r="F311">
-        <v>551</v>
+        <v>583</v>
       </c>
       <c r="G311">
         <v>0</v>
@@ -21805,7 +21805,7 @@
         <v>0</v>
       </c>
       <c r="W311">
-        <v>1135</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="312">
@@ -21819,13 +21819,13 @@
         <v>FORM6</v>
       </c>
       <c r="D312">
-        <v>1716</v>
+        <v>1735</v>
       </c>
       <c r="E312">
         <v>0</v>
       </c>
       <c r="F312">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="G312">
         <v>0</v>
@@ -21961,13 +21961,13 @@
         <v>FORM8</v>
       </c>
       <c r="D314">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E314">
         <v>0</v>
       </c>
       <c r="F314">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G314">
         <v>0</v>
@@ -22026,13 +22026,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D315">
-        <v>5626</v>
+        <v>5646</v>
       </c>
       <c r="E315">
         <v>0</v>
       </c>
       <c r="F315">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="G315">
         <v>0</v>
@@ -22097,16 +22097,16 @@
         <v>FORM6</v>
       </c>
       <c r="D316">
-        <v>1355</v>
+        <v>1374</v>
       </c>
       <c r="E316">
         <v>0</v>
       </c>
       <c r="F316">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="G316">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H316">
         <v>0</v>
@@ -22115,7 +22115,7 @@
         <v>0</v>
       </c>
       <c r="J316">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K316">
         <v>0</v>
@@ -22127,7 +22127,7 @@
         <v>0</v>
       </c>
       <c r="N316">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O316">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>4</v>
       </c>
       <c r="R316">
-        <v>1017</v>
+        <v>1059</v>
       </c>
       <c r="S316">
         <v>0</v>
@@ -22239,7 +22239,7 @@
         <v>FORM7</v>
       </c>
       <c r="D318">
-        <v>2290</v>
+        <v>2325</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -22278,7 +22278,7 @@
         <v>0</v>
       </c>
       <c r="Q318">
-        <v>725</v>
+        <v>1194</v>
       </c>
       <c r="R318">
         <v>7</v>
@@ -22290,13 +22290,13 @@
         <v>0</v>
       </c>
       <c r="U318">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="V318">
         <v>0</v>
       </c>
       <c r="W318">
-        <v>1086</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="319">
@@ -22310,16 +22310,16 @@
         <v>FORM8</v>
       </c>
       <c r="D319">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="E319">
         <v>0</v>
       </c>
       <c r="F319">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G319">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H319">
         <v>0</v>
@@ -22352,7 +22352,7 @@
         <v>59</v>
       </c>
       <c r="R319">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="S319">
         <v>0</v>
@@ -22375,16 +22375,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D320">
-        <v>4406</v>
+        <v>4469</v>
       </c>
       <c r="E320">
         <v>0</v>
       </c>
       <c r="F320">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="G320">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="H320">
         <v>0</v>
@@ -22393,7 +22393,7 @@
         <v>0</v>
       </c>
       <c r="J320">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K320">
         <v>0</v>
@@ -22405,7 +22405,7 @@
         <v>0</v>
       </c>
       <c r="N320">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O320">
         <v>0</v>
@@ -22414,10 +22414,10 @@
         <v>0</v>
       </c>
       <c r="Q320">
-        <v>789</v>
+        <v>1258</v>
       </c>
       <c r="R320">
-        <v>1616</v>
+        <v>1673</v>
       </c>
       <c r="S320">
         <v>0</v>
@@ -22426,13 +22426,13 @@
         <v>0</v>
       </c>
       <c r="U320">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="V320">
         <v>0</v>
       </c>
       <c r="W320">
-        <v>1086</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="321">
@@ -22440,49 +22440,49 @@
         <v>All AC Form-6 Total</v>
       </c>
       <c r="D321">
-        <v>164964</v>
+        <v>165627</v>
       </c>
       <c r="E321">
         <v>0</v>
       </c>
       <c r="F321">
-        <v>13911</v>
+        <v>14559</v>
       </c>
       <c r="G321">
-        <v>567</v>
+        <v>429</v>
       </c>
       <c r="H321">
         <v>92</v>
       </c>
       <c r="I321">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J321">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K321">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="L321">
-        <v>1843</v>
+        <v>131</v>
       </c>
       <c r="M321">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N321">
-        <v>7785</v>
+        <v>7753</v>
       </c>
       <c r="O321">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P321">
         <v>0</v>
       </c>
       <c r="Q321">
-        <v>15815</v>
+        <v>16623</v>
       </c>
       <c r="R321">
-        <v>103391</v>
+        <v>104577</v>
       </c>
       <c r="S321">
         <v>0</v>
@@ -22491,7 +22491,7 @@
         <v>0</v>
       </c>
       <c r="U321">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V321">
         <v>0</v>
@@ -22505,16 +22505,16 @@
         <v>All AC Form-6A Total</v>
       </c>
       <c r="D322">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E322">
         <v>0</v>
       </c>
       <c r="F322">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G322">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H322">
         <v>0</v>
@@ -22526,7 +22526,7 @@
         <v>0</v>
       </c>
       <c r="K322">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L322">
         <v>0</v>
@@ -22544,10 +22544,10 @@
         <v>0</v>
       </c>
       <c r="Q322">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="R322">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="S322">
         <v>0</v>
@@ -22570,31 +22570,31 @@
         <v>All AC Form-7 Total</v>
       </c>
       <c r="D323">
-        <v>166500</v>
+        <v>174152</v>
       </c>
       <c r="E323">
         <v>0</v>
       </c>
       <c r="F323">
-        <v>3093</v>
+        <v>394</v>
       </c>
       <c r="G323">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H323">
         <v>0</v>
       </c>
       <c r="I323">
-        <v>2395</v>
+        <v>1959</v>
       </c>
       <c r="J323">
         <v>0</v>
       </c>
       <c r="K323">
-        <v>890</v>
+        <v>419</v>
       </c>
       <c r="L323">
-        <v>9009</v>
+        <v>5185</v>
       </c>
       <c r="M323">
         <v>1</v>
@@ -22609,25 +22609,25 @@
         <v>0</v>
       </c>
       <c r="Q323">
-        <v>73947</v>
+        <v>81369</v>
       </c>
       <c r="R323">
-        <v>5958</v>
+        <v>6338</v>
       </c>
       <c r="S323">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T323">
         <v>0</v>
       </c>
       <c r="U323">
-        <v>470</v>
+        <v>1</v>
       </c>
       <c r="V323">
         <v>0</v>
       </c>
       <c r="W323">
-        <v>70242</v>
+        <v>77991</v>
       </c>
     </row>
     <row r="324">
@@ -22635,16 +22635,16 @@
         <v>All AC Form-8 Total</v>
       </c>
       <c r="D324">
-        <v>62685</v>
+        <v>63064</v>
       </c>
       <c r="E324">
         <v>0</v>
       </c>
       <c r="F324">
-        <v>6587</v>
+        <v>6967</v>
       </c>
       <c r="G324">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="H324">
         <v>0</v>
@@ -22653,10 +22653,10 @@
         <v>0</v>
       </c>
       <c r="J324">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K324">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="L324">
         <v>10</v>
@@ -22665,7 +22665,7 @@
         <v>1</v>
       </c>
       <c r="N324">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="O324">
         <v>2</v>
@@ -22674,10 +22674,10 @@
         <v>0</v>
       </c>
       <c r="Q324">
-        <v>5337</v>
+        <v>5343</v>
       </c>
       <c r="R324">
-        <v>35450</v>
+        <v>35472</v>
       </c>
       <c r="S324">
         <v>0</v>
@@ -22700,64 +22700,64 @@
         <v>All AC Form Total</v>
       </c>
       <c r="D325">
-        <v>394291</v>
+        <v>402986</v>
       </c>
       <c r="E325">
         <v>0</v>
       </c>
       <c r="F325">
-        <v>23613</v>
+        <v>21940</v>
       </c>
       <c r="G325">
-        <v>1027</v>
+        <v>835</v>
       </c>
       <c r="H325">
         <v>92</v>
       </c>
       <c r="I325">
-        <v>2398</v>
+        <v>1963</v>
       </c>
       <c r="J325">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="K325">
-        <v>1067</v>
+        <v>500</v>
       </c>
       <c r="L325">
-        <v>10862</v>
+        <v>5326</v>
       </c>
       <c r="M325">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N325">
-        <v>9524</v>
+        <v>9494</v>
       </c>
       <c r="O325">
+        <v>4</v>
+      </c>
+      <c r="P325">
+        <v>0</v>
+      </c>
+      <c r="Q325">
+        <v>103404</v>
+      </c>
+      <c r="R325">
+        <v>146435</v>
+      </c>
+      <c r="S325">
         <v>7</v>
       </c>
-      <c r="P325">
-        <v>0</v>
-      </c>
-      <c r="Q325">
-        <v>95165</v>
-      </c>
-      <c r="R325">
-        <v>144843</v>
-      </c>
-      <c r="S325">
-        <v>0</v>
-      </c>
       <c r="T325">
         <v>0</v>
       </c>
       <c r="U325">
-        <v>482</v>
+        <v>10</v>
       </c>
       <c r="V325">
         <v>0</v>
       </c>
       <c r="W325">
-        <v>105082</v>
+        <v>112831</v>
       </c>
     </row>
   </sheetData>

--- a/Form_Processing.xlsx
+++ b/Form_Processing.xlsx
@@ -411,7 +411,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>From - 15/07/2026       To - 28/09/2026</v>
+        <v>From - 15/07/2026       To - 29/09/2026</v>
       </c>
     </row>
     <row r="4">
@@ -501,13 +501,13 @@
         <v>FORM6</v>
       </c>
       <c r="D6">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>12</v>
@@ -708,13 +708,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D9">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9">
         <v>21</v>
@@ -850,7 +850,7 @@
         <v>FORM7</v>
       </c>
       <c r="D11">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -986,7 +986,7 @@
         <v>AC Form Total</v>
       </c>
       <c r="D13">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1057,13 +1057,13 @@
         <v>FORM6</v>
       </c>
       <c r="D14">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1199,13 +1199,13 @@
         <v>FORM8</v>
       </c>
       <c r="D16">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D17">
-        <v>2772</v>
+        <v>2775</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1335,13 +1335,13 @@
         <v>FORM6</v>
       </c>
       <c r="D18">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -1548,13 +1548,13 @@
         <v>FORM8</v>
       </c>
       <c r="D21">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D22">
-        <v>3706</v>
+        <v>3708</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -1826,13 +1826,13 @@
         <v>FORM8</v>
       </c>
       <c r="D25">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D26">
-        <v>3579</v>
+        <v>3581</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>FORM6</v>
       </c>
       <c r="D32">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -2589,13 +2589,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D36">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -2802,13 +2802,13 @@
         <v>FORM8</v>
       </c>
       <c r="D39">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -2867,13 +2867,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D40">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -3080,13 +3080,13 @@
         <v>FORM8</v>
       </c>
       <c r="D43">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D44">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>FORM6</v>
       </c>
       <c r="D45">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -3358,13 +3358,13 @@
         <v>FORM8</v>
       </c>
       <c r="D47">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -3423,13 +3423,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D48">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -3494,13 +3494,13 @@
         <v>FORM6</v>
       </c>
       <c r="D49">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -3772,13 +3772,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D53">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -4683,13 +4683,13 @@
         <v>FORM8</v>
       </c>
       <c r="D66">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E66">
         <v>0</v>
       </c>
       <c r="F66">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -4748,13 +4748,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D67">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E67">
         <v>0</v>
       </c>
       <c r="F67">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -4961,13 +4961,13 @@
         <v>FORM8</v>
       </c>
       <c r="D70">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D71">
-        <v>4982</v>
+        <v>4993</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -5097,13 +5097,13 @@
         <v>FORM6</v>
       </c>
       <c r="D72">
-        <v>3738</v>
+        <v>3740</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G72">
         <v>6</v>
@@ -5310,13 +5310,13 @@
         <v>FORM8</v>
       </c>
       <c r="D75">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="E75">
         <v>0</v>
       </c>
       <c r="F75">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -5375,13 +5375,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D76">
-        <v>9125</v>
+        <v>9128</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G76">
         <v>6</v>
@@ -5446,13 +5446,13 @@
         <v>FORM6</v>
       </c>
       <c r="D77">
-        <v>4853</v>
+        <v>4865</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -5659,13 +5659,13 @@
         <v>FORM8</v>
       </c>
       <c r="D80">
-        <v>1583</v>
+        <v>1590</v>
       </c>
       <c r="E80">
         <v>0</v>
       </c>
       <c r="F80">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -5724,13 +5724,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D81">
-        <v>11233</v>
+        <v>11252</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="F81">
-        <v>690</v>
+        <v>709</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -5795,13 +5795,13 @@
         <v>FORM6</v>
       </c>
       <c r="D82">
-        <v>9864</v>
+        <v>9888</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82">
-        <v>832</v>
+        <v>856</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -5837,10 +5837,10 @@
         <v>820</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82">
         <v>0</v>
@@ -6008,13 +6008,13 @@
         <v>FORM8</v>
       </c>
       <c r="D85">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -6053,13 +6053,13 @@
         <v>0</v>
       </c>
       <c r="S85">
+        <v>0</v>
+      </c>
+      <c r="T85">
+        <v>0</v>
+      </c>
+      <c r="U85">
         <v>1</v>
-      </c>
-      <c r="T85">
-        <v>0</v>
-      </c>
-      <c r="U85">
-        <v>0</v>
       </c>
       <c r="V85">
         <v>0</v>
@@ -6073,13 +6073,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D86">
-        <v>17204</v>
+        <v>17230</v>
       </c>
       <c r="E86">
         <v>0</v>
       </c>
       <c r="F86">
-        <v>1105</v>
+        <v>1131</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -6115,16 +6115,16 @@
         <v>1965</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T86">
         <v>0</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V86">
         <v>0</v>
@@ -6144,13 +6144,13 @@
         <v>FORM6</v>
       </c>
       <c r="D87">
-        <v>4979</v>
+        <v>4984</v>
       </c>
       <c r="E87">
         <v>0</v>
       </c>
       <c r="F87">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -6286,13 +6286,13 @@
         <v>FORM7</v>
       </c>
       <c r="D89">
-        <v>3774</v>
+        <v>3779</v>
       </c>
       <c r="E89">
         <v>0</v>
       </c>
       <c r="F89">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -6325,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>1948</v>
+        <v>1953</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="W89">
-        <v>1801</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="90">
@@ -6357,13 +6357,13 @@
         <v>FORM8</v>
       </c>
       <c r="D90">
-        <v>1798</v>
+        <v>1802</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
       <c r="F90">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -6422,13 +6422,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D91">
-        <v>10557</v>
+        <v>10571</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -6461,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="Q91">
-        <v>3012</v>
+        <v>3017</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -6479,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="W91">
-        <v>6230</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="92">
@@ -6493,13 +6493,13 @@
         <v>FORM6</v>
       </c>
       <c r="D92">
-        <v>4042</v>
+        <v>4044</v>
       </c>
       <c r="E92">
         <v>0</v>
       </c>
       <c r="F92">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -6771,13 +6771,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D96">
-        <v>9097</v>
+        <v>9099</v>
       </c>
       <c r="E96">
         <v>0</v>
       </c>
       <c r="F96">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -6842,13 +6842,13 @@
         <v>FORM6</v>
       </c>
       <c r="D97">
-        <v>3547</v>
+        <v>3550</v>
       </c>
       <c r="E97">
         <v>0</v>
       </c>
       <c r="F97">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -6984,7 +6984,7 @@
         <v>FORM7</v>
       </c>
       <c r="D99">
-        <v>3713</v>
+        <v>3715</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -7041,7 +7041,7 @@
         <v>0</v>
       </c>
       <c r="W99">
-        <v>3347</v>
+        <v>3349</v>
       </c>
     </row>
     <row r="100">
@@ -7120,13 +7120,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D101">
-        <v>8644</v>
+        <v>8649</v>
       </c>
       <c r="E101">
         <v>0</v>
       </c>
       <c r="F101">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -7177,7 +7177,7 @@
         <v>0</v>
       </c>
       <c r="W101">
-        <v>7042</v>
+        <v>7044</v>
       </c>
     </row>
     <row r="102">
@@ -7191,13 +7191,13 @@
         <v>FORM6</v>
       </c>
       <c r="D102">
-        <v>4969</v>
+        <v>4971</v>
       </c>
       <c r="E102">
         <v>0</v>
       </c>
       <c r="F102">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -7469,13 +7469,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D106">
-        <v>12112</v>
+        <v>12114</v>
       </c>
       <c r="E106">
         <v>0</v>
       </c>
       <c r="F106">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -7540,13 +7540,13 @@
         <v>FORM6</v>
       </c>
       <c r="D107">
-        <v>5309</v>
+        <v>5314</v>
       </c>
       <c r="E107">
         <v>0</v>
       </c>
       <c r="F107">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -7682,13 +7682,13 @@
         <v>FORM7</v>
       </c>
       <c r="D109">
-        <v>5080</v>
+        <v>5086</v>
       </c>
       <c r="E109">
         <v>0</v>
       </c>
       <c r="F109">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -7721,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="R109">
         <v>1</v>
@@ -7739,7 +7739,7 @@
         <v>0</v>
       </c>
       <c r="W109">
-        <v>3895</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="110">
@@ -7753,13 +7753,13 @@
         <v>FORM8</v>
       </c>
       <c r="D110">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="F110">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -7818,13 +7818,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D111">
-        <v>12580</v>
+        <v>12593</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="Q111">
-        <v>2037</v>
+        <v>2043</v>
       </c>
       <c r="R111">
         <v>1</v>
@@ -7875,7 +7875,7 @@
         <v>0</v>
       </c>
       <c r="W111">
-        <v>9249</v>
+        <v>9255</v>
       </c>
     </row>
     <row r="112">
@@ -7889,13 +7889,13 @@
         <v>FORM6</v>
       </c>
       <c r="D112">
-        <v>5331</v>
+        <v>5342</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
       <c r="F112">
-        <v>814</v>
+        <v>825</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -8031,13 +8031,13 @@
         <v>FORM7</v>
       </c>
       <c r="D114">
-        <v>4796</v>
+        <v>4797</v>
       </c>
       <c r="E114">
         <v>0</v>
       </c>
       <c r="F114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -8070,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="Q114">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="R114">
         <v>0</v>
@@ -8088,7 +8088,7 @@
         <v>0</v>
       </c>
       <c r="W114">
-        <v>3968</v>
+        <v>3969</v>
       </c>
     </row>
     <row r="115">
@@ -8102,13 +8102,13 @@
         <v>FORM8</v>
       </c>
       <c r="D115">
-        <v>1451</v>
+        <v>1456</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -8167,13 +8167,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D116">
-        <v>11582</v>
+        <v>11599</v>
       </c>
       <c r="E116">
         <v>0</v>
       </c>
       <c r="F116">
-        <v>1168</v>
+        <v>1183</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -8206,7 +8206,7 @@
         <v>0</v>
       </c>
       <c r="Q116">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -8224,7 +8224,7 @@
         <v>0</v>
       </c>
       <c r="W116">
-        <v>7770</v>
+        <v>7771</v>
       </c>
     </row>
     <row r="117">
@@ -8238,13 +8238,13 @@
         <v>FORM6</v>
       </c>
       <c r="D117">
-        <v>5767</v>
+        <v>5771</v>
       </c>
       <c r="E117">
         <v>0</v>
       </c>
       <c r="F117">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G117">
         <v>5</v>
@@ -8309,13 +8309,13 @@
         <v>FORM7</v>
       </c>
       <c r="D118">
-        <v>1200</v>
+        <v>1205</v>
       </c>
       <c r="E118">
         <v>0</v>
       </c>
       <c r="F118">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G118">
         <v>4</v>
@@ -8348,14 +8348,14 @@
         <v>0</v>
       </c>
       <c r="Q118">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="R118">
+        <v>0</v>
+      </c>
+      <c r="S118">
         <v>1</v>
       </c>
-      <c r="S118">
-        <v>0</v>
-      </c>
       <c r="T118">
         <v>0</v>
       </c>
@@ -8366,7 +8366,7 @@
         <v>0</v>
       </c>
       <c r="W118">
-        <v>1044</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="119">
@@ -8380,13 +8380,13 @@
         <v>FORM8</v>
       </c>
       <c r="D119">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
       <c r="F119">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -8445,13 +8445,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D120">
-        <v>7867</v>
+        <v>7880</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="G120">
         <v>9</v>
@@ -8484,14 +8484,14 @@
         <v>0</v>
       </c>
       <c r="Q120">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="R120">
+        <v>0</v>
+      </c>
+      <c r="S120">
         <v>1</v>
       </c>
-      <c r="S120">
-        <v>0</v>
-      </c>
       <c r="T120">
         <v>0</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="W120">
-        <v>7042</v>
+        <v>7047</v>
       </c>
     </row>
     <row r="121">
@@ -8516,13 +8516,13 @@
         <v>FORM6</v>
       </c>
       <c r="D121">
-        <v>4567</v>
+        <v>4574</v>
       </c>
       <c r="E121">
         <v>0</v>
       </c>
       <c r="F121">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="G121">
         <v>6</v>
@@ -8729,13 +8729,13 @@
         <v>FORM8</v>
       </c>
       <c r="D124">
-        <v>1595</v>
+        <v>1601</v>
       </c>
       <c r="E124">
         <v>0</v>
       </c>
       <c r="F124">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -8794,13 +8794,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D125">
-        <v>9385</v>
+        <v>9398</v>
       </c>
       <c r="E125">
         <v>0</v>
       </c>
       <c r="F125">
-        <v>715</v>
+        <v>728</v>
       </c>
       <c r="G125">
         <v>13</v>
@@ -8865,13 +8865,13 @@
         <v>FORM6</v>
       </c>
       <c r="D126">
-        <v>2472</v>
+        <v>2476</v>
       </c>
       <c r="E126">
         <v>0</v>
       </c>
       <c r="F126">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -9007,7 +9007,7 @@
         <v>FORM7</v>
       </c>
       <c r="D128">
-        <v>4248</v>
+        <v>4258</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -9016,7 +9016,7 @@
         <v>0</v>
       </c>
       <c r="G128">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -9037,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="N128">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="Q128">
-        <v>2055</v>
+        <v>2065</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -9064,7 +9064,7 @@
         <v>0</v>
       </c>
       <c r="W128">
-        <v>1979</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="129">
@@ -9078,13 +9078,13 @@
         <v>FORM8</v>
       </c>
       <c r="D129">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="E129">
         <v>0</v>
       </c>
       <c r="F129">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -9143,16 +9143,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D130">
-        <v>7724</v>
+        <v>7742</v>
       </c>
       <c r="E130">
         <v>0</v>
       </c>
       <c r="F130">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="G130">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="H130">
         <v>3</v>
@@ -9173,7 +9173,7 @@
         <v>1</v>
       </c>
       <c r="N130">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O130">
         <v>5</v>
@@ -9182,7 +9182,7 @@
         <v>0</v>
       </c>
       <c r="Q130">
-        <v>3205</v>
+        <v>3215</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -9200,7 +9200,7 @@
         <v>0</v>
       </c>
       <c r="W130">
-        <v>3712</v>
+        <v>3722</v>
       </c>
     </row>
     <row r="131">
@@ -9214,13 +9214,13 @@
         <v>FORM6</v>
       </c>
       <c r="D131">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="E131">
         <v>0</v>
       </c>
       <c r="F131">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G131">
         <v>98</v>
@@ -9285,13 +9285,13 @@
         <v>FORM7</v>
       </c>
       <c r="D132">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="E132">
         <v>0</v>
       </c>
       <c r="F132">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -9324,7 +9324,7 @@
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -9342,7 +9342,7 @@
         <v>0</v>
       </c>
       <c r="W132">
-        <v>2061</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="133">
@@ -9356,13 +9356,13 @@
         <v>FORM8</v>
       </c>
       <c r="D133">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="E133">
         <v>0</v>
       </c>
       <c r="F133">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G133">
         <v>6</v>
@@ -9421,13 +9421,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D134">
-        <v>4981</v>
+        <v>4987</v>
       </c>
       <c r="E134">
         <v>0</v>
       </c>
       <c r="F134">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G134">
         <v>105</v>
@@ -9460,7 +9460,7 @@
         <v>0</v>
       </c>
       <c r="Q134">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -9478,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="W134">
-        <v>3689</v>
+        <v>3691</v>
       </c>
     </row>
     <row r="135">
@@ -9492,13 +9492,13 @@
         <v>FORM6</v>
       </c>
       <c r="D135">
-        <v>1717</v>
+        <v>1720</v>
       </c>
       <c r="E135">
         <v>0</v>
       </c>
       <c r="F135">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G135">
         <v>27</v>
@@ -9705,13 +9705,13 @@
         <v>FORM8</v>
       </c>
       <c r="D138">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="E138">
         <v>0</v>
       </c>
       <c r="F138">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -9770,13 +9770,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D139">
-        <v>9113</v>
+        <v>9119</v>
       </c>
       <c r="E139">
         <v>0</v>
       </c>
       <c r="F139">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="G139">
         <v>27</v>
@@ -9841,13 +9841,13 @@
         <v>FORM6</v>
       </c>
       <c r="D140">
-        <v>2435</v>
+        <v>2440</v>
       </c>
       <c r="E140">
         <v>0</v>
       </c>
       <c r="F140">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G140">
         <v>81</v>
@@ -9912,7 +9912,7 @@
         <v>FORM7</v>
       </c>
       <c r="D141">
-        <v>3113</v>
+        <v>3115</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -9921,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="G141">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H141">
         <v>0</v>
@@ -9951,7 +9951,7 @@
         <v>0</v>
       </c>
       <c r="Q141">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="R141">
         <v>0</v>
@@ -9969,7 +9969,7 @@
         <v>0</v>
       </c>
       <c r="W141">
-        <v>1377</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="142">
@@ -9983,13 +9983,13 @@
         <v>FORM8</v>
       </c>
       <c r="D142">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="E142">
         <v>0</v>
       </c>
       <c r="F142">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G142">
         <v>51</v>
@@ -10048,16 +10048,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D143">
-        <v>6834</v>
+        <v>6843</v>
       </c>
       <c r="E143">
         <v>0</v>
       </c>
       <c r="F143">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="G143">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -10087,7 +10087,7 @@
         <v>0</v>
       </c>
       <c r="Q143">
-        <v>3507</v>
+        <v>3509</v>
       </c>
       <c r="R143">
         <v>3</v>
@@ -10105,7 +10105,7 @@
         <v>0</v>
       </c>
       <c r="W143">
-        <v>2876</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="144">
@@ -10119,13 +10119,13 @@
         <v>FORM6</v>
       </c>
       <c r="D144">
-        <v>3029</v>
+        <v>3034</v>
       </c>
       <c r="E144">
         <v>0</v>
       </c>
       <c r="F144">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G144">
         <v>35</v>
@@ -10261,13 +10261,13 @@
         <v>FORM7</v>
       </c>
       <c r="D146">
-        <v>2065</v>
+        <v>2074</v>
       </c>
       <c r="E146">
         <v>0</v>
       </c>
       <c r="F146">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -10300,7 +10300,7 @@
         <v>0</v>
       </c>
       <c r="Q146">
-        <v>1136</v>
+        <v>1145</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -10318,7 +10318,7 @@
         <v>0</v>
       </c>
       <c r="W146">
-        <v>916</v>
+        <v>925</v>
       </c>
     </row>
     <row r="147">
@@ -10332,13 +10332,13 @@
         <v>FORM8</v>
       </c>
       <c r="D147">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G147">
         <v>32</v>
@@ -10397,13 +10397,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D148">
-        <v>6673</v>
+        <v>6688</v>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
       <c r="F148">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="G148">
         <v>68</v>
@@ -10436,7 +10436,7 @@
         <v>0</v>
       </c>
       <c r="Q148">
-        <v>2247</v>
+        <v>2256</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -10454,7 +10454,7 @@
         <v>0</v>
       </c>
       <c r="W148">
-        <v>3808</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="149">
@@ -10468,13 +10468,13 @@
         <v>FORM6</v>
       </c>
       <c r="D149">
-        <v>2481</v>
+        <v>2485</v>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
       <c r="F149">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -10681,13 +10681,13 @@
         <v>FORM8</v>
       </c>
       <c r="D152">
-        <v>1265</v>
+        <v>1272</v>
       </c>
       <c r="E152">
         <v>0</v>
       </c>
       <c r="F152">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -10746,13 +10746,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D153">
-        <v>6592</v>
+        <v>6603</v>
       </c>
       <c r="E153">
         <v>0</v>
       </c>
       <c r="F153">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -10817,13 +10817,13 @@
         <v>FORM6</v>
       </c>
       <c r="D154">
-        <v>3244</v>
+        <v>3253</v>
       </c>
       <c r="E154">
         <v>0</v>
       </c>
       <c r="F154">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -10888,7 +10888,7 @@
         <v>FORM7</v>
       </c>
       <c r="D155">
-        <v>3034</v>
+        <v>3036</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -10927,7 +10927,7 @@
         <v>0</v>
       </c>
       <c r="Q155">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="R155">
         <v>0</v>
@@ -10945,7 +10945,7 @@
         <v>0</v>
       </c>
       <c r="W155">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="156">
@@ -11024,13 +11024,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D157">
-        <v>7551</v>
+        <v>7562</v>
       </c>
       <c r="E157">
         <v>0</v>
       </c>
       <c r="F157">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -11063,7 +11063,7 @@
         <v>0</v>
       </c>
       <c r="Q157">
-        <v>3575</v>
+        <v>3576</v>
       </c>
       <c r="R157">
         <v>0</v>
@@ -11081,7 +11081,7 @@
         <v>0</v>
       </c>
       <c r="W157">
-        <v>3143</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="158">
@@ -11095,16 +11095,16 @@
         <v>FORM6</v>
       </c>
       <c r="D158">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="E158">
         <v>0</v>
       </c>
       <c r="F158">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158">
         <v>0</v>
@@ -11134,7 +11134,7 @@
         <v>0</v>
       </c>
       <c r="Q158">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="R158">
         <v>0</v>
@@ -11166,7 +11166,7 @@
         <v>FORM7</v>
       </c>
       <c r="D159">
-        <v>4033</v>
+        <v>4044</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -11205,7 +11205,7 @@
         <v>0</v>
       </c>
       <c r="Q159">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="R159">
         <v>0</v>
@@ -11223,7 +11223,7 @@
         <v>0</v>
       </c>
       <c r="W159">
-        <v>3839</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="160">
@@ -11237,16 +11237,16 @@
         <v>FORM8</v>
       </c>
       <c r="D160">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="E160">
         <v>0</v>
       </c>
       <c r="F160">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G160">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H160">
         <v>0</v>
@@ -11276,7 +11276,7 @@
         <v>0</v>
       </c>
       <c r="Q160">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="R160">
         <v>0</v>
@@ -11302,16 +11302,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D161">
-        <v>6953</v>
+        <v>6972</v>
       </c>
       <c r="E161">
         <v>0</v>
       </c>
       <c r="F161">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="G161">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -11341,7 +11341,7 @@
         <v>0</v>
       </c>
       <c r="Q161">
-        <v>862</v>
+        <v>888</v>
       </c>
       <c r="R161">
         <v>0</v>
@@ -11359,7 +11359,7 @@
         <v>0</v>
       </c>
       <c r="W161">
-        <v>5627</v>
+        <v>5628</v>
       </c>
     </row>
     <row r="162">
@@ -11373,13 +11373,13 @@
         <v>FORM6</v>
       </c>
       <c r="D162">
-        <v>3668</v>
+        <v>3670</v>
       </c>
       <c r="E162">
         <v>0</v>
       </c>
       <c r="F162">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G162">
         <v>0</v>
@@ -11515,13 +11515,13 @@
         <v>FORM8</v>
       </c>
       <c r="D164">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="E164">
         <v>0</v>
       </c>
       <c r="F164">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G164">
         <v>0</v>
@@ -11580,13 +11580,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D165">
-        <v>12505</v>
+        <v>12509</v>
       </c>
       <c r="E165">
         <v>0</v>
       </c>
       <c r="F165">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G165">
         <v>7</v>
@@ -11651,13 +11651,13 @@
         <v>FORM6</v>
       </c>
       <c r="D166">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="E166">
         <v>0</v>
       </c>
       <c r="F166">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G166">
         <v>40</v>
@@ -11722,13 +11722,13 @@
         <v>FORM7</v>
       </c>
       <c r="D167">
-        <v>1232</v>
+        <v>1239</v>
       </c>
       <c r="E167">
         <v>0</v>
       </c>
       <c r="F167">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G167">
         <v>0</v>
@@ -11761,7 +11761,7 @@
         <v>0</v>
       </c>
       <c r="Q167">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="R167">
         <v>0</v>
@@ -11779,7 +11779,7 @@
         <v>0</v>
       </c>
       <c r="W167">
-        <v>646</v>
+        <v>653</v>
       </c>
     </row>
     <row r="168">
@@ -11793,13 +11793,13 @@
         <v>FORM8</v>
       </c>
       <c r="D168">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E168">
         <v>0</v>
       </c>
       <c r="F168">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G168">
         <v>0</v>
@@ -11858,13 +11858,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D169">
-        <v>2873</v>
+        <v>2885</v>
       </c>
       <c r="E169">
         <v>0</v>
       </c>
       <c r="F169">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G169">
         <v>40</v>
@@ -11897,7 +11897,7 @@
         <v>0</v>
       </c>
       <c r="Q169">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="R169">
         <v>0</v>
@@ -11915,7 +11915,7 @@
         <v>0</v>
       </c>
       <c r="W169">
-        <v>2095</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="170">
@@ -11929,13 +11929,13 @@
         <v>FORM6</v>
       </c>
       <c r="D170">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E170">
         <v>0</v>
       </c>
       <c r="F170">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G170">
         <v>5</v>
@@ -12207,13 +12207,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D174">
-        <v>1591</v>
+        <v>1594</v>
       </c>
       <c r="E174">
         <v>0</v>
       </c>
       <c r="F174">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G174">
         <v>10</v>
@@ -12349,13 +12349,13 @@
         <v>FORM7</v>
       </c>
       <c r="D176">
-        <v>1300</v>
+        <v>1345</v>
       </c>
       <c r="E176">
         <v>0</v>
       </c>
       <c r="F176">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G176">
         <v>0</v>
@@ -12388,7 +12388,7 @@
         <v>0</v>
       </c>
       <c r="Q176">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="R176">
         <v>0</v>
@@ -12406,7 +12406,7 @@
         <v>0</v>
       </c>
       <c r="W176">
-        <v>375</v>
+        <v>420</v>
       </c>
     </row>
     <row r="177">
@@ -12420,13 +12420,13 @@
         <v>FORM8</v>
       </c>
       <c r="D177">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E177">
         <v>0</v>
       </c>
       <c r="F177">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G177">
         <v>2</v>
@@ -12485,13 +12485,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D178">
-        <v>3543</v>
+        <v>3590</v>
       </c>
       <c r="E178">
         <v>0</v>
       </c>
       <c r="F178">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G178">
         <v>14</v>
@@ -12524,7 +12524,7 @@
         <v>0</v>
       </c>
       <c r="Q178">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="R178">
         <v>0</v>
@@ -12542,7 +12542,7 @@
         <v>0</v>
       </c>
       <c r="W178">
-        <v>2344</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="179">
@@ -12556,13 +12556,13 @@
         <v>FORM6</v>
       </c>
       <c r="D179">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E179">
         <v>0</v>
       </c>
       <c r="F179">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G179">
         <v>0</v>
@@ -12698,13 +12698,13 @@
         <v>FORM8</v>
       </c>
       <c r="D181">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E181">
         <v>0</v>
       </c>
       <c r="F181">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G181">
         <v>0</v>
@@ -12763,13 +12763,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D182">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="E182">
         <v>0</v>
       </c>
       <c r="F182">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G182">
         <v>22</v>
@@ -12834,13 +12834,13 @@
         <v>FORM6</v>
       </c>
       <c r="D183">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="E183">
         <v>0</v>
       </c>
       <c r="F183">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G183">
         <v>0</v>
@@ -13041,13 +13041,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D186">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="E186">
         <v>0</v>
       </c>
       <c r="F186">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G186">
         <v>0</v>
@@ -13112,13 +13112,13 @@
         <v>FORM6</v>
       </c>
       <c r="D187">
-        <v>2713</v>
+        <v>2720</v>
       </c>
       <c r="E187">
         <v>0</v>
       </c>
       <c r="F187">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G187">
         <v>0</v>
@@ -13325,13 +13325,13 @@
         <v>FORM8</v>
       </c>
       <c r="D190">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="E190">
         <v>0</v>
       </c>
       <c r="F190">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G190">
         <v>0</v>
@@ -13390,13 +13390,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D191">
-        <v>4891</v>
+        <v>4901</v>
       </c>
       <c r="E191">
         <v>0</v>
       </c>
       <c r="F191">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="G191">
         <v>0</v>
@@ -13881,13 +13881,13 @@
         <v>FORM8</v>
       </c>
       <c r="D198">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E198">
         <v>0</v>
       </c>
       <c r="F198">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G198">
         <v>0</v>
@@ -13946,13 +13946,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D199">
-        <v>2368</v>
+        <v>2370</v>
       </c>
       <c r="E199">
         <v>0</v>
       </c>
       <c r="F199">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G199">
         <v>0</v>
@@ -14230,13 +14230,13 @@
         <v>FORM8</v>
       </c>
       <c r="D203">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E203">
         <v>0</v>
       </c>
       <c r="F203">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G203">
         <v>0</v>
@@ -14295,13 +14295,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D204">
-        <v>3058</v>
+        <v>3060</v>
       </c>
       <c r="E204">
         <v>0</v>
       </c>
       <c r="F204">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G204">
         <v>0</v>
@@ -14366,13 +14366,13 @@
         <v>FORM6</v>
       </c>
       <c r="D205">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E205">
         <v>0</v>
       </c>
       <c r="F205">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G205">
         <v>0</v>
@@ -14508,13 +14508,13 @@
         <v>FORM8</v>
       </c>
       <c r="D207">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E207">
         <v>0</v>
       </c>
       <c r="F207">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G207">
         <v>0</v>
@@ -14573,13 +14573,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D208">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="E208">
         <v>0</v>
       </c>
       <c r="F208">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G208">
         <v>0</v>
@@ -14993,13 +14993,13 @@
         <v>FORM7</v>
       </c>
       <c r="D214">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E214">
         <v>0</v>
       </c>
       <c r="F214">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G214">
         <v>1</v>
@@ -15032,7 +15032,7 @@
         <v>0</v>
       </c>
       <c r="Q214">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -15050,7 +15050,7 @@
         <v>0</v>
       </c>
       <c r="W214">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="215">
@@ -15064,13 +15064,13 @@
         <v>FORM8</v>
       </c>
       <c r="D215">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E215">
         <v>0</v>
       </c>
       <c r="F215">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G215">
         <v>1</v>
@@ -15129,7 +15129,7 @@
         <v>AC Form Total</v>
       </c>
       <c r="D216">
-        <v>3689</v>
+        <v>3691</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -15168,7 +15168,7 @@
         <v>0</v>
       </c>
       <c r="Q216">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R216">
         <v>0</v>
@@ -15186,7 +15186,7 @@
         <v>0</v>
       </c>
       <c r="W216">
-        <v>3367</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="217">
@@ -15209,7 +15209,7 @@
         <v>53</v>
       </c>
       <c r="G217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H217">
         <v>0</v>
@@ -15239,7 +15239,7 @@
         <v>0</v>
       </c>
       <c r="Q217">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R217">
         <v>0</v>
@@ -15251,7 +15251,7 @@
         <v>0</v>
       </c>
       <c r="U217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V217">
         <v>0</v>
@@ -15271,7 +15271,7 @@
         <v>FORM7</v>
       </c>
       <c r="D218">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -15280,7 +15280,7 @@
         <v>0</v>
       </c>
       <c r="G218">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H218">
         <v>0</v>
@@ -15310,7 +15310,7 @@
         <v>0</v>
       </c>
       <c r="Q218">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="R218">
         <v>0</v>
@@ -15328,7 +15328,7 @@
         <v>0</v>
       </c>
       <c r="W218">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="219">
@@ -15342,16 +15342,16 @@
         <v>FORM8</v>
       </c>
       <c r="D219">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E219">
         <v>0</v>
       </c>
       <c r="F219">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H219">
         <v>0</v>
@@ -15381,7 +15381,7 @@
         <v>0</v>
       </c>
       <c r="Q219">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R219">
         <v>0</v>
@@ -15407,16 +15407,16 @@
         <v>AC Form Total</v>
       </c>
       <c r="D220">
-        <v>1916</v>
+        <v>1921</v>
       </c>
       <c r="E220">
         <v>0</v>
       </c>
       <c r="F220">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G220">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H220">
         <v>0</v>
@@ -15446,7 +15446,7 @@
         <v>0</v>
       </c>
       <c r="Q220">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="R220">
         <v>0</v>
@@ -15458,13 +15458,13 @@
         <v>0</v>
       </c>
       <c r="U220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V220">
         <v>0</v>
       </c>
       <c r="W220">
-        <v>1502</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="221">
@@ -15691,13 +15691,13 @@
         <v>FORM8</v>
       </c>
       <c r="D224">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E224">
         <v>0</v>
       </c>
       <c r="F224">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G224">
         <v>9</v>
@@ -15756,13 +15756,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D225">
-        <v>2289</v>
+        <v>2292</v>
       </c>
       <c r="E225">
         <v>0</v>
       </c>
       <c r="F225">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G225">
         <v>27</v>
@@ -16040,13 +16040,13 @@
         <v>FORM8</v>
       </c>
       <c r="D229">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E229">
         <v>0</v>
       </c>
       <c r="F229">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G229">
         <v>0</v>
@@ -16105,13 +16105,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D230">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="E230">
         <v>0</v>
       </c>
       <c r="F230">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G230">
         <v>0</v>
@@ -16803,13 +16803,13 @@
         <v>FORM6</v>
       </c>
       <c r="D240">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E240">
         <v>0</v>
       </c>
       <c r="F240">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G240">
         <v>1</v>
@@ -16945,13 +16945,13 @@
         <v>FORM8</v>
       </c>
       <c r="D242">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E242">
         <v>0</v>
       </c>
       <c r="F242">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G242">
         <v>0</v>
@@ -17010,13 +17010,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D243">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="E243">
         <v>0</v>
       </c>
       <c r="F243">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G243">
         <v>1</v>
@@ -17223,13 +17223,13 @@
         <v>FORM8</v>
       </c>
       <c r="D246">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E246">
         <v>0</v>
       </c>
       <c r="F246">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G246">
         <v>0</v>
@@ -17288,13 +17288,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D247">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="E247">
         <v>0</v>
       </c>
       <c r="F247">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G247">
         <v>0</v>
@@ -17501,13 +17501,13 @@
         <v>FORM8</v>
       </c>
       <c r="D250">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E250">
         <v>0</v>
       </c>
       <c r="F250">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G250">
         <v>0</v>
@@ -17566,13 +17566,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D251">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="E251">
         <v>0</v>
       </c>
       <c r="F251">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G251">
         <v>0</v>
@@ -17637,13 +17637,13 @@
         <v>FORM6</v>
       </c>
       <c r="D252">
-        <v>2156</v>
+        <v>2165</v>
       </c>
       <c r="E252">
         <v>0</v>
       </c>
       <c r="F252">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="G252">
         <v>0</v>
@@ -17708,7 +17708,7 @@
         <v>FORM7</v>
       </c>
       <c r="D253">
-        <v>3481</v>
+        <v>3483</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -17738,7 +17738,7 @@
         <v>0</v>
       </c>
       <c r="N253">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O253">
         <v>0</v>
@@ -17747,7 +17747,7 @@
         <v>0</v>
       </c>
       <c r="Q253">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="R253">
         <v>0</v>
@@ -17765,7 +17765,7 @@
         <v>0</v>
       </c>
       <c r="W253">
-        <v>2883</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="254">
@@ -17779,13 +17779,13 @@
         <v>FORM8</v>
       </c>
       <c r="D254">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="E254">
         <v>0</v>
       </c>
       <c r="F254">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G254">
         <v>0</v>
@@ -17844,13 +17844,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D255">
-        <v>6537</v>
+        <v>6552</v>
       </c>
       <c r="E255">
         <v>0</v>
       </c>
       <c r="F255">
-        <v>590</v>
+        <v>603</v>
       </c>
       <c r="G255">
         <v>0</v>
@@ -17874,7 +17874,7 @@
         <v>0</v>
       </c>
       <c r="N255">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O255">
         <v>0</v>
@@ -17883,7 +17883,7 @@
         <v>0</v>
       </c>
       <c r="Q255">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="R255">
         <v>0</v>
@@ -17901,7 +17901,7 @@
         <v>0</v>
       </c>
       <c r="W255">
-        <v>4996</v>
+        <v>4998</v>
       </c>
     </row>
     <row r="256">
@@ -17915,13 +17915,13 @@
         <v>FORM6</v>
       </c>
       <c r="D256">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="E256">
         <v>0</v>
       </c>
       <c r="F256">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G256">
         <v>0</v>
@@ -17986,7 +17986,7 @@
         <v>FORM7</v>
       </c>
       <c r="D257">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="N257">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O257">
         <v>0</v>
@@ -18025,7 +18025,7 @@
         <v>0</v>
       </c>
       <c r="Q257">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R257">
         <v>0</v>
@@ -18043,7 +18043,7 @@
         <v>0</v>
       </c>
       <c r="W257">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="258">
@@ -18122,13 +18122,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D259">
-        <v>1759</v>
+        <v>1764</v>
       </c>
       <c r="E259">
         <v>0</v>
       </c>
       <c r="F259">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G259">
         <v>0</v>
@@ -18152,7 +18152,7 @@
         <v>0</v>
       </c>
       <c r="N259">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O259">
         <v>0</v>
@@ -18161,7 +18161,7 @@
         <v>0</v>
       </c>
       <c r="Q259">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R259">
         <v>0</v>
@@ -18179,7 +18179,7 @@
         <v>0</v>
       </c>
       <c r="W259">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="260">
@@ -18193,13 +18193,13 @@
         <v>FORM6</v>
       </c>
       <c r="D260">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="E260">
         <v>0</v>
       </c>
       <c r="F260">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G260">
         <v>0</v>
@@ -18471,13 +18471,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D264">
-        <v>2269</v>
+        <v>2275</v>
       </c>
       <c r="E264">
         <v>0</v>
       </c>
       <c r="F264">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G264">
         <v>0</v>
@@ -18542,13 +18542,13 @@
         <v>FORM6</v>
       </c>
       <c r="D265">
-        <v>5639</v>
+        <v>5653</v>
       </c>
       <c r="E265">
         <v>0</v>
       </c>
       <c r="F265">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="G265">
         <v>0</v>
@@ -18684,7 +18684,7 @@
         <v>FORM7</v>
       </c>
       <c r="D267">
-        <v>9578</v>
+        <v>9584</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -18714,7 +18714,7 @@
         <v>0</v>
       </c>
       <c r="N267">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O267">
         <v>0</v>
@@ -18723,7 +18723,7 @@
         <v>0</v>
       </c>
       <c r="Q267">
-        <v>7169</v>
+        <v>7170</v>
       </c>
       <c r="R267">
         <v>1</v>
@@ -18741,7 +18741,7 @@
         <v>0</v>
       </c>
       <c r="W267">
-        <v>2404</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="268">
@@ -18755,13 +18755,13 @@
         <v>FORM8</v>
       </c>
       <c r="D268">
-        <v>2504</v>
+        <v>2510</v>
       </c>
       <c r="E268">
         <v>0</v>
       </c>
       <c r="F268">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G268">
         <v>0</v>
@@ -18820,13 +18820,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D269">
-        <v>17746</v>
+        <v>17772</v>
       </c>
       <c r="E269">
         <v>0</v>
       </c>
       <c r="F269">
-        <v>841</v>
+        <v>861</v>
       </c>
       <c r="G269">
         <v>0</v>
@@ -18850,7 +18850,7 @@
         <v>0</v>
       </c>
       <c r="N269">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O269">
         <v>0</v>
@@ -18859,7 +18859,7 @@
         <v>0</v>
       </c>
       <c r="Q269">
-        <v>8164</v>
+        <v>8165</v>
       </c>
       <c r="R269">
         <v>8</v>
@@ -18877,7 +18877,7 @@
         <v>0</v>
       </c>
       <c r="W269">
-        <v>7885</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="270">
@@ -18891,13 +18891,13 @@
         <v>FORM6</v>
       </c>
       <c r="D270">
-        <v>4933</v>
+        <v>4942</v>
       </c>
       <c r="E270">
         <v>0</v>
       </c>
       <c r="F270">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="G270">
         <v>0</v>
@@ -19033,13 +19033,13 @@
         <v>FORM7</v>
       </c>
       <c r="D272">
-        <v>2141</v>
+        <v>2154</v>
       </c>
       <c r="E272">
         <v>0</v>
       </c>
       <c r="F272">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G272">
         <v>0</v>
@@ -19063,7 +19063,7 @@
         <v>0</v>
       </c>
       <c r="N272">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O272">
         <v>0</v>
@@ -19072,7 +19072,7 @@
         <v>0</v>
       </c>
       <c r="Q272">
-        <v>998</v>
+        <v>1011</v>
       </c>
       <c r="R272">
         <v>0</v>
@@ -19090,7 +19090,7 @@
         <v>0</v>
       </c>
       <c r="W272">
-        <v>1125</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="273">
@@ -19104,13 +19104,13 @@
         <v>FORM8</v>
       </c>
       <c r="D273">
-        <v>2039</v>
+        <v>2046</v>
       </c>
       <c r="E273">
         <v>0</v>
       </c>
       <c r="F273">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G273">
         <v>0</v>
@@ -19169,13 +19169,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D274">
-        <v>9117</v>
+        <v>9146</v>
       </c>
       <c r="E274">
         <v>0</v>
       </c>
       <c r="F274">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="G274">
         <v>0</v>
@@ -19199,7 +19199,7 @@
         <v>0</v>
       </c>
       <c r="N274">
-        <v>1042</v>
+        <v>1030</v>
       </c>
       <c r="O274">
         <v>0</v>
@@ -19208,7 +19208,7 @@
         <v>0</v>
       </c>
       <c r="Q274">
-        <v>1166</v>
+        <v>1179</v>
       </c>
       <c r="R274">
         <v>4</v>
@@ -19226,7 +19226,7 @@
         <v>0</v>
       </c>
       <c r="W274">
-        <v>6037</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="275">
@@ -19240,13 +19240,13 @@
         <v>FORM6</v>
       </c>
       <c r="D275">
-        <v>2695</v>
+        <v>2697</v>
       </c>
       <c r="E275">
         <v>0</v>
       </c>
       <c r="F275">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G275">
         <v>0</v>
@@ -19382,7 +19382,7 @@
         <v>FORM7</v>
       </c>
       <c r="D277">
-        <v>2261</v>
+        <v>2266</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -19439,7 +19439,7 @@
         <v>0</v>
       </c>
       <c r="W277">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="278">
@@ -19453,13 +19453,13 @@
         <v>FORM8</v>
       </c>
       <c r="D278">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="E278">
         <v>0</v>
       </c>
       <c r="F278">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G278">
         <v>0</v>
@@ -19518,13 +19518,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D279">
-        <v>6190</v>
+        <v>6199</v>
       </c>
       <c r="E279">
         <v>0</v>
       </c>
       <c r="F279">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G279">
         <v>0</v>
@@ -19575,7 +19575,7 @@
         <v>0</v>
       </c>
       <c r="W279">
-        <v>3494</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="280">
@@ -19589,13 +19589,13 @@
         <v>FORM6</v>
       </c>
       <c r="D280">
-        <v>3740</v>
+        <v>3751</v>
       </c>
       <c r="E280">
         <v>0</v>
       </c>
       <c r="F280">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="G280">
         <v>4</v>
@@ -19660,13 +19660,13 @@
         <v>FORM6A</v>
       </c>
       <c r="D281">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E281">
         <v>0</v>
       </c>
       <c r="F281">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G281">
         <v>0</v>
@@ -19770,7 +19770,7 @@
         <v>0</v>
       </c>
       <c r="Q282">
-        <v>6273</v>
+        <v>6274</v>
       </c>
       <c r="R282">
         <v>0</v>
@@ -19782,7 +19782,7 @@
         <v>0</v>
       </c>
       <c r="U282">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V282">
         <v>0</v>
@@ -19802,13 +19802,13 @@
         <v>FORM8</v>
       </c>
       <c r="D283">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="E283">
         <v>0</v>
       </c>
       <c r="F283">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G283">
         <v>0</v>
@@ -19867,13 +19867,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D284">
-        <v>15397</v>
+        <v>15414</v>
       </c>
       <c r="E284">
         <v>0</v>
       </c>
       <c r="F284">
-        <v>881</v>
+        <v>898</v>
       </c>
       <c r="G284">
         <v>4</v>
@@ -19906,7 +19906,7 @@
         <v>0</v>
       </c>
       <c r="Q284">
-        <v>7562</v>
+        <v>7563</v>
       </c>
       <c r="R284">
         <v>0</v>
@@ -19918,7 +19918,7 @@
         <v>0</v>
       </c>
       <c r="U284">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V284">
         <v>0</v>
@@ -19938,13 +19938,13 @@
         <v>FORM6</v>
       </c>
       <c r="D285">
-        <v>6077</v>
+        <v>6115</v>
       </c>
       <c r="E285">
         <v>0</v>
       </c>
       <c r="F285">
-        <v>1213</v>
+        <v>1251</v>
       </c>
       <c r="G285">
         <v>0</v>
@@ -20151,13 +20151,13 @@
         <v>FORM8</v>
       </c>
       <c r="D288">
-        <v>2235</v>
+        <v>2241</v>
       </c>
       <c r="E288">
         <v>0</v>
       </c>
       <c r="F288">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="G288">
         <v>0</v>
@@ -20216,13 +20216,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D289">
-        <v>18779</v>
+        <v>18823</v>
       </c>
       <c r="E289">
         <v>0</v>
       </c>
       <c r="F289">
-        <v>1462</v>
+        <v>1506</v>
       </c>
       <c r="G289">
         <v>0</v>
@@ -20287,13 +20287,13 @@
         <v>FORM6</v>
       </c>
       <c r="D290">
-        <v>3522</v>
+        <v>3535</v>
       </c>
       <c r="E290">
         <v>0</v>
       </c>
       <c r="F290">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="G290">
         <v>0</v>
@@ -20500,13 +20500,13 @@
         <v>FORM8</v>
       </c>
       <c r="D293">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="E293">
         <v>0</v>
       </c>
       <c r="F293">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G293">
         <v>0</v>
@@ -20539,10 +20539,10 @@
         <v>0</v>
       </c>
       <c r="Q293">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S293">
         <v>0</v>
@@ -20565,13 +20565,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D294">
-        <v>11818</v>
+        <v>11834</v>
       </c>
       <c r="E294">
         <v>0</v>
       </c>
       <c r="F294">
-        <v>791</v>
+        <v>807</v>
       </c>
       <c r="G294">
         <v>0</v>
@@ -20604,10 +20604,10 @@
         <v>0</v>
       </c>
       <c r="Q294">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="R294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S294">
         <v>0</v>
@@ -20636,13 +20636,13 @@
         <v>FORM6</v>
       </c>
       <c r="D295">
-        <v>1421</v>
+        <v>1426</v>
       </c>
       <c r="E295">
         <v>0</v>
       </c>
       <c r="F295">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G295">
         <v>0</v>
@@ -20778,13 +20778,13 @@
         <v>FORM8</v>
       </c>
       <c r="D297">
-        <v>962</v>
+        <v>978</v>
       </c>
       <c r="E297">
         <v>0</v>
       </c>
       <c r="F297">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="G297">
         <v>0</v>
@@ -20843,13 +20843,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D298">
-        <v>13183</v>
+        <v>13204</v>
       </c>
       <c r="E298">
         <v>0</v>
       </c>
       <c r="F298">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="G298">
         <v>0</v>
@@ -20914,13 +20914,13 @@
         <v>FORM6</v>
       </c>
       <c r="D299">
-        <v>3040</v>
+        <v>3047</v>
       </c>
       <c r="E299">
         <v>0</v>
       </c>
       <c r="F299">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="G299">
         <v>0</v>
@@ -21127,13 +21127,13 @@
         <v>FORM8</v>
       </c>
       <c r="D302">
-        <v>1491</v>
+        <v>1504</v>
       </c>
       <c r="E302">
         <v>0</v>
       </c>
       <c r="F302">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="G302">
         <v>0</v>
@@ -21192,13 +21192,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D303">
-        <v>13324</v>
+        <v>13344</v>
       </c>
       <c r="E303">
         <v>0</v>
       </c>
       <c r="F303">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="G303">
         <v>0</v>
@@ -21263,13 +21263,13 @@
         <v>FORM6</v>
       </c>
       <c r="D304">
-        <v>1856</v>
+        <v>1869</v>
       </c>
       <c r="E304">
         <v>0</v>
       </c>
       <c r="F304">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="G304">
         <v>0</v>
@@ -21405,13 +21405,13 @@
         <v>FORM8</v>
       </c>
       <c r="D306">
-        <v>1185</v>
+        <v>1194</v>
       </c>
       <c r="E306">
         <v>0</v>
       </c>
       <c r="F306">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G306">
         <v>0</v>
@@ -21444,7 +21444,7 @@
         <v>0</v>
       </c>
       <c r="Q306">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="R306">
         <v>0</v>
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="U306">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V306">
         <v>0</v>
@@ -21470,13 +21470,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D307">
-        <v>18198</v>
+        <v>18220</v>
       </c>
       <c r="E307">
         <v>0</v>
       </c>
       <c r="F307">
-        <v>551</v>
+        <v>573</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="Q307">
-        <v>10825</v>
+        <v>10851</v>
       </c>
       <c r="R307">
         <v>0</v>
@@ -21521,7 +21521,7 @@
         <v>0</v>
       </c>
       <c r="U307">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V307">
         <v>0</v>
@@ -21541,13 +21541,13 @@
         <v>FORM6</v>
       </c>
       <c r="D308">
-        <v>2475</v>
+        <v>2481</v>
       </c>
       <c r="E308">
         <v>0</v>
       </c>
       <c r="F308">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="G308">
         <v>0</v>
@@ -21683,13 +21683,13 @@
         <v>FORM8</v>
       </c>
       <c r="D310">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="E310">
         <v>0</v>
       </c>
       <c r="F310">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G310">
         <v>0</v>
@@ -21748,13 +21748,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D311">
-        <v>6934</v>
+        <v>6948</v>
       </c>
       <c r="E311">
         <v>0</v>
       </c>
       <c r="F311">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="G311">
         <v>0</v>
@@ -21819,13 +21819,13 @@
         <v>FORM6</v>
       </c>
       <c r="D312">
-        <v>1750</v>
+        <v>1754</v>
       </c>
       <c r="E312">
         <v>0</v>
       </c>
       <c r="F312">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G312">
         <v>0</v>
@@ -21858,10 +21858,10 @@
         <v>0</v>
       </c>
       <c r="Q312">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R312">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S312">
         <v>0</v>
@@ -21911,7 +21911,7 @@
         <v>0</v>
       </c>
       <c r="K313">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L313">
         <v>0</v>
@@ -21929,10 +21929,10 @@
         <v>0</v>
       </c>
       <c r="Q313">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="R313">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S313">
         <v>0</v>
@@ -21961,13 +21961,13 @@
         <v>FORM8</v>
       </c>
       <c r="D314">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E314">
         <v>0</v>
       </c>
       <c r="F314">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G314">
         <v>0</v>
@@ -22000,10 +22000,10 @@
         <v>0</v>
       </c>
       <c r="Q314">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="R314">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S314">
         <v>0</v>
@@ -22026,13 +22026,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D315">
-        <v>5701</v>
+        <v>5706</v>
       </c>
       <c r="E315">
         <v>0</v>
       </c>
       <c r="F315">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="G315">
         <v>0</v>
@@ -22047,7 +22047,7 @@
         <v>0</v>
       </c>
       <c r="K315">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L315">
         <v>0</v>
@@ -22065,10 +22065,10 @@
         <v>0</v>
       </c>
       <c r="Q315">
-        <v>1725</v>
+        <v>1739</v>
       </c>
       <c r="R315">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S315">
         <v>0</v>
@@ -22097,13 +22097,13 @@
         <v>FORM6</v>
       </c>
       <c r="D316">
-        <v>1405</v>
+        <v>1415</v>
       </c>
       <c r="E316">
         <v>0</v>
       </c>
       <c r="F316">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="G316">
         <v>8</v>
@@ -22239,7 +22239,7 @@
         <v>FORM7</v>
       </c>
       <c r="D318">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -22296,7 +22296,7 @@
         <v>0</v>
       </c>
       <c r="W318">
-        <v>1160</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="319">
@@ -22310,13 +22310,13 @@
         <v>FORM8</v>
       </c>
       <c r="D319">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E319">
         <v>0</v>
       </c>
       <c r="F319">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G319">
         <v>0</v>
@@ -22375,13 +22375,13 @@
         <v>AC Form Total</v>
       </c>
       <c r="D320">
-        <v>4545</v>
+        <v>4559</v>
       </c>
       <c r="E320">
         <v>0</v>
       </c>
       <c r="F320">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="G320">
         <v>11</v>
@@ -22432,7 +22432,7 @@
         <v>0</v>
       </c>
       <c r="W320">
-        <v>2836</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="321">
@@ -22440,16 +22440,16 @@
         <v>All AC Form-6 Total</v>
       </c>
       <c r="D321">
-        <v>166971</v>
+        <v>167258</v>
       </c>
       <c r="E321">
         <v>0</v>
       </c>
       <c r="F321">
-        <v>15877</v>
+        <v>16164</v>
       </c>
       <c r="G321">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H321">
         <v>92</v>
@@ -22479,19 +22479,19 @@
         <v>0</v>
       </c>
       <c r="Q321">
-        <v>16630</v>
+        <v>16637</v>
       </c>
       <c r="R321">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S321">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T321">
         <v>0</v>
       </c>
       <c r="U321">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V321">
         <v>0</v>
@@ -22505,13 +22505,13 @@
         <v>All AC Form-6A Total</v>
       </c>
       <c r="D322">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E322">
         <v>0</v>
       </c>
       <c r="F322">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G322">
         <v>0</v>
@@ -22570,16 +22570,16 @@
         <v>All AC Form-7 Total</v>
       </c>
       <c r="D323">
-        <v>194469</v>
+        <v>194610</v>
       </c>
       <c r="E323">
         <v>0</v>
       </c>
       <c r="F323">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="G323">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="H323">
         <v>0</v>
@@ -22600,7 +22600,7 @@
         <v>1</v>
       </c>
       <c r="N323">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="O323">
         <v>0</v>
@@ -22609,25 +22609,25 @@
         <v>0</v>
       </c>
       <c r="Q323">
-        <v>89089</v>
+        <v>89173</v>
       </c>
       <c r="R323">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S323">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T323">
         <v>0</v>
       </c>
       <c r="U323">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V323">
         <v>0</v>
       </c>
       <c r="W323">
-        <v>104607</v>
+        <v>104736</v>
       </c>
     </row>
     <row r="324">
@@ -22635,16 +22635,16 @@
         <v>All AC Form-8 Total</v>
       </c>
       <c r="D324">
-        <v>64139</v>
+        <v>64329</v>
       </c>
       <c r="E324">
         <v>0</v>
       </c>
       <c r="F324">
-        <v>7951</v>
+        <v>8139</v>
       </c>
       <c r="G324">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="H324">
         <v>0</v>
@@ -22674,19 +22674,19 @@
         <v>0</v>
       </c>
       <c r="Q324">
-        <v>5549</v>
+        <v>5598</v>
       </c>
       <c r="R324">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="S324">
+        <v>0</v>
+      </c>
+      <c r="T324">
+        <v>0</v>
+      </c>
+      <c r="U324">
         <v>1</v>
-      </c>
-      <c r="T324">
-        <v>0</v>
-      </c>
-      <c r="U324">
-        <v>26</v>
       </c>
       <c r="V324">
         <v>0</v>
@@ -22700,16 +22700,16 @@
         <v>All AC Form Total</v>
       </c>
       <c r="D325">
-        <v>425732</v>
+        <v>426351</v>
       </c>
       <c r="E325">
         <v>0</v>
       </c>
       <c r="F325">
-        <v>24123</v>
+        <v>24563</v>
       </c>
       <c r="G325">
-        <v>773</v>
+        <v>744</v>
       </c>
       <c r="H325">
         <v>92</v>
@@ -22730,7 +22730,7 @@
         <v>40</v>
       </c>
       <c r="N325">
-        <v>9417</v>
+        <v>9398</v>
       </c>
       <c r="O325">
         <v>5</v>
@@ -22739,25 +22739,25 @@
         <v>0</v>
       </c>
       <c r="Q325">
-        <v>111379</v>
+        <v>111519</v>
       </c>
       <c r="R325">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="S325">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T325">
         <v>0</v>
       </c>
       <c r="U325">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="V325">
         <v>0</v>
       </c>
       <c r="W325">
-        <v>279653</v>
+        <v>279782</v>
       </c>
     </row>
   </sheetData>
